--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B95E6315-B349-471A-9A6F-CD2E5FBB4D08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E894B4-E949-4658-87AB-9E0096180C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5473" uniqueCount="1932">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5539" uniqueCount="1956">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5836,6 +5836,78 @@
   </si>
   <si>
     <t>Dispositivo Elétrico - sobrepor - Tampa PVC p/ condulete - Interruptor 2 teclas simples</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 240 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 240 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 240 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 240 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. EPR - 0,6/1kV - 120 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 500x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>COMP 520</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 500 E ALTURA 100MM E , INCLUSIVE FIXAÇÃO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: 061106 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Suporte vertical - 70x183mm</t>
+  </si>
+  <si>
+    <t>COMP 1093</t>
+  </si>
+  <si>
+    <t>SUPORTE VERTICAL - 70X183MM (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1900x800x800mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23</t>
+  </si>
+  <si>
+    <t>COMP 1501</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -1900x800x800mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 1000 A - 50 kA</t>
+  </si>
+  <si>
+    <t>COMP 1109</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 1000A, 60kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva horizontal 90° - 500x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>Gerador - Gerador de energia a diesel - 550 kVA</t>
+  </si>
+  <si>
+    <t>COMP 868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRUPO GERADOR 500 kVA - (REFERÊNCIA SBC 065016 05/2023)  </t>
+  </si>
+  <si>
+    <t>COMP 517</t>
+  </si>
+  <si>
+    <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 500MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Eletroduto metálico rígido leve - Braçadeira galvan. tipo D - 1"</t>
   </si>
 </sst>
 </file>
@@ -6234,7 +6306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1016"/>
+  <dimension ref="A1:B1028"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -14369,6 +14441,102 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1017" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1017" s="3" t="s">
+        <v>1932</v>
+      </c>
+      <c r="B1017" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1018" s="3" t="s">
+        <v>1933</v>
+      </c>
+      <c r="B1018" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1019" s="3" t="s">
+        <v>1934</v>
+      </c>
+      <c r="B1019" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1020" s="3" t="s">
+        <v>1935</v>
+      </c>
+      <c r="B1020" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1021" s="3" t="s">
+        <v>1936</v>
+      </c>
+      <c r="B1021" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1022" s="3" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1022" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1023" s="3" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1023" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1024" s="3" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1024" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1025" s="3" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1025" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1026" s="3" t="s">
+        <v>1949</v>
+      </c>
+      <c r="B1026" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1027" s="3" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1027" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1028" s="3" t="s">
+        <v>1955</v>
+      </c>
+      <c r="B1028" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14376,7 +14544,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1016"/>
+  <dimension ref="A1:D1028"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -28609,6 +28777,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1017" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1017" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1017" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1017" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1017" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1018" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1018" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1018" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1018" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1018" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1019" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1019" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1019" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1019" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1019" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1020" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1020" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1020" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1020" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1020" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1021" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1021" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1021" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1021" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1021" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1022" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1022" s="5" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B1022" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1022" s="3" t="s">
+        <v>1939</v>
+      </c>
+      <c r="D1022" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1023" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1023" s="5" t="s">
+        <v>1941</v>
+      </c>
+      <c r="B1023" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1023" s="3" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D1023" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1024" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1024" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1024" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1024" s="3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1024" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1025" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1025" s="5" t="s">
+        <v>1947</v>
+      </c>
+      <c r="B1025" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1025" s="3" t="s">
+        <v>1948</v>
+      </c>
+      <c r="D1025" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1026" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1026" s="5" t="s">
+        <v>1953</v>
+      </c>
+      <c r="B1026" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1026" s="3" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D1026" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1027" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1027" s="5" t="s">
+        <v>1951</v>
+      </c>
+      <c r="B1027" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1027" s="3" t="s">
+        <v>1952</v>
+      </c>
+      <c r="D1027" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1028" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1028" s="5">
+        <v>91868</v>
+      </c>
+      <c r="B1028" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1028" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="D1028" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9E894B4-E949-4658-87AB-9E0096180C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F503F3EE-7863-45DB-8E87-82F7D0840CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5539" uniqueCount="1956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5849" uniqueCount="2033">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5907,7 +5907,238 @@
     <t>CURVA HORIZONTAL 90º PARA ELETROCALHA, LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA DE 500MM E ALTURA DE 100MM - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97278 - 02/2023)</t>
   </si>
   <si>
-    <t>Eletroduto metálico rígido leve - Braçadeira galvan. tipo D - 1"</t>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 1.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 1.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 1.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 1.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 10 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 10 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 120 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 120 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 120 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 120 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 16 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 16 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 16 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 16 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 2.5 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 2.5 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 2.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 2.5 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 2.5 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 2.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 25 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 25 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 35 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 4 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 4 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 50 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 6 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 6 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 70 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 70 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 70 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 70 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 95 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 95 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 95 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 95 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1200x800x350mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23</t>
+  </si>
+  <si>
+    <t>COMP 821</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -800x600x350mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23</t>
+  </si>
+  <si>
+    <t>COMP 525</t>
+  </si>
+  <si>
+    <t>Dispositivo de Comando - Interruptor autom. por presença - 220V - 1200W resistivo</t>
+  </si>
+  <si>
+    <t>SENSOR DE PRESENÇA SEM FOTOCÉLULA, FIXAÇÃO EM TETO - FORNECIMENTO E INSTALAÇÃO. AF_09/2024</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 70 A - 18 kA</t>
+  </si>
+  <si>
+    <t>COMP 1085</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 70A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 250 A - 18 kA</t>
+  </si>
+  <si>
+    <t>COMP 951</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 500 A - 50 kA</t>
+  </si>
+  <si>
+    <t>COMP 1395</t>
+  </si>
+  <si>
+    <t>Dispositivo de Transferência - Chave de Transferência Automática - 4 polos - 630A</t>
+  </si>
+  <si>
+    <t>COMP 1781</t>
+  </si>
+  <si>
+    <t>CHAVE DE TRANSFERÊNCIA AUTOMÁTICA 630A 4 POLOS (COMPOSIÇÃO DE REFERÊNCIA: CPOS/CDHU 37.14.640 - 09/2026)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 4x4" - Interruptor 3 teclas simples</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical externa 90° - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>COMP 1783</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL EXTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 400X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0644-0 01/2026)</t>
+  </si>
+  <si>
+    <t>Estabilizador de rede - Nobreak - 80kVA</t>
+  </si>
+  <si>
+    <t>COMP 1782</t>
+  </si>
+  <si>
+    <t>NOBREAK SENOIDAL TRIFÁSICO 80 KVA – AUTONOMIA DE 15MIN – TENSÃO DE ENTRADA 220V/TENSÃO DE SAÍDA 220V (COMPOSIÇÃO REFERÊNCIA: SIURB 9010082 - 01/2026)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical interna 90° - 100x100mm chapa 18</t>
+  </si>
+  <si>
+    <t>COMP 1784</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL INTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 100X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0724-0 01/2026)</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Curva vertical interna 90° - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>COMP 1785</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL INTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 400X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0724-0 01/2026)</t>
   </si>
 </sst>
 </file>
@@ -6306,7 +6537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1028"/>
+  <dimension ref="A1:B1088"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -14537,6 +14768,486 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1029" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1029" s="3" t="s">
+        <v>1956</v>
+      </c>
+      <c r="B1029" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1030" s="3" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B1030" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1031" s="3" t="s">
+        <v>1958</v>
+      </c>
+      <c r="B1031" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1032" s="3" t="s">
+        <v>1959</v>
+      </c>
+      <c r="B1032" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1033" s="3" t="s">
+        <v>1960</v>
+      </c>
+      <c r="B1033" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1034" s="3" t="s">
+        <v>1961</v>
+      </c>
+      <c r="B1034" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1035" s="3" t="s">
+        <v>1962</v>
+      </c>
+      <c r="B1035" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1036" s="3" t="s">
+        <v>1963</v>
+      </c>
+      <c r="B1036" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1037" s="3" t="s">
+        <v>1964</v>
+      </c>
+      <c r="B1037" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1038" s="3" t="s">
+        <v>1965</v>
+      </c>
+      <c r="B1038" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1039" s="3" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B1039" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1040" s="3" t="s">
+        <v>1967</v>
+      </c>
+      <c r="B1040" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1041" s="3" t="s">
+        <v>1968</v>
+      </c>
+      <c r="B1041" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1042" s="3" t="s">
+        <v>1969</v>
+      </c>
+      <c r="B1042" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1043" s="3" t="s">
+        <v>1970</v>
+      </c>
+      <c r="B1043" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1044" s="3" t="s">
+        <v>1971</v>
+      </c>
+      <c r="B1044" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1045" s="3" t="s">
+        <v>1972</v>
+      </c>
+      <c r="B1045" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1046" s="3" t="s">
+        <v>1973</v>
+      </c>
+      <c r="B1046" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1047" s="3" t="s">
+        <v>1974</v>
+      </c>
+      <c r="B1047" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1048" s="3" t="s">
+        <v>1975</v>
+      </c>
+      <c r="B1048" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1049" s="3" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B1049" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1050" s="3" t="s">
+        <v>1977</v>
+      </c>
+      <c r="B1050" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1051" s="3" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B1051" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1052" s="3" t="s">
+        <v>1979</v>
+      </c>
+      <c r="B1052" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1053" s="3" t="s">
+        <v>1980</v>
+      </c>
+      <c r="B1053" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1054" s="3" t="s">
+        <v>1981</v>
+      </c>
+      <c r="B1054" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1055" s="3" t="s">
+        <v>1982</v>
+      </c>
+      <c r="B1055" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1056" s="3" t="s">
+        <v>1983</v>
+      </c>
+      <c r="B1056" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1057" s="3" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B1057" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1058" s="3" t="s">
+        <v>1985</v>
+      </c>
+      <c r="B1058" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1059" s="3" t="s">
+        <v>1986</v>
+      </c>
+      <c r="B1059" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1060" s="3" t="s">
+        <v>1987</v>
+      </c>
+      <c r="B1060" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1061" s="3" t="s">
+        <v>1988</v>
+      </c>
+      <c r="B1061" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1062" s="3" t="s">
+        <v>1989</v>
+      </c>
+      <c r="B1062" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1063" s="3" t="s">
+        <v>1990</v>
+      </c>
+      <c r="B1063" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1064" s="3" t="s">
+        <v>1991</v>
+      </c>
+      <c r="B1064" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1065" s="3" t="s">
+        <v>1992</v>
+      </c>
+      <c r="B1065" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1066" s="3" t="s">
+        <v>1993</v>
+      </c>
+      <c r="B1066" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1067" s="3" t="s">
+        <v>1994</v>
+      </c>
+      <c r="B1067" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1068" s="3" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B1068" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1069" s="3" t="s">
+        <v>1996</v>
+      </c>
+      <c r="B1069" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1070" s="3" t="s">
+        <v>1997</v>
+      </c>
+      <c r="B1070" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1071" s="3" t="s">
+        <v>1998</v>
+      </c>
+      <c r="B1071" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1072" s="3" t="s">
+        <v>1999</v>
+      </c>
+      <c r="B1072" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1073" s="3" t="s">
+        <v>2000</v>
+      </c>
+      <c r="B1073" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1074" s="3" t="s">
+        <v>2001</v>
+      </c>
+      <c r="B1074" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1075" s="3" t="s">
+        <v>2002</v>
+      </c>
+      <c r="B1075" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1076" s="3" t="s">
+        <v>2003</v>
+      </c>
+      <c r="B1076" s="6" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1077" s="3" t="s">
+        <v>2004</v>
+      </c>
+      <c r="B1077" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1078" s="3" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B1078" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1079" s="3" t="s">
+        <v>2008</v>
+      </c>
+      <c r="B1079" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1080" s="3" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B1080" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1081" s="3" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B1081" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1082" s="3" t="s">
+        <v>2015</v>
+      </c>
+      <c r="B1082" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1083" s="3" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1083" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1084" s="3" t="s">
+        <v>2020</v>
+      </c>
+      <c r="B1084" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1085" s="3" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1085" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1086" s="3" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B1086" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1087" s="3" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1087" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1088" s="3" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B1088" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -14544,7 +15255,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1028"/>
+  <dimension ref="A1:D1088"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -28931,18 +29642,858 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1028" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="1028" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1028" s="5">
-        <v>91868</v>
+        <v>91925</v>
       </c>
       <c r="B1028" s="5" t="s">
         <v>5</v>
       </c>
       <c r="C1028" s="3" t="s">
-        <v>406</v>
+        <v>19</v>
       </c>
       <c r="D1028" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="1029" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1029" s="5">
+        <v>91925</v>
+      </c>
+      <c r="B1029" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1029" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1029" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1030" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1030" s="5">
+        <v>91925</v>
+      </c>
+      <c r="B1030" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1030" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1030" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1031" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1031" s="5">
+        <v>91925</v>
+      </c>
+      <c r="B1031" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1031" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1031" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1032" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1032" s="5">
+        <v>91925</v>
+      </c>
+      <c r="B1032" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1032" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1032" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1033" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1033" s="5">
+        <v>91933</v>
+      </c>
+      <c r="B1033" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1033" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1033" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1034" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1034" s="5">
+        <v>91933</v>
+      </c>
+      <c r="B1034" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1034" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1034" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1035" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1035" s="5">
+        <v>91933</v>
+      </c>
+      <c r="B1035" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1035" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1035" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1036" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1036" s="5">
+        <v>91933</v>
+      </c>
+      <c r="B1036" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1036" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1036" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1037" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1037" s="5">
+        <v>91933</v>
+      </c>
+      <c r="B1037" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1037" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D1037" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1038" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1038" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B1038" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1038" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1038" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1039" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1039" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B1039" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1039" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1039" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1040" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1040" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B1040" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1040" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1040" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1041" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1041" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B1041" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1041" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1041" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1042" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1042" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B1042" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1042" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1042" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1043" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1043" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B1043" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1043" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1043" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1044" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1044" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B1044" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1044" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1044" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1045" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1045" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B1045" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1045" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1045" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1046" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1046" s="5">
+        <v>91935</v>
+      </c>
+      <c r="B1046" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1046" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1046" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1047" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1047" s="5">
+        <v>91927</v>
+      </c>
+      <c r="B1047" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1047" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1047" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1048" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1048" s="5">
+        <v>91927</v>
+      </c>
+      <c r="B1048" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1048" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1048" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1049" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1049" s="5">
+        <v>91927</v>
+      </c>
+      <c r="B1049" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1049" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1049" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1050" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1050" s="5">
+        <v>91927</v>
+      </c>
+      <c r="B1050" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1050" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1050" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1051" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1051" s="5">
+        <v>91927</v>
+      </c>
+      <c r="B1051" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1051" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1051" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1052" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1052" s="5">
+        <v>91927</v>
+      </c>
+      <c r="B1052" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1052" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D1052" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1053" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1053" s="5">
+        <v>92984</v>
+      </c>
+      <c r="B1053" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1053" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1053" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1054" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1054" s="5">
+        <v>92984</v>
+      </c>
+      <c r="B1054" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1054" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1054" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1055" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1055" s="5">
+        <v>92984</v>
+      </c>
+      <c r="B1055" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1055" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1055" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1056" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1056" s="5">
+        <v>92984</v>
+      </c>
+      <c r="B1056" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1056" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1056" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1057" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1057" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B1057" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1057" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1057" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1058" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1058" s="5">
+        <v>91929</v>
+      </c>
+      <c r="B1058" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1058" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1058" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1059" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1059" s="5">
+        <v>91929</v>
+      </c>
+      <c r="B1059" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1059" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1059" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1060" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1060" s="5">
+        <v>91929</v>
+      </c>
+      <c r="B1060" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1060" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1060" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1061" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1061" s="5">
+        <v>91929</v>
+      </c>
+      <c r="B1061" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1061" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1061" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1062" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1062" s="5">
+        <v>91929</v>
+      </c>
+      <c r="B1062" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1062" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1062" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1063" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1063" s="5">
+        <v>92988</v>
+      </c>
+      <c r="B1063" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1063" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1063" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1064" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1064" s="5">
+        <v>91931</v>
+      </c>
+      <c r="B1064" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1064" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1064" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1065" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1065" s="5">
+        <v>91931</v>
+      </c>
+      <c r="B1065" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1065" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1065" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1066" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1066" s="5">
+        <v>91931</v>
+      </c>
+      <c r="B1066" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1066" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1066" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1067" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1067" s="5">
+        <v>91931</v>
+      </c>
+      <c r="B1067" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1067" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1067" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1068" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1068" s="5">
+        <v>91931</v>
+      </c>
+      <c r="B1068" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1068" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1068" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1069" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1069" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B1069" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1069" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1069" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1070" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1070" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B1070" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1070" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1070" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1071" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1071" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B1071" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1071" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1071" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1072" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1072" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B1072" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1072" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1072" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1073" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1073" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B1073" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1073" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1073" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1074" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1074" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B1074" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1074" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1074" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1075" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1075" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B1075" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1075" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1075" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1076" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1076" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B1076" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1076" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1076" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1077" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1077" s="5" t="s">
+        <v>2005</v>
+      </c>
+      <c r="B1077" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1077" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="D1077" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1078" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1078" s="5" t="s">
+        <v>2007</v>
+      </c>
+      <c r="B1078" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1078" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="D1078" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1079" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1079" s="5">
+        <v>97598</v>
+      </c>
+      <c r="B1079" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1079" s="3" t="s">
+        <v>2009</v>
+      </c>
+      <c r="D1079" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1080" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1080" s="5" t="s">
+        <v>2011</v>
+      </c>
+      <c r="B1080" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1080" s="3" t="s">
+        <v>2012</v>
+      </c>
+      <c r="D1080" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1081" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1081" s="5" t="s">
+        <v>2014</v>
+      </c>
+      <c r="B1081" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1081" s="3" t="s">
+        <v>1788</v>
+      </c>
+      <c r="D1081" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1082" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1082" s="5" t="s">
+        <v>2016</v>
+      </c>
+      <c r="B1082" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1082" s="3" t="s">
+        <v>825</v>
+      </c>
+      <c r="D1082" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1083" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1083" s="5" t="s">
+        <v>2018</v>
+      </c>
+      <c r="B1083" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1083" s="3" t="s">
+        <v>2019</v>
+      </c>
+      <c r="D1083" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1084" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1084" s="5">
+        <v>91967</v>
+      </c>
+      <c r="B1084" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1084" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="D1084" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1085" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1085" s="5" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B1085" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1085" s="3" t="s">
+        <v>2023</v>
+      </c>
+      <c r="D1085" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1086" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1086" s="5" t="s">
+        <v>2025</v>
+      </c>
+      <c r="B1086" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1086" s="3" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D1086" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1087" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1087" s="5" t="s">
+        <v>2028</v>
+      </c>
+      <c r="B1087" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1087" s="3" t="s">
+        <v>2029</v>
+      </c>
+      <c r="D1087" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1088" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1088" s="5" t="s">
+        <v>2031</v>
+      </c>
+      <c r="B1088" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1088" s="3" t="s">
+        <v>2032</v>
+      </c>
+      <c r="D1088" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F503F3EE-7863-45DB-8E87-82F7D0840CBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D1CC8A-2AD3-4AED-9E0A-4EF53725C96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5849" uniqueCount="2033">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5885" uniqueCount="2051">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6139,6 +6139,60 @@
   </si>
   <si>
     <t>CURVA VERTICAL INTERNA, 90º, PARA ELETROCALHA PERFURADA OU LISA, 400X100MM. FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO REFERÊNCIA: EMOP 15.018.0724-0 01/2026)</t>
+  </si>
+  <si>
+    <t>COMP 1786</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 12 W - FORNECIMENTO E INSTALAÇÃO. AF_09/2024 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103786 - 08/2026)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Painel Pop Embutir Quadrado 12W</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Painel Pop Embutir Quadrado 18W</t>
+  </si>
+  <si>
+    <t>COMP 481</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA PLAFON QUADRADA, DE EMBUTIR, COM LÂMPADA LED 18W, SOQUETE E27 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>COMP 1787</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 24 W - FORNECIMENTO E INSTALAÇÃO. AF_09/2024 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103786 - 08/2026)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Painel Pop Embutir Quadrado 24W</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Painel Pop Embutir Quadrado 30W</t>
+  </si>
+  <si>
+    <t>COMP 1788</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 30 W - FORNECIMENTO E INSTALAÇÃO. AF_09/2024 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103786 - 08/2026)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Painel Pop Embutir Quadrado 40W</t>
+  </si>
+  <si>
+    <t>COMP 1789</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO PLAFON QUADRADA, DE EMBUTIR, COM LED DE 40 W - FORNECIMENTO E INSTALAÇÃO. AF_09/2024 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103786 - 08/2026)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 25 A - 18 kA</t>
+  </si>
+  <si>
+    <t>COMP 1790</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 25A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -6537,7 +6591,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1088"/>
+  <dimension ref="A1:B1094"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15248,6 +15302,54 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1089" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1089" s="3" t="s">
+        <v>2035</v>
+      </c>
+      <c r="B1089" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1090" s="3" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B1090" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1091" s="3" t="s">
+        <v>2041</v>
+      </c>
+      <c r="B1091" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1092" s="3" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1092" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1093" s="3" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1093" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1094" s="3" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1094" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15255,7 +15357,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1088"/>
+  <dimension ref="A1:D1094"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -30496,6 +30598,90 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1089" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1089" s="5" t="s">
+        <v>2033</v>
+      </c>
+      <c r="B1089" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1089" s="3" t="s">
+        <v>2034</v>
+      </c>
+      <c r="D1089" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1090" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1090" s="5" t="s">
+        <v>2037</v>
+      </c>
+      <c r="B1090" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1090" s="3" t="s">
+        <v>2038</v>
+      </c>
+      <c r="D1090" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1091" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1091" s="5" t="s">
+        <v>2039</v>
+      </c>
+      <c r="B1091" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1091" s="3" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D1091" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1092" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1092" s="5" t="s">
+        <v>2043</v>
+      </c>
+      <c r="B1092" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1092" s="3" t="s">
+        <v>2044</v>
+      </c>
+      <c r="D1092" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1093" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1093" s="5" t="s">
+        <v>2046</v>
+      </c>
+      <c r="B1093" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1093" s="3" t="s">
+        <v>2047</v>
+      </c>
+      <c r="D1093" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1094" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1094" s="5" t="s">
+        <v>2049</v>
+      </c>
+      <c r="B1094" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1094" s="3" t="s">
+        <v>2050</v>
+      </c>
+      <c r="D1094" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03D1CC8A-2AD3-4AED-9E0A-4EF53725C96E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DC3AE8-9E33-4495-9553-977863B0A97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5885" uniqueCount="2051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5985" uniqueCount="2095">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6193,6 +6193,138 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA MOLDADA 25A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva B - 25 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 380 V/220 V - DIN - Curva B - 32 A - 4.5 kA</t>
+  </si>
+  <si>
+    <t>COMP 1581</t>
+  </si>
+  <si>
+    <t>.S.O.S CFTV e Segurança - CFTV - IP/POE - Câmera de Segurança tipo Dome 90° IP66</t>
+  </si>
+  <si>
+    <t>CÂMERA IP SPEED DOME - FORNECIMENTO E INSTALAÇÃO.( COMPOSIÇÃO REFERÊNCIA SINAPI CÓD. 105550 08/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Rack - Sistema UPS para Rack - recomendação mínima - Nobreak 2200VA - Ref: Atrium Rack 2200 VA, SMS</t>
+  </si>
+  <si>
+    <t>COMP 1187</t>
+  </si>
+  <si>
+    <t>NOBREAK APC SMART-UPS X 3000VA RM MONO115 SMX3000LV2U-BR (COMPOSIÇÃO DE REFERÊNCIA: ORSE 13119 - 03/2025)</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Mini Rack de Parede - 12U unc 19” x 570mm MRD 1257</t>
+  </si>
+  <si>
+    <t>COMP 72</t>
+  </si>
+  <si>
+    <t>RACK ABERTO PADRÃO 19" 12U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 32U unc 19” x 670mm RPD 3267</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada lógica RJ45 redonda</t>
+  </si>
+  <si>
+    <t>COMP 1791</t>
+  </si>
+  <si>
+    <t>TOMADA RJ45, 1 MÓDULO,  INSTALADA NO PISO - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA:ORSE  13604 - 11/2024)</t>
+  </si>
+  <si>
+    <t>Cabeamento de sonorização - Cabo para Caixa Acústica- 12 AWG - 2 x 2,5mm - 1</t>
+  </si>
+  <si>
+    <t>CABO PARA SOM PP 2X2,5MM (COMPOSIÇÃO REFERÊNCIA COD 070561 AGETOP CIVIL 05/2023)</t>
+  </si>
+  <si>
+    <t>COMP 1533</t>
+  </si>
+  <si>
+    <t>COMP 1532</t>
+  </si>
+  <si>
+    <t>CABO SPEAKON PROFISSIONAL PP 2X2,5MM (COMPOSIÇÃO REFERÊNCIA COD 070561 AGETOP CIVIL 05/2023)</t>
+  </si>
+  <si>
+    <t>Itens Rack - Cabo de áudio - áudio balanceado de 2 condutores + malha - fio de microfone/linha</t>
+  </si>
+  <si>
+    <t>COMP 929</t>
+  </si>
+  <si>
+    <t>CABO BALANCEADO 2X0,3MM PARA MICROFONE (REFERÊNCIA: ORSE 11752 11/2024)</t>
+  </si>
+  <si>
+    <t>Cabeamento de sonorização - Cabo Speakon Profissional PP - 12 AWG - 2 x 2,5mm - 1</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - PLUG SANTO ANGELO CANNON XLR FEMEA</t>
+  </si>
+  <si>
+    <t>COMP 1526</t>
+  </si>
+  <si>
+    <t>PLUG SANTO ANGELO CANNON XLR FEMEA ( COMPOSIÇÃO REFERÊNCIA: SBC 068094 08/2025)</t>
+  </si>
+  <si>
+    <t>COMP 1527</t>
+  </si>
+  <si>
+    <t>PLUG SANTO ANGELO CANNON XLR MACHO ( COMPOSIÇÃO REFERÊNCIA: SBC 068094 08/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Plugue - PLUG SANTO ANGELO CANNON XLR MACHO</t>
+  </si>
+  <si>
+    <t>Dispositivo TV/Som - Caixas de Som - Caixa de som para parede 40W</t>
+  </si>
+  <si>
+    <t>COMP 1534</t>
+  </si>
+  <si>
+    <t>CAIXA DE SOM ACÚSTICA AMBIENTE CSR 75M 40W RMS 8 OHMS PAR COR PRETO C/TRANSFORMADOR PARA LINHA DE 70 VOLTS.(COMPOSIÇÃO DE REFERÊNCIA: SBC 059438 - 06/2023)</t>
+  </si>
+  <si>
+    <t>COMP 1792</t>
+  </si>
+  <si>
+    <t>AMPLIFICADOR DE ÁUDIO PROFISSIONAL - 400W (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Amplificador de áudio profissional - 400W</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Mesa de Som Digital - 24 canais</t>
+  </si>
+  <si>
+    <t>COMP 1528</t>
+  </si>
+  <si>
+    <t>MESA DE SOM DIGITAL 24 CANAIS (COMPOSIÇÃO REFERÊNCIA ORSE CÓD. 12397 02/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Patch panel XLR - 24 posições</t>
+  </si>
+  <si>
+    <t>COMP 1990</t>
+  </si>
+  <si>
+    <t>Processador de áudio profissional - DBX PA2 127V 3in/3out</t>
+  </si>
+  <si>
+    <t>COMP 1793</t>
+  </si>
+  <si>
+    <t>PROCESSADOR DE ÁUDIO PROFISSIONAL - DBX PA2 127V 3 IN/3 OUT (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
   </si>
 </sst>
 </file>
@@ -6591,7 +6723,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1094"/>
+  <dimension ref="A1:B1111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15350,6 +15482,142 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1095" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1095" s="3" t="s">
+        <v>2051</v>
+      </c>
+      <c r="B1095" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1096" s="3" t="s">
+        <v>2052</v>
+      </c>
+      <c r="B1096" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1097" s="3" t="s">
+        <v>2054</v>
+      </c>
+      <c r="B1097" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1098" s="3" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1098" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1099" s="3" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1099" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1100" s="3" t="s">
+        <v>2062</v>
+      </c>
+      <c r="B1100" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1101" s="3" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1101" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1102" s="3" t="s">
+        <v>2066</v>
+      </c>
+      <c r="B1102" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1103" s="3" t="s">
+        <v>2074</v>
+      </c>
+      <c r="B1103" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1104" s="3" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1104" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1105" s="3" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B1105" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1106" s="3" t="s">
+        <v>2080</v>
+      </c>
+      <c r="B1106" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1107" s="3" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B1107" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1108" s="3" t="s">
+        <v>2086</v>
+      </c>
+      <c r="B1108" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1109" s="3" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1109" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1110" s="3" t="s">
+        <v>2090</v>
+      </c>
+      <c r="B1110" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1111" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1111" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15357,7 +15625,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1094"/>
+  <dimension ref="A1:D1111"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -30682,6 +30950,244 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1095" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1095" s="5">
+        <v>93663</v>
+      </c>
+      <c r="B1095" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1095" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1095" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1096" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1096" s="5">
+        <v>93664</v>
+      </c>
+      <c r="B1096" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1096" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1096" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1097" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1097" s="5" t="s">
+        <v>2053</v>
+      </c>
+      <c r="B1097" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1097" s="3" t="s">
+        <v>2055</v>
+      </c>
+      <c r="D1097" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1098" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1098" s="5" t="s">
+        <v>2057</v>
+      </c>
+      <c r="B1098" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1098" s="3" t="s">
+        <v>2058</v>
+      </c>
+      <c r="D1098" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1099" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1099" s="5" t="s">
+        <v>2060</v>
+      </c>
+      <c r="B1099" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1099" s="3" t="s">
+        <v>2061</v>
+      </c>
+      <c r="D1099" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1100" s="5" t="s">
+        <v>1715</v>
+      </c>
+      <c r="B1100" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1100" s="3" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D1100" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1101" s="5" t="s">
+        <v>2064</v>
+      </c>
+      <c r="B1101" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1101" s="3" t="s">
+        <v>2065</v>
+      </c>
+      <c r="D1101" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1102" s="5" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1102" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1102" s="3" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D1102" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1103" s="5" t="s">
+        <v>2069</v>
+      </c>
+      <c r="B1103" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1103" s="3" t="s">
+        <v>2070</v>
+      </c>
+      <c r="D1103" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1104" s="5" t="s">
+        <v>2072</v>
+      </c>
+      <c r="B1104" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1104" s="3" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D1104" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1105" s="5" t="s">
+        <v>2076</v>
+      </c>
+      <c r="B1105" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1105" s="3" t="s">
+        <v>2077</v>
+      </c>
+      <c r="D1105" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1106" s="5" t="s">
+        <v>2078</v>
+      </c>
+      <c r="B1106" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1106" s="3" t="s">
+        <v>2079</v>
+      </c>
+      <c r="D1106" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1107" s="5" t="s">
+        <v>2082</v>
+      </c>
+      <c r="B1107" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1107" s="3" t="s">
+        <v>2083</v>
+      </c>
+      <c r="D1107" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1108" s="5" t="s">
+        <v>2084</v>
+      </c>
+      <c r="B1108" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1108" s="3" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D1108" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1109" s="5" t="s">
+        <v>2088</v>
+      </c>
+      <c r="B1109" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1109" s="3" t="s">
+        <v>2089</v>
+      </c>
+      <c r="D1109" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1110" s="5" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1110" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1110" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D1110" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1111" s="5" t="s">
+        <v>2093</v>
+      </c>
+      <c r="B1111" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1111" s="3" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D1111" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17DC3AE8-9E33-4495-9553-977863B0A97E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2AEEF2-9B8F-42B0-8895-FD403BD4F632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5985" uniqueCount="2095">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5991" uniqueCount="2097">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6318,13 +6318,19 @@
     <t>COMP 1990</t>
   </si>
   <si>
-    <t>Processador de áudio profissional - DBX PA2 127V 3in/3out</t>
-  </si>
-  <si>
     <t>COMP 1793</t>
   </si>
   <si>
     <t>PROCESSADOR DE ÁUDIO PROFISSIONAL - DBX PA2 127V 3 IN/3 OUT (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Processador de áudio profissional - DBX PA2 127V 3in/3out</t>
+  </si>
+  <si>
+    <t>Lâmpadas Led - E27 A55 4000K - 20W</t>
+  </si>
+  <si>
+    <t>COMP 866</t>
   </si>
 </sst>
 </file>
@@ -6723,7 +6729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1111"/>
+  <dimension ref="A1:B1112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15612,9 +15618,17 @@
     </row>
     <row r="1111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1111" s="3" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="B1111" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1112" s="3" t="s">
+        <v>2095</v>
+      </c>
+      <c r="B1112" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -15625,7 +15639,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1111"/>
+  <dimension ref="A1:D1112"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -31176,15 +31190,29 @@
     </row>
     <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1111" s="5" t="s">
+        <v>2092</v>
+      </c>
+      <c r="B1111" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1111" s="3" t="s">
         <v>2093</v>
       </c>
-      <c r="B1111" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1111" s="3" t="s">
-        <v>2094</v>
-      </c>
       <c r="D1111" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1112" s="5" t="s">
+        <v>2096</v>
+      </c>
+      <c r="B1112" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1112" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D1112" s="5" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D2AEEF2-9B8F-42B0-8895-FD403BD4F632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD172A1-067A-4178-9DF4-EFEAD68FAD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5991" uniqueCount="2097">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="2114">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6331,6 +6331,57 @@
   </si>
   <si>
     <t>COMP 866</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 1.5 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - ref. Prysmian Voltalene Ecolene - 1.5 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Cap. 70 disj. unip. - In barr. 225 A</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, - DIN - Cap. 24 disj. unip. - In barr. 150 A</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Unipolar Termomagnético - norma DIN - Curva C - 32 A - 3 kA</t>
+  </si>
+  <si>
+    <t>DISJUNTOR MONOPOLAR TIPO DIN, CORRENTE NOMINAL DE 32A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>Quadro distrib. plástico - sobrepor - Barr. bif., - DIN - Cap. 12 disj. unip. - In Pente 63A</t>
+  </si>
+  <si>
+    <t>Dispositivo de Cabeamento - embutir - Placa 2x4" - Bege - 1 módulo - RJ45</t>
+  </si>
+  <si>
+    <t>COMP 1614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOMADA RJ45 CAT 6E (COMPLETA) - FORNECIMENTO E INSTALAÇÃO. AF_08/2025 (COMPOSIÇÃO REFERÊNCIA SINAPI - 106077 08/2025) </t>
+  </si>
+  <si>
+    <t>Condutores de proteção - SPDA - Vergalhão CA 50 - 3/8'' x 3,00m</t>
+  </si>
+  <si>
+    <t>ARMAÇÃO PARA EXECUÇÃO DE RADIER, PISO DE CONCRETO OU LAJE SOBRE SOLO, COM USO DE VERGALHÃO AÇO CA-50 DE 10,0 MM - MONTAGEM. AF_07/2026</t>
+  </si>
+  <si>
+    <t>-Composições - m³ - Escavação</t>
+  </si>
+  <si>
+    <t>-Composições - m³ - Reaterro</t>
+  </si>
+  <si>
+    <t>m³</t>
+  </si>
+  <si>
+    <t>ESCAVAÇÃO MANUAL DE VALA. AF_09/2024</t>
+  </si>
+  <si>
+    <t>REATERRO MANUAL DE VALAS, COM PLACA VIBRATÓRIA. AF_08/2023</t>
   </si>
 </sst>
 </file>
@@ -6729,7 +6780,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1112"/>
+  <dimension ref="A1:B1122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15632,6 +15683,86 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1113" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1113" s="3" t="s">
+        <v>2097</v>
+      </c>
+      <c r="B1113" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1114" s="3" t="s">
+        <v>2098</v>
+      </c>
+      <c r="B1114" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1115" s="3" t="s">
+        <v>2099</v>
+      </c>
+      <c r="B1115" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1116" s="3" t="s">
+        <v>2100</v>
+      </c>
+      <c r="B1116" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1117" s="3" t="s">
+        <v>2101</v>
+      </c>
+      <c r="B1117" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1118" s="3" t="s">
+        <v>2103</v>
+      </c>
+      <c r="B1118" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1119" s="3" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1119" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1120" s="3" t="s">
+        <v>2107</v>
+      </c>
+      <c r="B1120" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1121" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1121" s="6" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1122" s="3" t="s">
+        <v>2110</v>
+      </c>
+      <c r="B1122" s="6" t="s">
+        <v>2111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15639,7 +15770,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1112"/>
+  <dimension ref="A1:D1122"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -31216,6 +31347,146 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1113" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1113" s="5">
+        <v>91925</v>
+      </c>
+      <c r="B1113" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1113" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1113" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1114" s="5">
+        <v>91925</v>
+      </c>
+      <c r="B1114" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1114" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1114" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1115" s="5" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1115" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1115" s="3" t="s">
+        <v>776</v>
+      </c>
+      <c r="D1115" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1116" s="5" t="s">
+        <v>858</v>
+      </c>
+      <c r="B1116" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1116" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="D1116" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1117" s="5">
+        <v>93657</v>
+      </c>
+      <c r="B1117" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1117" s="3" t="s">
+        <v>2102</v>
+      </c>
+      <c r="D1117" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1118" s="5" t="s">
+        <v>795</v>
+      </c>
+      <c r="B1118" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1118" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="D1118" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1119" s="5" t="s">
+        <v>2105</v>
+      </c>
+      <c r="B1119" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1119" s="3" t="s">
+        <v>2106</v>
+      </c>
+      <c r="D1119" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1120" s="5">
+        <v>107281</v>
+      </c>
+      <c r="B1120" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1120" s="3" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D1120" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1121" s="5">
+        <v>93358</v>
+      </c>
+      <c r="B1121" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1121" s="3" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D1121" s="6" t="s">
+        <v>2111</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1122" s="5">
+        <v>104737</v>
+      </c>
+      <c r="B1122" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1122" s="3" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D1122" s="6" t="s">
+        <v>2111</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDD172A1-067A-4178-9DF4-EFEAD68FAD66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE06747E-2492-4DEF-B3D9-716F27D60CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6045" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6056" uniqueCount="2116">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6382,6 +6382,12 @@
   </si>
   <si>
     <t>REATERRO MANUAL DE VALAS, COM PLACA VIBRATÓRIA. AF_08/2023</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXA DE PASSAGEM - EMBUTIR NO PISO - Alvenaria - 40x40x70 cm</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1900x800x800mm</t>
   </si>
 </sst>
 </file>
@@ -6780,7 +6786,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1122"/>
+  <dimension ref="A1:B1124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15763,6 +15769,22 @@
         <v>2111</v>
       </c>
     </row>
+    <row r="1123" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1123" s="3" t="s">
+        <v>2114</v>
+      </c>
+      <c r="B1123" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1124" s="3" t="s">
+        <v>2115</v>
+      </c>
+      <c r="B1124" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15770,7 +15792,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1122"/>
+  <dimension ref="A1:D1124"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -31487,6 +31509,34 @@
         <v>2111</v>
       </c>
     </row>
+    <row r="1123" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1123" s="1">
+        <v>97887</v>
+      </c>
+      <c r="B1123" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1123" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="D1123" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1124" s="5" t="s">
+        <v>1944</v>
+      </c>
+      <c r="B1124" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1124" s="3" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D1124" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE06747E-2492-4DEF-B3D9-716F27D60CBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DF3F29-546D-4F72-9217-6F9DA23595DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6056" uniqueCount="2116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6255" uniqueCount="2184">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6388,6 +6388,210 @@
   </si>
   <si>
     <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1900x800x800mm</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 120 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - Cabo HDMI - 1</t>
+  </si>
+  <si>
+    <t>CABO HDMI x HDMI VERSAO 1.4 BLINDADO (COMPOSIÇÃO PRÓPRIA: SBC 079611 10/2026)</t>
+  </si>
+  <si>
+    <t>COMP 1868</t>
+  </si>
+  <si>
+    <t>Canaleta PVC - Canaleta PVC lisa - 15x15mm</t>
+  </si>
+  <si>
+    <t>COMP 1869</t>
+  </si>
+  <si>
+    <t>CANALETA PVC FECHADA HD-6F 15X15 (COMPOSIÇÃO REFERÊNCIA: SBC 059531 10/2026)</t>
+  </si>
+  <si>
+    <t>Câmeras - Câmera Analógica Dome - PTZ PRO Full Color</t>
+  </si>
+  <si>
+    <t>COMP 1870</t>
+  </si>
+  <si>
+    <t>CAMERA PTZ - MOVIMENTO HORIZONTAL,VERTICAL E ZOOM (COMPOSIÇÃO REFERÊNCIA: SBC 067207 10/2026)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Switch - 10/100 - BaseTX - Conference - Central completa</t>
+  </si>
+  <si>
+    <t>COMP 1871</t>
+  </si>
+  <si>
+    <t>MESA CONTROLADORA PARA CAMERAS PTZ - CONTROL KEYBOARD (COMPOSIÇÃO REFERÊNCIA ORSE CÓD. 12397 02/2025)</t>
+  </si>
+  <si>
+    <t>COMP 1872</t>
+  </si>
+  <si>
+    <t>PLUG KEYSTONE HDMI (COMPOSIÇÃO REFERÊNCIA: SBC 068094 08/2025)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Conector - HDMI</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 240 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 240 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 240 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 240 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 35 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 35 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 35 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 35 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária embutir p/ LED tubular - 4x9W</t>
+  </si>
+  <si>
+    <t>COMP 1873</t>
+  </si>
+  <si>
+    <t>LUMINARIA EMBUTIR ALETADA ALUMINIO BRILHANTE 4X9W LED SALA LIMPA (COMPOSIÇÃO REFERÊNCIA: SBC 060588 10/2026)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Dispositivo de proteção contra surto - 175 V - 40 KA</t>
+  </si>
+  <si>
+    <t>COMP 601</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE PROTEÇÃO CONTRA SURTO DE TENSÃO DPS 40KA -175V - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA:SINAPI 106028 - 09/2026)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Interruptor bipolar DR - fase/neutro - In 30mA - DIN - 25 A</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DR, CORRENTE NOMINAL DE 25A - FORNECIMENTO E INSTALAÇÃO. AF_07/2025</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -600x500x200mm</t>
+  </si>
+  <si>
+    <t>COMP 1060</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 100 A - 40 kA</t>
+  </si>
+  <si>
+    <t>COMP 128</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 80 A - 40 KA</t>
+  </si>
+  <si>
+    <t>COMP 142</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 50 A - 40 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 1250 A - 65 kA</t>
+  </si>
+  <si>
+    <t>COMP 770</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 1600 A - 65 kA</t>
+  </si>
+  <si>
+    <t>COMP 386</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 400 A - 65 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tetrapolar termomagnético caixa moldada - 380/415 V - 1600 A - 50 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tetrapolar termomagnético caixa moldada - 380/415 V - 500 A - 50 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Transferência - Chave de Transferência Manual - 4 Polos - 630A</t>
+  </si>
+  <si>
+    <t>COMP 1874</t>
+  </si>
+  <si>
+    <t>CHAVE DE TRANSFERÊNCIA MANUAL 630A 4 POLOS (COMPOSIÇÃO DE REFERÊNCIA: CPOS/CDHU 37.14.640 - 09/2026)</t>
+  </si>
+  <si>
+    <t>- Quadro distrib. - Trilho - Trilho DIN</t>
+  </si>
+  <si>
+    <t>COMP 1875</t>
+  </si>
+  <si>
+    <t>COMP 1876</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TETRAPOLAR CAIXA MOLDADA 1600A, 60kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>COMP 1877</t>
+  </si>
+  <si>
+    <t>DISJUNTOR TETRAPOLAR CAIXA MOLDADA 500A, 35kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6 - CMX - AZ - 4</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6A AZ - 4</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6A CZ - 4</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6A VRD - 4</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6A VRM - 4</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 44U unc 19" x 670mm RPD 4467</t>
+  </si>
+  <si>
+    <t>RACK FECHADO 44U PARA SERVIDOR - FORNECIMENTO E INSTALAÇÃO. AF_08/2025</t>
+  </si>
+  <si>
+    <t>Acessórios Perfilados perfurados - Curva vertical externa 90° - 38x38mm</t>
+  </si>
+  <si>
+    <t>COMP 698</t>
+  </si>
+  <si>
+    <t>CURVA VERTICAL EXTERNA 90° PARA PERFILADOS PERFURADOS 38x38mm (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 97274 - 09/2022)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Cabeamento - embutir - S/ placa - Roteador Empresarial Wi-Fi 4 de Longo Alcance AP 360 Branco Intelbras</t>
+  </si>
+  <si>
+    <t>ACCESS POINT UBIQUITI UNIFI WIFI - U7-PRO-MAX (COMPOSIÇÃO DE REFERÊNCIA: CPOS/CDHU: 61.15.140 09/2024)</t>
+  </si>
+  <si>
+    <t>COMP 1878</t>
   </si>
 </sst>
 </file>
@@ -6429,7 +6633,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6452,6 +6656,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6786,7 +6991,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1124"/>
+  <dimension ref="A1:B1160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15785,6 +15990,294 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1125" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1125" s="3" t="s">
+        <v>2117</v>
+      </c>
+      <c r="B1125" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1126" s="3" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1126" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1127" s="3" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1127" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1128" s="3" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1128" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1129" s="3" t="s">
+        <v>2131</v>
+      </c>
+      <c r="B1129" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1130" s="3" t="s">
+        <v>2116</v>
+      </c>
+      <c r="B1130" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1131" s="3" t="s">
+        <v>2132</v>
+      </c>
+      <c r="B1131" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1132" s="3" t="s">
+        <v>2133</v>
+      </c>
+      <c r="B1132" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1133" s="3" t="s">
+        <v>2134</v>
+      </c>
+      <c r="B1133" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1134" s="3" t="s">
+        <v>2135</v>
+      </c>
+      <c r="B1134" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1135" s="3" t="s">
+        <v>2136</v>
+      </c>
+      <c r="B1135" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1136" s="3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="B1136" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1137" s="3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="B1137" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1138" s="3" t="s">
+        <v>2139</v>
+      </c>
+      <c r="B1138" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1139" s="3" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1139" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1140" s="3" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1140" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1141" s="3" t="s">
+        <v>2146</v>
+      </c>
+      <c r="B1141" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1142" s="3" t="s">
+        <v>2148</v>
+      </c>
+      <c r="B1142" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1143" s="3" t="s">
+        <v>2150</v>
+      </c>
+      <c r="B1143" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1144" s="3" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B1144" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1145" s="3" t="s">
+        <v>2154</v>
+      </c>
+      <c r="B1145" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1146" s="3" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B1146" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1147" s="3" t="s">
+        <v>2157</v>
+      </c>
+      <c r="B1147" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1148" s="3" t="s">
+        <v>2159</v>
+      </c>
+      <c r="B1148" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1149" s="3" t="s">
+        <v>2160</v>
+      </c>
+      <c r="B1149" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1150" s="3" t="s">
+        <v>2161</v>
+      </c>
+      <c r="B1150" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1151" s="3" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1151" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1152" s="3" t="s">
+        <v>2165</v>
+      </c>
+      <c r="B1152" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1153" s="3" t="s">
+        <v>2171</v>
+      </c>
+      <c r="B1153" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1154" s="3" t="s">
+        <v>2172</v>
+      </c>
+      <c r="B1154" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1155" s="3" t="s">
+        <v>2173</v>
+      </c>
+      <c r="B1155" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1156" s="3" t="s">
+        <v>2174</v>
+      </c>
+      <c r="B1156" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1157" s="3" t="s">
+        <v>2175</v>
+      </c>
+      <c r="B1157" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1158" s="8" t="s">
+        <v>2176</v>
+      </c>
+      <c r="B1158" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1159" s="3" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1159" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1160" s="3" t="s">
+        <v>2181</v>
+      </c>
+      <c r="B1160" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -15792,7 +16285,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1124"/>
+  <dimension ref="A1:D1160"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -31537,6 +32030,510 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1125" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1125" s="5" t="s">
+        <v>2119</v>
+      </c>
+      <c r="B1125" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1125" s="3" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D1125" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1126" s="5" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B1126" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1126" s="3" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D1126" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1127" s="5" t="s">
+        <v>2124</v>
+      </c>
+      <c r="B1127" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1127" s="3" t="s">
+        <v>2125</v>
+      </c>
+      <c r="D1127" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1128" s="5" t="s">
+        <v>2127</v>
+      </c>
+      <c r="B1128" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1128" s="3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="D1128" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1129" s="5" t="s">
+        <v>2129</v>
+      </c>
+      <c r="B1129" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1129" s="3" t="s">
+        <v>2130</v>
+      </c>
+      <c r="D1129" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1130" s="5">
+        <v>92994</v>
+      </c>
+      <c r="B1130" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1130" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="D1130" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1131" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1131" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1131" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1131" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1132" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1132" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1132" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1132" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1133" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1133" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1133" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1133" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1134" s="5">
+        <v>93000</v>
+      </c>
+      <c r="B1134" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1134" s="3" t="s">
+        <v>804</v>
+      </c>
+      <c r="D1134" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1135" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B1135" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1135" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1135" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1136" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B1136" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1136" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1136" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1137" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B1137" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1137" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1137" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1138" s="5">
+        <v>92986</v>
+      </c>
+      <c r="B1138" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1138" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="D1138" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1139" s="5" t="s">
+        <v>2141</v>
+      </c>
+      <c r="B1139" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1139" s="3" t="s">
+        <v>2142</v>
+      </c>
+      <c r="D1139" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1140" s="5" t="s">
+        <v>2144</v>
+      </c>
+      <c r="B1140" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1140" s="3" t="s">
+        <v>2145</v>
+      </c>
+      <c r="D1140" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1141" s="5">
+        <v>93674</v>
+      </c>
+      <c r="B1141" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1141" s="3" t="s">
+        <v>2147</v>
+      </c>
+      <c r="D1141" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1142" s="5" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B1142" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1142" s="3" t="s">
+        <v>1599</v>
+      </c>
+      <c r="D1142" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1143" s="5" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B1143" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1143" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="D1143" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1144" s="5" t="s">
+        <v>2153</v>
+      </c>
+      <c r="B1144" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1144" s="3" t="s">
+        <v>1802</v>
+      </c>
+      <c r="D1144" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1145" s="5">
+        <v>93673</v>
+      </c>
+      <c r="B1145" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1145" s="3" t="s">
+        <v>1595</v>
+      </c>
+      <c r="D1145" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1146" s="5" t="s">
+        <v>2156</v>
+      </c>
+      <c r="B1146" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1146" s="3" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D1146" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1147" s="5" t="s">
+        <v>2158</v>
+      </c>
+      <c r="B1147" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1147" s="3" t="s">
+        <v>787</v>
+      </c>
+      <c r="D1147" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1148" s="5" t="s">
+        <v>1705</v>
+      </c>
+      <c r="B1148" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1148" s="3" t="s">
+        <v>1706</v>
+      </c>
+      <c r="D1148" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1149" s="5" t="s">
+        <v>2167</v>
+      </c>
+      <c r="B1149" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1149" s="3" t="s">
+        <v>2168</v>
+      </c>
+      <c r="D1149" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1150" s="5" t="s">
+        <v>2169</v>
+      </c>
+      <c r="B1150" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1150" s="3" t="s">
+        <v>2170</v>
+      </c>
+      <c r="D1150" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1151" s="5" t="s">
+        <v>2163</v>
+      </c>
+      <c r="B1151" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1151" s="3" t="s">
+        <v>2164</v>
+      </c>
+      <c r="D1151" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1152" s="5" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1152" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1152" s="3" t="s">
+        <v>1666</v>
+      </c>
+      <c r="D1152" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1153" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1153" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1153" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1153" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1154" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1154" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1154" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1154" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1155" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1155" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1155" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1155" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1156" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1156" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1156" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1156" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1157" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1157" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1157" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1157" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1158" s="5">
+        <v>98305</v>
+      </c>
+      <c r="B1158" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1158" s="3" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D1158" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1159" s="5" t="s">
+        <v>2179</v>
+      </c>
+      <c r="B1159" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1159" s="3" t="s">
+        <v>2180</v>
+      </c>
+      <c r="D1159" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1160" s="5" t="s">
+        <v>2183</v>
+      </c>
+      <c r="B1160" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1160" s="3" t="s">
+        <v>2182</v>
+      </c>
+      <c r="D1160" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5DF3F29-546D-4F72-9217-6F9DA23595DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8299D5D-3AFD-4CDD-813E-C36D1E1D4168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6255" uniqueCount="2184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6261" uniqueCount="2186">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6592,6 +6592,12 @@
   </si>
   <si>
     <t>COMP 1878</t>
+  </si>
+  <si>
+    <t>Dispositivo de Comando - Medidor de energia eletrônico - Trifásico</t>
+  </si>
+  <si>
+    <t>COMP 862</t>
   </si>
 </sst>
 </file>
@@ -6633,7 +6639,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -6656,7 +6662,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6991,7 +6996,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1160"/>
+  <dimension ref="A1:B1161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -16255,7 +16260,7 @@
       </c>
     </row>
     <row r="1158" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A1158" s="8" t="s">
+      <c r="A1158" t="s">
         <v>2176</v>
       </c>
       <c r="B1158" s="5" t="s">
@@ -16275,6 +16280,14 @@
         <v>2181</v>
       </c>
       <c r="B1160" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1161" s="3" t="s">
+        <v>2184</v>
+      </c>
+      <c r="B1161" s="5" t="s">
         <v>7</v>
       </c>
     </row>
@@ -16285,7 +16298,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1160"/>
+  <dimension ref="A1:D1161"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -32366,7 +32379,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1149" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1149" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1149" s="5" t="s">
         <v>2167</v>
       </c>
@@ -32531,6 +32544,20 @@
         <v>2182</v>
       </c>
       <c r="D1160" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1161" s="5" t="s">
+        <v>2185</v>
+      </c>
+      <c r="B1161" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1161" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="D1161" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8299D5D-3AFD-4CDD-813E-C36D1E1D4168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B44B3D-DE74-4795-926D-FC0E3EB2B70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6261" uniqueCount="2186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6302" uniqueCount="2196">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6598,6 +6598,36 @@
   </si>
   <si>
     <t>COMP 862</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva C - 16 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva C - 25 A - 25 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 16 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 25 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor bipolar termomagnético - 220 V/127 V - DIN - Curva C - 25 A - 25 kA</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Cruzeta 90° - 400x100mm chapa 16</t>
+  </si>
+  <si>
+    <t>COMP 1101</t>
+  </si>
+  <si>
+    <t>CRUZETA HORIZONTAL PARA ELETROCALHA 400X100MM (COMPOSIÇÃO DE REFERÊNCIA: 063746 SBC 06/2024)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 20 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 30 A - 5 kA</t>
   </si>
 </sst>
 </file>
@@ -6996,7 +7026,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1161"/>
+  <dimension ref="A1:B1169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -16291,6 +16321,70 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1162" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1162" s="3" t="s">
+        <v>2186</v>
+      </c>
+      <c r="B1162" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1163" s="3" t="s">
+        <v>2187</v>
+      </c>
+      <c r="B1163" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1164" s="3" t="s">
+        <v>2188</v>
+      </c>
+      <c r="B1164" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1165" s="3" t="s">
+        <v>2189</v>
+      </c>
+      <c r="B1165" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1166" s="3" t="s">
+        <v>2190</v>
+      </c>
+      <c r="B1166" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1167" s="3" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1167" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1168" s="3" t="s">
+        <v>2194</v>
+      </c>
+      <c r="B1168" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1169" s="3" t="s">
+        <v>2195</v>
+      </c>
+      <c r="B1169" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16298,11 +16392,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1161"/>
+  <dimension ref="A1:D1169"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="121.21875" style="3" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.88671875" style="2"/>
   </cols>
@@ -32561,6 +32655,118 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1162" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1162" s="5">
+        <v>93654</v>
+      </c>
+      <c r="B1162" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1162" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1162" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1163" s="5">
+        <v>93656</v>
+      </c>
+      <c r="B1163" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1163" s="3" t="s">
+        <v>772</v>
+      </c>
+      <c r="D1163" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1164" s="5">
+        <v>93668</v>
+      </c>
+      <c r="B1164" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1164" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="D1164" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1165" s="5">
+        <v>93670</v>
+      </c>
+      <c r="B1165" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1165" s="3" t="s">
+        <v>1693</v>
+      </c>
+      <c r="D1165" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1166" s="5">
+        <v>93663</v>
+      </c>
+      <c r="B1166" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1166" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1166" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1167" s="5" t="s">
+        <v>2192</v>
+      </c>
+      <c r="B1167" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1167" s="3" t="s">
+        <v>2193</v>
+      </c>
+      <c r="D1167" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1168" s="5">
+        <v>93669</v>
+      </c>
+      <c r="B1168" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1168" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D1168" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1169" s="5">
+        <v>93671</v>
+      </c>
+      <c r="B1169" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1169" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D1169" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B44B3D-DE74-4795-926D-FC0E3EB2B70C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD891F2-BCE3-45CD-B67C-8F46C1C55B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6302" uniqueCount="2196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6307" uniqueCount="2197">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6628,6 +6628,9 @@
   </si>
   <si>
     <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético - 220 V/127 V - DIN - Curva C - 30 A - 5 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva B - 16 A - 25 kA</t>
   </si>
 </sst>
 </file>
@@ -7026,7 +7029,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1169"/>
+  <dimension ref="A1:B1170"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -16385,6 +16388,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1170" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1170" s="3" t="s">
+        <v>2196</v>
+      </c>
+      <c r="B1170" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16392,7 +16403,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1169"/>
+  <dimension ref="A1:D1170"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -32767,6 +32778,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1170" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1170" s="5">
+        <v>93654</v>
+      </c>
+      <c r="B1170" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1170" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D1170" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBD891F2-BCE3-45CD-B67C-8F46C1C55B0E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852D7BB6-3794-420B-816B-AD56A849F6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6307" uniqueCount="2197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6410" uniqueCount="2232">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6631,6 +6631,111 @@
   </si>
   <si>
     <t>Dispositivo de Proteção - Disjuntor unipolar termomagnético - 220 V/127 V - DIN - Curva B - 16 A - 25 kA</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 150 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 150 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 150 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 150 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 95 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cobre - Barra - m - 100x10mm</t>
+  </si>
+  <si>
+    <t>COMP 1950</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 1935A , 100X10 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>COMP 1951</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 320A , 20X5 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>Cobre - Barra - m - 30x10mm</t>
+  </si>
+  <si>
+    <t>Cobre - Barra - m - 20x5mm</t>
+  </si>
+  <si>
+    <t>Cobre - Barra - m - 40x10mm</t>
+  </si>
+  <si>
+    <t>COMP 1952</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 630A , 30X10 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>COMP 1953</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 1350A , 40X10 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>COMP 1954</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -2000x800x800mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR - 2000x800x800mm</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 320 A - 65 kA</t>
+  </si>
+  <si>
+    <t>COMP 1363</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 320A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 25 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 50 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 50 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 50 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 50 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 70 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1600x600x600mm</t>
+  </si>
+  <si>
+    <t>COMP 841</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -1600x600x600mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético caixa moldada - 380/415 V - 90 A - 18 kA</t>
+  </si>
+  <si>
+    <t>COMP 1955</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA MOLDADA 90A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
   </si>
 </sst>
 </file>
@@ -7029,7 +7134,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1170"/>
+  <dimension ref="A1:B1189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -16396,6 +16501,158 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1171" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1171" s="3" t="s">
+        <v>2197</v>
+      </c>
+      <c r="B1171" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1172" s="3" t="s">
+        <v>2198</v>
+      </c>
+      <c r="B1172" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1173" s="3" t="s">
+        <v>2199</v>
+      </c>
+      <c r="B1173" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1174" s="3" t="s">
+        <v>2200</v>
+      </c>
+      <c r="B1174" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1175" s="3" t="s">
+        <v>2201</v>
+      </c>
+      <c r="B1175" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1176" s="3" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1176" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1177" s="3" t="s">
+        <v>2208</v>
+      </c>
+      <c r="B1177" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1178" s="3" t="s">
+        <v>2207</v>
+      </c>
+      <c r="B1178" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1179" s="3" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1179" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1180" s="3" t="s">
+        <v>2216</v>
+      </c>
+      <c r="B1180" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1181" s="3" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1181" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1182" s="3" t="s">
+        <v>2220</v>
+      </c>
+      <c r="B1182" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1183" s="3" t="s">
+        <v>2221</v>
+      </c>
+      <c r="B1183" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1184" s="3" t="s">
+        <v>2222</v>
+      </c>
+      <c r="B1184" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1185" s="3" t="s">
+        <v>2223</v>
+      </c>
+      <c r="B1185" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1186" s="3" t="s">
+        <v>2224</v>
+      </c>
+      <c r="B1186" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1187" s="3" t="s">
+        <v>2225</v>
+      </c>
+      <c r="B1187" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1188" s="3" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B1188" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1189" s="3" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1189" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16403,7 +16660,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1170"/>
+  <dimension ref="A1:D1189"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -32792,6 +33049,272 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1171" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1171" s="5">
+        <v>92996</v>
+      </c>
+      <c r="B1171" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1171" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D1171" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1172" s="5">
+        <v>92996</v>
+      </c>
+      <c r="B1172" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1172" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D1172" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1173" s="5">
+        <v>92996</v>
+      </c>
+      <c r="B1173" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1173" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D1173" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1174" s="5">
+        <v>92996</v>
+      </c>
+      <c r="B1174" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1174" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D1174" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1175" s="5">
+        <v>92992</v>
+      </c>
+      <c r="B1175" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1175" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="D1175" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1176" s="5" t="s">
+        <v>2203</v>
+      </c>
+      <c r="B1176" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1176" s="3" t="s">
+        <v>2204</v>
+      </c>
+      <c r="D1176" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1177" s="5" t="s">
+        <v>2205</v>
+      </c>
+      <c r="B1177" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1177" s="3" t="s">
+        <v>2206</v>
+      </c>
+      <c r="D1177" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1178" s="5" t="s">
+        <v>2210</v>
+      </c>
+      <c r="B1178" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1178" s="3" t="s">
+        <v>2211</v>
+      </c>
+      <c r="D1178" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1179" s="5" t="s">
+        <v>2212</v>
+      </c>
+      <c r="B1179" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1179" s="3" t="s">
+        <v>2213</v>
+      </c>
+      <c r="D1179" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1180" s="5" t="s">
+        <v>2214</v>
+      </c>
+      <c r="B1180" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1180" s="3" t="s">
+        <v>2215</v>
+      </c>
+      <c r="D1180" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1181" s="5" t="s">
+        <v>2218</v>
+      </c>
+      <c r="B1181" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1181" s="3" t="s">
+        <v>2219</v>
+      </c>
+      <c r="D1181" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1182" s="5">
+        <v>92984</v>
+      </c>
+      <c r="B1182" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1182" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1182" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1183" s="5">
+        <v>92988</v>
+      </c>
+      <c r="B1183" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1183" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1183" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1184" s="5">
+        <v>92988</v>
+      </c>
+      <c r="B1184" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1184" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1184" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1185" s="5">
+        <v>92988</v>
+      </c>
+      <c r="B1185" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1185" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1185" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1186" s="5">
+        <v>92988</v>
+      </c>
+      <c r="B1186" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1186" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="D1186" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1187" s="5">
+        <v>92990</v>
+      </c>
+      <c r="B1187" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1187" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="D1187" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1188" s="5" t="s">
+        <v>2227</v>
+      </c>
+      <c r="B1188" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1188" s="3" t="s">
+        <v>2228</v>
+      </c>
+      <c r="D1188" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1189" s="5" t="s">
+        <v>2230</v>
+      </c>
+      <c r="B1189" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1189" s="3" t="s">
+        <v>2231</v>
+      </c>
+      <c r="D1189" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{852D7BB6-3794-420B-816B-AD56A849F6B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF48888-B150-4223-A57D-9B90C235B07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6410" uniqueCount="2232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6525" uniqueCount="2270">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6736,6 +6736,120 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA MOLDADA 90A, 36kA - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 - 02/2023)</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 300 mm² - Azul claro</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 300 mm² - Branco</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 300 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 300 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>CABO DE COBRE FLEXÍVEL ISOLADO, 300 MM², ANTI-CHAMA 0,6/1,0 KV, PARA REDE ENTERRADA DE DISTRIBUIÇÃO DE ENERGIA ELÉTRICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 150 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol. XLPE - 0,6/1kV - 4 mm² - Amarelo</t>
+  </si>
+  <si>
+    <t>Poste - Balizador - Poste Balizador de Jardim em Alumínio P/ T40 Starlumen ST3152</t>
+  </si>
+  <si>
+    <t>COMP 1956</t>
+  </si>
+  <si>
+    <t>POSTE BALIZADOR DE JARDIM ALUMÍNIO P/ T40 STARLUMEN ST3152 CÚPULA CINZA ESTRUTURA PRETO (REFERÊNCIA: SBC 60286 01/2025)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Spot - 10W</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Balizador de 1W de 1 foco</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - S/ placa - Tomada hexagonal - NBR 14136 - 2 - 2P+T 20A - Baixa</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Bipolar Termomagnético - norma DIN - Curva C - 40 A - 3 kA</t>
+  </si>
+  <si>
+    <t>COMP 890</t>
+  </si>
+  <si>
+    <t>BALIZADOR DE EMBUTIR LED 1W COM 1 FACHO (REFERÊNCIA: SBC 60286 01/2025)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Sobrepor - Ledvance Livin 12W</t>
+  </si>
+  <si>
+    <t>COMP 235</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA PLAFON, DE SOBREPOR, COM LÂMPADA LED 12W, SOQUETE E27 (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 103782 - 09/2022)</t>
+  </si>
+  <si>
+    <t>COMP 1957</t>
+  </si>
+  <si>
+    <t>CONJUNTO PARA CONDULETE COM DUAS (2) TOMADAS,  TENSÃO 250V, (20A 250V) E PLACA DE UM (1) POSTO, INCLUSIVE FORNECIMENTO, INSTALAÇÃO, SUPORTE, MÓDULO E PLACA, SEM CONDULETE (COMPOSIÇÃP REFERÊNCIA: SETOP ED-17981 10/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tampa metálica p/ condulete - 2 Tomadas hexagonal - NBR 14136 - 2P+T 20A</t>
+  </si>
+  <si>
+    <t>- SINAPI - METROS - ELETRODUTO RIGIDO, EM ACO ZINCADO OU GALVANIZADO, TIPO PESADO, DN=3/4", APARENTE</t>
+  </si>
+  <si>
+    <t>COMP 1616</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Bipolar Termomagnético - norma DIN - Curva C - 25 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Ref. Moratori - Cap. 48 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>COMP 1579</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Sem barr., - DIN - Ref. Moratori - Cap. 16 disj. unip.</t>
+  </si>
+  <si>
+    <t>COMP 1609</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - embutir - Sem barr. - DIN - Ref. Cemar - Cap. 24 disj. unip.</t>
+  </si>
+  <si>
+    <t>COMP 1958</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE EMBUTIR, SEM BARRAMENTO, PARA 24 DISJUNTORES DIN - FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REF.  101879 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Luminária e acessórios - Luminária Led Embutir - Luminária de embutir redonda 36W</t>
+  </si>
+  <si>
+    <t>COMP 1959</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA DE EMBUTIR REDONDA LED 36W. (REFERÊNCIA: ORSE 13669 11/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios p/ eletrodutos - Caixa de Luz 4"x2" - 4"x 2"</t>
+  </si>
+  <si>
+    <t>COMP 1604</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor paralelo - 3 teclas</t>
   </si>
 </sst>
 </file>
@@ -7134,7 +7248,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1189"/>
+  <dimension ref="A1:B1210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -16653,6 +16767,171 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1190" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1190" s="3" t="s">
+        <v>2232</v>
+      </c>
+      <c r="B1190" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1191" s="3" t="s">
+        <v>2233</v>
+      </c>
+      <c r="B1191" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1192" s="3" t="s">
+        <v>2234</v>
+      </c>
+      <c r="B1192" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1193" s="3" t="s">
+        <v>2235</v>
+      </c>
+      <c r="B1193" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1194" s="3" t="s">
+        <v>2237</v>
+      </c>
+      <c r="B1194" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1195" s="3" t="s">
+        <v>2238</v>
+      </c>
+      <c r="B1195" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1196" s="3" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1196" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1197" s="3" t="s">
+        <v>2242</v>
+      </c>
+      <c r="B1197" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1198" s="3" t="s">
+        <v>2243</v>
+      </c>
+      <c r="B1198" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1199" s="3" t="s">
+        <v>2244</v>
+      </c>
+      <c r="B1199" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1200" s="3" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1200" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1201" s="3" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B1201" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1202" s="3" t="s">
+        <v>2253</v>
+      </c>
+      <c r="B1202" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1203" s="3" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B1203" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1204" s="3" t="s">
+        <v>2256</v>
+      </c>
+      <c r="B1204" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1205" s="3" t="s">
+        <v>2257</v>
+      </c>
+      <c r="B1205" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1206" s="3" t="s">
+        <v>2259</v>
+      </c>
+      <c r="B1206" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1207" s="3" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1207" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1208" s="3" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1208" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1209" s="3" t="s">
+        <v>2267</v>
+      </c>
+      <c r="B1209" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1210" s="3" t="s">
+        <v>2269</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -16660,7 +16939,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1189"/>
+  <dimension ref="A1:D1210"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -33315,6 +33594,300 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1190" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1190" s="5">
+        <v>93002</v>
+      </c>
+      <c r="B1190" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1190" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1190" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1191" s="5">
+        <v>93002</v>
+      </c>
+      <c r="B1191" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1191" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1191" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1192" s="5">
+        <v>93002</v>
+      </c>
+      <c r="B1192" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1192" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1192" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1193" s="5">
+        <v>93002</v>
+      </c>
+      <c r="B1193" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1193" s="3" t="s">
+        <v>2236</v>
+      </c>
+      <c r="D1193" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1194" s="5">
+        <v>92996</v>
+      </c>
+      <c r="B1194" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1194" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="D1194" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1195" s="5">
+        <v>91929</v>
+      </c>
+      <c r="B1195" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1195" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1195" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1196" s="5" t="s">
+        <v>2240</v>
+      </c>
+      <c r="B1196" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1196" s="3" t="s">
+        <v>2241</v>
+      </c>
+      <c r="D1196" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1197" s="5" t="s">
+        <v>1853</v>
+      </c>
+      <c r="B1197" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1197" s="3" t="s">
+        <v>1854</v>
+      </c>
+      <c r="D1197" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1198" s="5" t="s">
+        <v>2246</v>
+      </c>
+      <c r="B1198" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1198" s="3" t="s">
+        <v>2247</v>
+      </c>
+      <c r="D1198" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1199" s="5">
+        <v>92001</v>
+      </c>
+      <c r="B1199" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1199" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D1199" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1200" s="5">
+        <v>93665</v>
+      </c>
+      <c r="B1200" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1200" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="D1200" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1201" s="5" t="s">
+        <v>2249</v>
+      </c>
+      <c r="B1201" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1201" s="3" t="s">
+        <v>2250</v>
+      </c>
+      <c r="D1201" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1202" s="5" t="s">
+        <v>2251</v>
+      </c>
+      <c r="B1202" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1202" s="3" t="s">
+        <v>2252</v>
+      </c>
+      <c r="D1202" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1203" s="5" t="s">
+        <v>2255</v>
+      </c>
+      <c r="B1203" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1203" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1203" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1204" s="5">
+        <v>93663</v>
+      </c>
+      <c r="B1204" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1204" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D1204" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1205" s="5" t="s">
+        <v>2258</v>
+      </c>
+      <c r="B1205" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1205" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="D1205" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1206" s="5" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1206" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1206" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="D1206" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1207" s="5" t="s">
+        <v>2262</v>
+      </c>
+      <c r="B1207" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1207" s="3" t="s">
+        <v>2263</v>
+      </c>
+      <c r="D1207" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1208" s="5" t="s">
+        <v>2265</v>
+      </c>
+      <c r="B1208" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1208" s="3" t="s">
+        <v>2266</v>
+      </c>
+      <c r="D1208" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1209" s="1" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1209" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>313</v>
+      </c>
+      <c r="D1209" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1210" s="5">
+        <v>91969</v>
+      </c>
+      <c r="B1210" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1210" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="D1210" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FEF48888-B150-4223-A57D-9B90C235B07E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30DF877-F170-4071-BDE3-5932CC66ACC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6525" uniqueCount="2270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6619" uniqueCount="2303">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6816,9 +6816,6 @@
     <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Ref. Moratori - Cap. 48 disj. unip. - In barr. 100 A</t>
   </si>
   <si>
-    <t>COMP 1579</t>
-  </si>
-  <si>
     <t>Quadro distrib. chapa pintada - sobrepor - Sem barr., - DIN - Ref. Moratori - Cap. 16 disj. unip.</t>
   </si>
   <si>
@@ -6850,6 +6847,108 @@
   </si>
   <si>
     <t>Dispositivo Elétrico - embutido - Placa 2x4" - Interruptor paralelo - 3 teclas</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Cap. 48 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>COMP 1960</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, COM BARRAMENTO TRIFÁSICO, PARA 48 DISJUNTORES DIN 100A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO REFERÊNCIA SINAPI CÓD. 106023 08/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor Tripolar Termomagnético - norma DIN - Curva C - 20 A - 3 kA</t>
+  </si>
+  <si>
+    <t>Dispositivo Elétrico - sobrepor - Tomada de sobrepor - Tomada blindada 3P+T - 16A</t>
+  </si>
+  <si>
+    <t>COMP 1961</t>
+  </si>
+  <si>
+    <t>TOMADA INDUSTRIAL TRIFÁSICA, 3P+T, DE 16A (COMPOSIÇÃO REFERÊNCIA: SEDOP 170955 10/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor tripolar termomagnético em caixa aberta - 2000 A - 80 kA</t>
+  </si>
+  <si>
+    <t>COMP 1962</t>
+  </si>
+  <si>
+    <t>DISJUNTOR DE CAIXA ABERTA TRIPOLAR  2000A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 03/2024)</t>
+  </si>
+  <si>
+    <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Cap. 18 disj. unip. - In barr. 100 A</t>
+  </si>
+  <si>
+    <t>COMP 1963</t>
+  </si>
+  <si>
+    <t>QUADRO DE DISTRIBUIÇÃO DE ENERGIA EM CHAPA DE AÇO GALVANIZADO, DE SOBREPOR, SEM BARRAMENTO, PARA 18 DISJUNTORES DIN - FORNECIMENTO E INSTALAÇÃO. AF_10/2020  (COMPOSIÇÃO REFERÊNCIA: SINAPI 101883)</t>
+  </si>
+  <si>
+    <t>.S.O.S CAIXAS - Conduletes - CAIXA DE DERIVAÇÃO EM ALUMÍNIO SILÍCIO INJETADO, CONDULETE DE Ø3/4". FORNECIMENTO E INSTALAÇÃO.</t>
+  </si>
+  <si>
+    <t>Cabo Unipolar - cobre - Isol.PVC - 450/750V - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>COMP 1964</t>
+  </si>
+  <si>
+    <t>INVERSOR SOLAR FOTOVOLTAICO 110kW, TENSÃO 380/220V - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103506 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Elementos fotovoltaicos - Inversores fotovoltaicos - Inversor - trifásico - 110000W - 10SPMP</t>
+  </si>
+  <si>
+    <t>Elementos fotovoltaicos - Módulo fotovoltaico - Monocristalino - 238,4 x 130,3 x 3,5 cm - 670W</t>
+  </si>
+  <si>
+    <t>COMP 1965</t>
+  </si>
+  <si>
+    <t>PAINEL SOLAR FOTOVOLTAICO, 2,384 X 1,303 M, 670W, COM SUPORTE PARA TELHA METÁLICA - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103494 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 6 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 6 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 6 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>COMP 1619</t>
+  </si>
+  <si>
+    <t>CABO FOTOVOLTAICO 6 MM² INSTALADO EM ELETRODUTO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (REFERÊNCIA: SINAPI 103503 08/2025)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 10 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 10 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 10 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>COMP 1618</t>
+  </si>
+  <si>
+    <t>CABO FOTOVOLTAICO 10 MM² INSTALADO EM ELETRODUTO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (REFERÊNCIA: SINAPI 103503 08/2025)</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - sobrepor - Aço pintada - ref Lukbox - 200x200x100 mm</t>
+  </si>
+  <si>
+    <t>COMP 910</t>
+  </si>
+  <si>
+    <t>CAIXA DE PASSAGEM METALICA 20x20x10,5 CM. (COMPOSIÇÃO REFERÊNCIA: SINAPI 068209 01/2025)</t>
   </si>
 </sst>
 </file>
@@ -7248,7 +7347,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1210"/>
+  <dimension ref="A1:B1226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -16897,7 +16996,7 @@
     </row>
     <row r="1206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1206" s="3" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B1206" s="5" t="s">
         <v>7</v>
@@ -16905,7 +17004,7 @@
     </row>
     <row r="1207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1207" s="3" t="s">
-        <v>2261</v>
+        <v>2260</v>
       </c>
       <c r="B1207" s="5" t="s">
         <v>7</v>
@@ -16913,7 +17012,7 @@
     </row>
     <row r="1208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1208" s="3" t="s">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B1208" s="5" t="s">
         <v>7</v>
@@ -16921,7 +17020,7 @@
     </row>
     <row r="1209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1209" s="3" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="B1209" s="5" t="s">
         <v>7</v>
@@ -16929,7 +17028,138 @@
     </row>
     <row r="1210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1210" s="3" t="s">
+        <v>2268</v>
+      </c>
+      <c r="B1210" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1211" s="3" t="s">
         <v>2269</v>
+      </c>
+      <c r="B1211" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1212" s="3" t="s">
+        <v>2272</v>
+      </c>
+      <c r="B1212" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1213" s="3" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1213" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1214" s="3" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1214" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1215" s="3" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B1215" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1216" s="3" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1216" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1217" s="3" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B1217" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1218" s="3" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1218" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1219" s="3" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B1219" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1220" s="3" t="s">
+        <v>2290</v>
+      </c>
+      <c r="B1220" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1221" s="3" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1221" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1222" s="3" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1222" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1223" s="3" t="s">
+        <v>2295</v>
+      </c>
+      <c r="B1223" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1224" s="3" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1224" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1225" s="3" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B1225" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1226" s="3" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1226" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -16939,7 +17169,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1210"/>
+  <dimension ref="A1:D1226"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -33806,13 +34036,13 @@
     </row>
     <row r="1205" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1205" s="5" t="s">
-        <v>2258</v>
+        <v>2270</v>
       </c>
       <c r="B1205" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C1205" s="3" t="s">
-        <v>975</v>
+        <v>2271</v>
       </c>
       <c r="D1205" s="2" t="s">
         <v>7</v>
@@ -33820,7 +34050,7 @@
     </row>
     <row r="1206" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1206" s="5" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B1206" s="5" t="s">
         <v>68</v>
@@ -33834,13 +34064,13 @@
     </row>
     <row r="1207" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1207" s="5" t="s">
+        <v>2261</v>
+      </c>
+      <c r="B1207" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1207" s="3" t="s">
         <v>2262</v>
-      </c>
-      <c r="B1207" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1207" s="3" t="s">
-        <v>2263</v>
       </c>
       <c r="D1207" s="2" t="s">
         <v>7</v>
@@ -33848,13 +34078,13 @@
     </row>
     <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1208" s="5" t="s">
+        <v>2264</v>
+      </c>
+      <c r="B1208" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1208" s="3" t="s">
         <v>2265</v>
-      </c>
-      <c r="B1208" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1208" s="3" t="s">
-        <v>2266</v>
       </c>
       <c r="D1208" s="2" t="s">
         <v>7</v>
@@ -33862,7 +34092,7 @@
     </row>
     <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1209" s="1" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B1209" s="1" t="s">
         <v>68</v>
@@ -33885,6 +34115,230 @@
         <v>572</v>
       </c>
       <c r="D1210" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1211" s="5" t="s">
+        <v>2270</v>
+      </c>
+      <c r="B1211" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1211" s="3" t="s">
+        <v>2271</v>
+      </c>
+      <c r="D1211" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1212" s="5">
+        <v>93669</v>
+      </c>
+      <c r="B1212" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1212" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D1212" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1213" s="5" t="s">
+        <v>2274</v>
+      </c>
+      <c r="B1213" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1213" s="3" t="s">
+        <v>2275</v>
+      </c>
+      <c r="D1213" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1214" s="5" t="s">
+        <v>2277</v>
+      </c>
+      <c r="B1214" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1214" s="3" t="s">
+        <v>2278</v>
+      </c>
+      <c r="D1214" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1215" s="5" t="s">
+        <v>2280</v>
+      </c>
+      <c r="B1215" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1215" s="3" t="s">
+        <v>2281</v>
+      </c>
+      <c r="D1215" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1216" s="5">
+        <v>95801</v>
+      </c>
+      <c r="B1216" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1216" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="D1216" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1217" s="5">
+        <v>91932</v>
+      </c>
+      <c r="B1217" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1217" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="D1217" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1218" s="5" t="s">
+        <v>2284</v>
+      </c>
+      <c r="B1218" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1218" s="3" t="s">
+        <v>2285</v>
+      </c>
+      <c r="D1218" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1219" s="5" t="s">
+        <v>2288</v>
+      </c>
+      <c r="B1219" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1219" s="3" t="s">
+        <v>2289</v>
+      </c>
+      <c r="D1219" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1220" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1220" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1220" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D1220" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1221" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1221" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1221" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D1221" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1222" s="5" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B1222" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1222" s="3" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D1222" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1223" s="5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1223" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1223" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D1223" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1224" s="5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1224" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1224" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D1224" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1225" s="5" t="s">
+        <v>2298</v>
+      </c>
+      <c r="B1225" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1225" s="3" t="s">
+        <v>2299</v>
+      </c>
+      <c r="D1225" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1226" s="5" t="s">
+        <v>2301</v>
+      </c>
+      <c r="B1226" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1226" s="3" t="s">
+        <v>2302</v>
+      </c>
+      <c r="D1226" s="2" t="s">
         <v>7</v>
       </c>
     </row>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D30DF877-F170-4071-BDE3-5932CC66ACC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DFFE7B-39D9-42CF-BED3-F5465C7EA2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6619" uniqueCount="2303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6689" uniqueCount="2332">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -6949,6 +6949,93 @@
   </si>
   <si>
     <t>CAIXA DE PASSAGEM METALICA 20x20x10,5 CM. (COMPOSIÇÃO REFERÊNCIA: SINAPI 068209 01/2025)</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6 CZ - 4</t>
+  </si>
+  <si>
+    <t>Leito para cabo - Médio e médio especial - 200x100mm</t>
+  </si>
+  <si>
+    <t>COMP 1966</t>
+  </si>
+  <si>
+    <t>LEITO PARA CABOS TIPO PESADO 200x100mm S/TAMPA, SUP, EMENDA (COMPOSIÇÃO REFERÊNCIA: SBC 063629 -  10/2026)</t>
+  </si>
+  <si>
+    <t>Leito para cabo - Médio e médio especial - 350x75mm</t>
+  </si>
+  <si>
+    <t>Leito para cabo - Médio especial e pesado - 400x100mm</t>
+  </si>
+  <si>
+    <t>COMP 1967</t>
+  </si>
+  <si>
+    <t>LEITO PARA CABOS TIPO PESADO 400x100mm S/TAMPA, SUP, EMENDA (COMPOSIÇÃO REFERÊNCIA: SBC 063629 -  10/2026)</t>
+  </si>
+  <si>
+    <t>Cabeamento estruturado - metálico - UTP-CAT.6 AZ - 4</t>
+  </si>
+  <si>
+    <t>Eletrocalha furada tipo U pré-galv. quen - Eletrocalha perfurada tipo U - 50x25mm chapa 18</t>
+  </si>
+  <si>
+    <t>COMP 1968</t>
+  </si>
+  <si>
+    <t>ELETROCALHA LISA OU PERFURADA EM AÇO GALVANIZADO, LARGURA 50MM E ALTURA 25MM, INCLUSIVE SUPORTE DE FIXAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: 063036 SBC 05/2024)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Huawei Switch S570035 - 48 portas</t>
+  </si>
+  <si>
+    <t>COMP 1613</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Rack - Guia de cabos aberto - 1U</t>
+  </si>
+  <si>
+    <t>COMP 1272</t>
+  </si>
+  <si>
+    <t>GUIA DE CABOS SIMPLES - FORNECIMENTO E INSTALAÇÃO (COMPOSIÇÃO DE REFERÊNCIA: SBC 059448 - 03/2023)</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Rack de Piso - 44U unc 19" x 570mm RPD 4457</t>
+  </si>
+  <si>
+    <t>COMP 1969</t>
+  </si>
+  <si>
+    <t>RACK ABERTO PADRÃO 19" 44U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Mini Rack de Parede - 5U unc 19” x 570mm MRD 557</t>
+  </si>
+  <si>
+    <t>COMP 1391</t>
+  </si>
+  <si>
+    <t>RACK FECHADO PADRÃO 19" 5U  (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Ótico - DIO - 24 fibras</t>
+  </si>
+  <si>
+    <t>COMP 1970</t>
+  </si>
+  <si>
+    <t>DISTRIBUIDOR INTERNO OPTICO (DIO) 24 FIBRAS, FORNECIMENTO E INSTALAÇÃO ( COMPOSIÇÃO REFERÊNCIA SBC CÓD. 059251 10/2025)</t>
+  </si>
+  <si>
+    <t>Leito para cabo - Médio e médio especial - 100x100mm</t>
+  </si>
+  <si>
+    <t>COMP 1971</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> LEITO PARA CABOS TIPO PESADO 100x100mm S/TAMPA, SUP, EMENDA (COMPOSIÇÃO REFERÊNCIA: SBC 063629 -  10/2026)</t>
   </si>
 </sst>
 </file>
@@ -7347,7 +7434,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1226"/>
+  <dimension ref="A1:B1238"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -17162,6 +17249,102 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1227" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1227" s="3" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1227" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1228" s="3" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1228" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1229" s="3" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1229" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1230" s="3" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B1230" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1231" s="3" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B1231" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1232" s="3" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B1232" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1233" s="3" t="s">
+        <v>2315</v>
+      </c>
+      <c r="B1233" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1234" s="3" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B1234" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1235" s="3" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B1235" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1236" s="3" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B1236" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1237" s="3" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B1237" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1238" s="3" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B1238" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17169,7 +17352,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1226"/>
+  <dimension ref="A1:D1238"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -34342,6 +34525,174 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1227" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1227" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1227" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1227" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1227" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1228" s="5" t="s">
+        <v>2305</v>
+      </c>
+      <c r="B1228" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1228" s="3" t="s">
+        <v>2306</v>
+      </c>
+      <c r="D1228" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1229" s="5" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1229" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1229" s="3" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D1229" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1230" s="5" t="s">
+        <v>2309</v>
+      </c>
+      <c r="B1230" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1230" s="3" t="s">
+        <v>2310</v>
+      </c>
+      <c r="D1230" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1231" s="5">
+        <v>98297</v>
+      </c>
+      <c r="B1231" s="5" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1231" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1231" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1232" s="5" t="s">
+        <v>2313</v>
+      </c>
+      <c r="B1232" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1232" s="3" t="s">
+        <v>2314</v>
+      </c>
+      <c r="D1232" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1233" s="5" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B1233" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1233" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D1233" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1234" s="5" t="s">
+        <v>2318</v>
+      </c>
+      <c r="B1234" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1234" s="3" t="s">
+        <v>2319</v>
+      </c>
+      <c r="D1234" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1235" s="5" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B1235" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1235" s="3" t="s">
+        <v>2322</v>
+      </c>
+      <c r="D1235" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1236" s="5" t="s">
+        <v>2324</v>
+      </c>
+      <c r="B1236" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1236" s="3" t="s">
+        <v>2325</v>
+      </c>
+      <c r="D1236" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1237" s="5" t="s">
+        <v>2327</v>
+      </c>
+      <c r="B1237" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1237" s="3" t="s">
+        <v>2328</v>
+      </c>
+      <c r="D1237" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1238" s="5" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B1238" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1238" s="3" t="s">
+        <v>2331</v>
+      </c>
+      <c r="D1238" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9DFFE7B-39D9-42CF-BED3-F5465C7EA2B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0627E266-F969-4325-BBC9-1148F1DBAFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6689" uniqueCount="2332">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6714" uniqueCount="2341">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -5628,9 +5628,6 @@
     <t>Luminária e acessórios - Luminária Elegance Fit Avant - 36W</t>
   </si>
   <si>
-    <t>LUMINÁRIA TIPO CALHA, DE EMBUTIR, PARA 1 LÂMPADA TUBULAR LED DE 36 W, SEM LÂMPADA E SEM REATOR - FORNECIMENTO E INSTALAÇÃO. AF_09/2024</t>
-  </si>
-  <si>
     <t>Luminária e acessórios - Spot - Avant - 5W</t>
   </si>
   <si>
@@ -7036,6 +7033,36 @@
   </si>
   <si>
     <t xml:space="preserve"> LEITO PARA CABOS TIPO PESADO 100x100mm S/TAMPA, SUP, EMENDA (COMPOSIÇÃO REFERÊNCIA: SBC 063629 -  10/2026)</t>
+  </si>
+  <si>
+    <t>COMP 1973</t>
+  </si>
+  <si>
+    <t>LUMINÁRIA TIPO CALHA, DE EMBUTIR, PARA 1 LÂMPADA TUBULAR LED DE 36 W, SEM LÂMPADA E SEM REATOR - FORNECIMENTO E INSTALAÇÃO. AF_09/2024 (COMPOSIÇÃO REFERÊNCIA: SINAPI 100914 - 09/2026)</t>
+  </si>
+  <si>
+    <t>Intelbras - Equipamentos de Rede e Rack - Mini Rack de Parede - 12U  19” x 570mm MRD 1257</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Processador de áudio profissional - DBX Drive Rack Venu 127V 3in/6out</t>
+  </si>
+  <si>
+    <t>Acessórios Cabeamento - Metálico - Amplificador de áudio profissional - 2000W</t>
+  </si>
+  <si>
+    <t>COMP 1529</t>
+  </si>
+  <si>
+    <t>AMPLIFICADOR DE ÁUDIO PROFISSIONAL - 2000W (COMPOSIÇÃO DE REFERÊNCIA: SBC 059085 - 06/2022)</t>
+  </si>
+  <si>
+    <t>Dispositivo TV/Som - Grupo - Microfone de Piso</t>
+  </si>
+  <si>
+    <t>COMP 927</t>
+  </si>
+  <si>
+    <t>MICROFONE DE PISO (REFERÊNCIA: SBC 068282 01/2025)</t>
   </si>
 </sst>
 </file>
@@ -7434,7 +7461,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1238"/>
+  <dimension ref="A1:B1242"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -15299,7 +15326,7 @@
     </row>
     <row r="983" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A983" s="3" t="s">
-        <v>1863</v>
+        <v>1862</v>
       </c>
       <c r="B983" s="5" t="s">
         <v>7</v>
@@ -15307,7 +15334,7 @@
     </row>
     <row r="984" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A984" s="3" t="s">
-        <v>1868</v>
+        <v>1867</v>
       </c>
       <c r="B984" s="5" t="s">
         <v>7</v>
@@ -15315,7 +15342,7 @@
     </row>
     <row r="985" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A985" s="3" t="s">
-        <v>1869</v>
+        <v>1868</v>
       </c>
       <c r="B985" s="5" t="s">
         <v>7</v>
@@ -15323,7 +15350,7 @@
     </row>
     <row r="986" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A986" s="3" t="s">
-        <v>1873</v>
+        <v>1872</v>
       </c>
       <c r="B986" s="5" t="s">
         <v>7</v>
@@ -15331,7 +15358,7 @@
     </row>
     <row r="987" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A987" s="3" t="s">
-        <v>1874</v>
+        <v>1873</v>
       </c>
       <c r="B987" s="5" t="s">
         <v>7</v>
@@ -15339,7 +15366,7 @@
     </row>
     <row r="988" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A988" s="3" t="s">
-        <v>1875</v>
+        <v>1874</v>
       </c>
       <c r="B988" s="5" t="s">
         <v>7</v>
@@ -15347,7 +15374,7 @@
     </row>
     <row r="989" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A989" s="3" t="s">
-        <v>1876</v>
+        <v>1875</v>
       </c>
       <c r="B989" s="5" t="s">
         <v>7</v>
@@ -15355,7 +15382,7 @@
     </row>
     <row r="990" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A990" s="3" t="s">
-        <v>1877</v>
+        <v>1876</v>
       </c>
       <c r="B990" s="5" t="s">
         <v>7</v>
@@ -15363,7 +15390,7 @@
     </row>
     <row r="991" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A991" s="3" t="s">
-        <v>1872</v>
+        <v>1871</v>
       </c>
       <c r="B991" s="5" t="s">
         <v>7</v>
@@ -15371,7 +15398,7 @@
     </row>
     <row r="992" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A992" s="3" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="B992" s="6" t="s">
         <v>20</v>
@@ -15379,7 +15406,7 @@
     </row>
     <row r="993" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A993" s="3" t="s">
-        <v>1892</v>
+        <v>1891</v>
       </c>
       <c r="B993" s="6" t="s">
         <v>20</v>
@@ -15387,7 +15414,7 @@
     </row>
     <row r="994" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A994" s="3" t="s">
-        <v>1894</v>
+        <v>1893</v>
       </c>
       <c r="B994" s="6" t="s">
         <v>20</v>
@@ -15395,7 +15422,7 @@
     </row>
     <row r="995" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A995" s="3" t="s">
-        <v>1895</v>
+        <v>1894</v>
       </c>
       <c r="B995" s="6" t="s">
         <v>20</v>
@@ -15403,7 +15430,7 @@
     </row>
     <row r="996" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A996" s="3" t="s">
-        <v>1896</v>
+        <v>1895</v>
       </c>
       <c r="B996" s="6" t="s">
         <v>20</v>
@@ -15411,7 +15438,7 @@
     </row>
     <row r="997" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A997" s="3" t="s">
-        <v>1897</v>
+        <v>1896</v>
       </c>
       <c r="B997" s="6" t="s">
         <v>20</v>
@@ -15419,7 +15446,7 @@
     </row>
     <row r="998" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A998" s="3" t="s">
-        <v>1898</v>
+        <v>1897</v>
       </c>
       <c r="B998" s="6" t="s">
         <v>20</v>
@@ -15427,7 +15454,7 @@
     </row>
     <row r="999" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A999" s="3" t="s">
-        <v>1899</v>
+        <v>1898</v>
       </c>
       <c r="B999" s="6" t="s">
         <v>20</v>
@@ -15435,7 +15462,7 @@
     </row>
     <row r="1000" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1000" s="3" t="s">
-        <v>1900</v>
+        <v>1899</v>
       </c>
       <c r="B1000" s="6" t="s">
         <v>20</v>
@@ -15443,7 +15470,7 @@
     </row>
     <row r="1001" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1001" s="3" t="s">
-        <v>1902</v>
+        <v>1901</v>
       </c>
       <c r="B1001" s="5" t="s">
         <v>7</v>
@@ -15451,7 +15478,7 @@
     </row>
     <row r="1002" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1002" s="3" t="s">
-        <v>1903</v>
+        <v>1902</v>
       </c>
       <c r="B1002" s="5" t="s">
         <v>7</v>
@@ -15459,7 +15486,7 @@
     </row>
     <row r="1003" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1003" s="3" t="s">
-        <v>1905</v>
+        <v>1904</v>
       </c>
       <c r="B1003" s="5" t="s">
         <v>7</v>
@@ -15467,7 +15494,7 @@
     </row>
     <row r="1004" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1004" s="3" t="s">
-        <v>1908</v>
+        <v>1907</v>
       </c>
       <c r="B1004" s="5" t="s">
         <v>7</v>
@@ -15475,7 +15502,7 @@
     </row>
     <row r="1005" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1005" s="3" t="s">
-        <v>1914</v>
+        <v>1913</v>
       </c>
       <c r="B1005" s="5" t="s">
         <v>7</v>
@@ -15483,7 +15510,7 @@
     </row>
     <row r="1006" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1006" s="3" t="s">
-        <v>1911</v>
+        <v>1910</v>
       </c>
       <c r="B1006" s="5" t="s">
         <v>7</v>
@@ -15491,7 +15518,7 @@
     </row>
     <row r="1007" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1007" s="3" t="s">
-        <v>1913</v>
+        <v>1912</v>
       </c>
       <c r="B1007" s="5" t="s">
         <v>7</v>
@@ -15499,7 +15526,7 @@
     </row>
     <row r="1008" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1008" s="3" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="B1008" s="5" t="s">
         <v>7</v>
@@ -15507,7 +15534,7 @@
     </row>
     <row r="1009" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1009" s="3" t="s">
-        <v>1917</v>
+        <v>1916</v>
       </c>
       <c r="B1009" s="5" t="s">
         <v>7</v>
@@ -15515,7 +15542,7 @@
     </row>
     <row r="1010" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1010" s="3" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="B1010" s="5" t="s">
         <v>7</v>
@@ -15523,7 +15550,7 @@
     </row>
     <row r="1011" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1011" s="3" t="s">
-        <v>1921</v>
+        <v>1920</v>
       </c>
       <c r="B1011" s="5" t="s">
         <v>7</v>
@@ -15531,7 +15558,7 @@
     </row>
     <row r="1012" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1012" s="3" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="B1012" s="5" t="s">
         <v>7</v>
@@ -15539,7 +15566,7 @@
     </row>
     <row r="1013" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1013" s="3" t="s">
-        <v>1926</v>
+        <v>1925</v>
       </c>
       <c r="B1013" s="5" t="s">
         <v>7</v>
@@ -15547,7 +15574,7 @@
     </row>
     <row r="1014" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1014" s="3" t="s">
-        <v>1927</v>
+        <v>1926</v>
       </c>
       <c r="B1014" s="5" t="s">
         <v>7</v>
@@ -15555,7 +15582,7 @@
     </row>
     <row r="1015" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1015" s="3" t="s">
-        <v>1928</v>
+        <v>1927</v>
       </c>
       <c r="B1015" s="5" t="s">
         <v>7</v>
@@ -15563,7 +15590,7 @@
     </row>
     <row r="1016" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1016" s="3" t="s">
-        <v>1931</v>
+        <v>1930</v>
       </c>
       <c r="B1016" s="5" t="s">
         <v>7</v>
@@ -15571,7 +15598,7 @@
     </row>
     <row r="1017" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1017" s="3" t="s">
-        <v>1932</v>
+        <v>1931</v>
       </c>
       <c r="B1017" s="6" t="s">
         <v>20</v>
@@ -15579,7 +15606,7 @@
     </row>
     <row r="1018" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1018" s="3" t="s">
-        <v>1933</v>
+        <v>1932</v>
       </c>
       <c r="B1018" s="6" t="s">
         <v>20</v>
@@ -15587,7 +15614,7 @@
     </row>
     <row r="1019" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1019" s="3" t="s">
-        <v>1934</v>
+        <v>1933</v>
       </c>
       <c r="B1019" s="6" t="s">
         <v>20</v>
@@ -15595,7 +15622,7 @@
     </row>
     <row r="1020" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1020" s="3" t="s">
-        <v>1935</v>
+        <v>1934</v>
       </c>
       <c r="B1020" s="6" t="s">
         <v>20</v>
@@ -15603,7 +15630,7 @@
     </row>
     <row r="1021" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1021" s="3" t="s">
-        <v>1936</v>
+        <v>1935</v>
       </c>
       <c r="B1021" s="6" t="s">
         <v>20</v>
@@ -15611,7 +15638,7 @@
     </row>
     <row r="1022" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1022" s="3" t="s">
-        <v>1937</v>
+        <v>1936</v>
       </c>
       <c r="B1022" s="6" t="s">
         <v>20</v>
@@ -15619,7 +15646,7 @@
     </row>
     <row r="1023" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1023" s="3" t="s">
-        <v>1940</v>
+        <v>1939</v>
       </c>
       <c r="B1023" s="6" t="s">
         <v>20</v>
@@ -15627,7 +15654,7 @@
     </row>
     <row r="1024" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1024" s="3" t="s">
-        <v>1943</v>
+        <v>1942</v>
       </c>
       <c r="B1024" s="5" t="s">
         <v>7</v>
@@ -15635,7 +15662,7 @@
     </row>
     <row r="1025" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1025" s="3" t="s">
-        <v>1946</v>
+        <v>1945</v>
       </c>
       <c r="B1025" s="5" t="s">
         <v>7</v>
@@ -15643,7 +15670,7 @@
     </row>
     <row r="1026" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1026" s="3" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="B1026" s="5" t="s">
         <v>7</v>
@@ -15651,7 +15678,7 @@
     </row>
     <row r="1027" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1027" s="3" t="s">
-        <v>1950</v>
+        <v>1949</v>
       </c>
       <c r="B1027" s="5" t="s">
         <v>7</v>
@@ -15659,7 +15686,7 @@
     </row>
     <row r="1028" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1028" s="3" t="s">
-        <v>1955</v>
+        <v>1954</v>
       </c>
       <c r="B1028" s="6" t="s">
         <v>20</v>
@@ -15667,7 +15694,7 @@
     </row>
     <row r="1029" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1029" s="3" t="s">
-        <v>1956</v>
+        <v>1955</v>
       </c>
       <c r="B1029" s="6" t="s">
         <v>20</v>
@@ -15675,7 +15702,7 @@
     </row>
     <row r="1030" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1030" s="3" t="s">
-        <v>1957</v>
+        <v>1956</v>
       </c>
       <c r="B1030" s="6" t="s">
         <v>20</v>
@@ -15683,7 +15710,7 @@
     </row>
     <row r="1031" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1031" s="3" t="s">
-        <v>1958</v>
+        <v>1957</v>
       </c>
       <c r="B1031" s="6" t="s">
         <v>20</v>
@@ -15691,7 +15718,7 @@
     </row>
     <row r="1032" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1032" s="3" t="s">
-        <v>1959</v>
+        <v>1958</v>
       </c>
       <c r="B1032" s="6" t="s">
         <v>20</v>
@@ -15699,7 +15726,7 @@
     </row>
     <row r="1033" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1033" s="3" t="s">
-        <v>1960</v>
+        <v>1959</v>
       </c>
       <c r="B1033" s="6" t="s">
         <v>20</v>
@@ -15707,7 +15734,7 @@
     </row>
     <row r="1034" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1034" s="3" t="s">
-        <v>1961</v>
+        <v>1960</v>
       </c>
       <c r="B1034" s="6" t="s">
         <v>20</v>
@@ -15715,7 +15742,7 @@
     </row>
     <row r="1035" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1035" s="3" t="s">
-        <v>1962</v>
+        <v>1961</v>
       </c>
       <c r="B1035" s="6" t="s">
         <v>20</v>
@@ -15723,7 +15750,7 @@
     </row>
     <row r="1036" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1036" s="3" t="s">
-        <v>1963</v>
+        <v>1962</v>
       </c>
       <c r="B1036" s="6" t="s">
         <v>20</v>
@@ -15731,7 +15758,7 @@
     </row>
     <row r="1037" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1037" s="3" t="s">
-        <v>1964</v>
+        <v>1963</v>
       </c>
       <c r="B1037" s="6" t="s">
         <v>20</v>
@@ -15739,7 +15766,7 @@
     </row>
     <row r="1038" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1038" s="3" t="s">
-        <v>1965</v>
+        <v>1964</v>
       </c>
       <c r="B1038" s="6" t="s">
         <v>20</v>
@@ -15747,7 +15774,7 @@
     </row>
     <row r="1039" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1039" s="3" t="s">
-        <v>1966</v>
+        <v>1965</v>
       </c>
       <c r="B1039" s="6" t="s">
         <v>20</v>
@@ -15755,7 +15782,7 @@
     </row>
     <row r="1040" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1040" s="3" t="s">
-        <v>1967</v>
+        <v>1966</v>
       </c>
       <c r="B1040" s="6" t="s">
         <v>20</v>
@@ -15763,7 +15790,7 @@
     </row>
     <row r="1041" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1041" s="3" t="s">
-        <v>1968</v>
+        <v>1967</v>
       </c>
       <c r="B1041" s="6" t="s">
         <v>20</v>
@@ -15771,7 +15798,7 @@
     </row>
     <row r="1042" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1042" s="3" t="s">
-        <v>1969</v>
+        <v>1968</v>
       </c>
       <c r="B1042" s="6" t="s">
         <v>20</v>
@@ -15779,7 +15806,7 @@
     </row>
     <row r="1043" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1043" s="3" t="s">
-        <v>1970</v>
+        <v>1969</v>
       </c>
       <c r="B1043" s="6" t="s">
         <v>20</v>
@@ -15787,7 +15814,7 @@
     </row>
     <row r="1044" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1044" s="3" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B1044" s="6" t="s">
         <v>20</v>
@@ -15795,7 +15822,7 @@
     </row>
     <row r="1045" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1045" s="3" t="s">
-        <v>1972</v>
+        <v>1971</v>
       </c>
       <c r="B1045" s="6" t="s">
         <v>20</v>
@@ -15803,7 +15830,7 @@
     </row>
     <row r="1046" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1046" s="3" t="s">
-        <v>1973</v>
+        <v>1972</v>
       </c>
       <c r="B1046" s="6" t="s">
         <v>20</v>
@@ -15811,7 +15838,7 @@
     </row>
     <row r="1047" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1047" s="3" t="s">
-        <v>1974</v>
+        <v>1973</v>
       </c>
       <c r="B1047" s="6" t="s">
         <v>20</v>
@@ -15819,7 +15846,7 @@
     </row>
     <row r="1048" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1048" s="3" t="s">
-        <v>1975</v>
+        <v>1974</v>
       </c>
       <c r="B1048" s="6" t="s">
         <v>20</v>
@@ -15827,7 +15854,7 @@
     </row>
     <row r="1049" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1049" s="3" t="s">
-        <v>1976</v>
+        <v>1975</v>
       </c>
       <c r="B1049" s="6" t="s">
         <v>20</v>
@@ -15835,7 +15862,7 @@
     </row>
     <row r="1050" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1050" s="3" t="s">
-        <v>1977</v>
+        <v>1976</v>
       </c>
       <c r="B1050" s="6" t="s">
         <v>20</v>
@@ -15843,7 +15870,7 @@
     </row>
     <row r="1051" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1051" s="3" t="s">
-        <v>1978</v>
+        <v>1977</v>
       </c>
       <c r="B1051" s="6" t="s">
         <v>20</v>
@@ -15851,7 +15878,7 @@
     </row>
     <row r="1052" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1052" s="3" t="s">
-        <v>1979</v>
+        <v>1978</v>
       </c>
       <c r="B1052" s="6" t="s">
         <v>20</v>
@@ -15859,7 +15886,7 @@
     </row>
     <row r="1053" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1053" s="3" t="s">
-        <v>1980</v>
+        <v>1979</v>
       </c>
       <c r="B1053" s="6" t="s">
         <v>20</v>
@@ -15867,7 +15894,7 @@
     </row>
     <row r="1054" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1054" s="3" t="s">
-        <v>1981</v>
+        <v>1980</v>
       </c>
       <c r="B1054" s="6" t="s">
         <v>20</v>
@@ -15875,7 +15902,7 @@
     </row>
     <row r="1055" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1055" s="3" t="s">
-        <v>1982</v>
+        <v>1981</v>
       </c>
       <c r="B1055" s="6" t="s">
         <v>20</v>
@@ -15883,7 +15910,7 @@
     </row>
     <row r="1056" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1056" s="3" t="s">
-        <v>1983</v>
+        <v>1982</v>
       </c>
       <c r="B1056" s="6" t="s">
         <v>20</v>
@@ -15891,7 +15918,7 @@
     </row>
     <row r="1057" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1057" s="3" t="s">
-        <v>1984</v>
+        <v>1983</v>
       </c>
       <c r="B1057" s="6" t="s">
         <v>20</v>
@@ -15899,7 +15926,7 @@
     </row>
     <row r="1058" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1058" s="3" t="s">
-        <v>1985</v>
+        <v>1984</v>
       </c>
       <c r="B1058" s="6" t="s">
         <v>20</v>
@@ -15907,7 +15934,7 @@
     </row>
     <row r="1059" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1059" s="3" t="s">
-        <v>1986</v>
+        <v>1985</v>
       </c>
       <c r="B1059" s="6" t="s">
         <v>20</v>
@@ -15915,7 +15942,7 @@
     </row>
     <row r="1060" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1060" s="3" t="s">
-        <v>1987</v>
+        <v>1986</v>
       </c>
       <c r="B1060" s="6" t="s">
         <v>20</v>
@@ -15923,7 +15950,7 @@
     </row>
     <row r="1061" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1061" s="3" t="s">
-        <v>1988</v>
+        <v>1987</v>
       </c>
       <c r="B1061" s="6" t="s">
         <v>20</v>
@@ -15931,7 +15958,7 @@
     </row>
     <row r="1062" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1062" s="3" t="s">
-        <v>1989</v>
+        <v>1988</v>
       </c>
       <c r="B1062" s="6" t="s">
         <v>20</v>
@@ -15939,7 +15966,7 @@
     </row>
     <row r="1063" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1063" s="3" t="s">
-        <v>1990</v>
+        <v>1989</v>
       </c>
       <c r="B1063" s="6" t="s">
         <v>20</v>
@@ -15947,7 +15974,7 @@
     </row>
     <row r="1064" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1064" s="3" t="s">
-        <v>1991</v>
+        <v>1990</v>
       </c>
       <c r="B1064" s="6" t="s">
         <v>20</v>
@@ -15955,7 +15982,7 @@
     </row>
     <row r="1065" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1065" s="3" t="s">
-        <v>1992</v>
+        <v>1991</v>
       </c>
       <c r="B1065" s="6" t="s">
         <v>20</v>
@@ -15963,7 +15990,7 @@
     </row>
     <row r="1066" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1066" s="3" t="s">
-        <v>1993</v>
+        <v>1992</v>
       </c>
       <c r="B1066" s="6" t="s">
         <v>20</v>
@@ -15971,7 +15998,7 @@
     </row>
     <row r="1067" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1067" s="3" t="s">
-        <v>1994</v>
+        <v>1993</v>
       </c>
       <c r="B1067" s="6" t="s">
         <v>20</v>
@@ -15979,7 +16006,7 @@
     </row>
     <row r="1068" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1068" s="3" t="s">
-        <v>1995</v>
+        <v>1994</v>
       </c>
       <c r="B1068" s="6" t="s">
         <v>20</v>
@@ -15987,7 +16014,7 @@
     </row>
     <row r="1069" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1069" s="3" t="s">
-        <v>1996</v>
+        <v>1995</v>
       </c>
       <c r="B1069" s="6" t="s">
         <v>20</v>
@@ -15995,7 +16022,7 @@
     </row>
     <row r="1070" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1070" s="3" t="s">
-        <v>1997</v>
+        <v>1996</v>
       </c>
       <c r="B1070" s="6" t="s">
         <v>20</v>
@@ -16003,7 +16030,7 @@
     </row>
     <row r="1071" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1071" s="3" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="B1071" s="6" t="s">
         <v>20</v>
@@ -16011,7 +16038,7 @@
     </row>
     <row r="1072" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1072" s="3" t="s">
-        <v>1999</v>
+        <v>1998</v>
       </c>
       <c r="B1072" s="6" t="s">
         <v>20</v>
@@ -16019,7 +16046,7 @@
     </row>
     <row r="1073" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1073" s="3" t="s">
-        <v>2000</v>
+        <v>1999</v>
       </c>
       <c r="B1073" s="6" t="s">
         <v>20</v>
@@ -16027,7 +16054,7 @@
     </row>
     <row r="1074" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1074" s="3" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="B1074" s="6" t="s">
         <v>20</v>
@@ -16035,7 +16062,7 @@
     </row>
     <row r="1075" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1075" s="3" t="s">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="B1075" s="6" t="s">
         <v>20</v>
@@ -16043,7 +16070,7 @@
     </row>
     <row r="1076" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1076" s="3" t="s">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="B1076" s="6" t="s">
         <v>20</v>
@@ -16051,7 +16078,7 @@
     </row>
     <row r="1077" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1077" s="3" t="s">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="B1077" s="5" t="s">
         <v>7</v>
@@ -16059,7 +16086,7 @@
     </row>
     <row r="1078" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1078" s="3" t="s">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="B1078" s="5" t="s">
         <v>7</v>
@@ -16067,7 +16094,7 @@
     </row>
     <row r="1079" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1079" s="3" t="s">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="B1079" s="5" t="s">
         <v>7</v>
@@ -16075,7 +16102,7 @@
     </row>
     <row r="1080" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1080" s="3" t="s">
-        <v>2010</v>
+        <v>2009</v>
       </c>
       <c r="B1080" s="5" t="s">
         <v>7</v>
@@ -16083,7 +16110,7 @@
     </row>
     <row r="1081" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1081" s="3" t="s">
-        <v>2013</v>
+        <v>2012</v>
       </c>
       <c r="B1081" s="5" t="s">
         <v>7</v>
@@ -16091,7 +16118,7 @@
     </row>
     <row r="1082" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1082" s="3" t="s">
-        <v>2015</v>
+        <v>2014</v>
       </c>
       <c r="B1082" s="5" t="s">
         <v>7</v>
@@ -16099,7 +16126,7 @@
     </row>
     <row r="1083" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1083" s="3" t="s">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="B1083" s="5" t="s">
         <v>7</v>
@@ -16107,7 +16134,7 @@
     </row>
     <row r="1084" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1084" s="3" t="s">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="B1084" s="5" t="s">
         <v>7</v>
@@ -16115,7 +16142,7 @@
     </row>
     <row r="1085" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1085" s="3" t="s">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="B1085" s="5" t="s">
         <v>7</v>
@@ -16123,7 +16150,7 @@
     </row>
     <row r="1086" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1086" s="3" t="s">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="B1086" s="5" t="s">
         <v>7</v>
@@ -16131,7 +16158,7 @@
     </row>
     <row r="1087" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1087" s="3" t="s">
-        <v>2027</v>
+        <v>2026</v>
       </c>
       <c r="B1087" s="5" t="s">
         <v>7</v>
@@ -16139,7 +16166,7 @@
     </row>
     <row r="1088" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1088" s="3" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="B1088" s="5" t="s">
         <v>7</v>
@@ -16147,7 +16174,7 @@
     </row>
     <row r="1089" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1089" s="3" t="s">
-        <v>2035</v>
+        <v>2034</v>
       </c>
       <c r="B1089" s="5" t="s">
         <v>7</v>
@@ -16155,7 +16182,7 @@
     </row>
     <row r="1090" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1090" s="3" t="s">
-        <v>2036</v>
+        <v>2035</v>
       </c>
       <c r="B1090" s="5" t="s">
         <v>7</v>
@@ -16163,7 +16190,7 @@
     </row>
     <row r="1091" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1091" s="3" t="s">
-        <v>2041</v>
+        <v>2040</v>
       </c>
       <c r="B1091" s="5" t="s">
         <v>7</v>
@@ -16171,7 +16198,7 @@
     </row>
     <row r="1092" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1092" s="3" t="s">
-        <v>2042</v>
+        <v>2041</v>
       </c>
       <c r="B1092" s="5" t="s">
         <v>7</v>
@@ -16179,7 +16206,7 @@
     </row>
     <row r="1093" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1093" s="3" t="s">
-        <v>2045</v>
+        <v>2044</v>
       </c>
       <c r="B1093" s="5" t="s">
         <v>7</v>
@@ -16187,7 +16214,7 @@
     </row>
     <row r="1094" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1094" s="3" t="s">
-        <v>2048</v>
+        <v>2047</v>
       </c>
       <c r="B1094" s="5" t="s">
         <v>7</v>
@@ -16195,7 +16222,7 @@
     </row>
     <row r="1095" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1095" s="3" t="s">
-        <v>2051</v>
+        <v>2050</v>
       </c>
       <c r="B1095" s="5" t="s">
         <v>7</v>
@@ -16203,7 +16230,7 @@
     </row>
     <row r="1096" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1096" s="3" t="s">
-        <v>2052</v>
+        <v>2051</v>
       </c>
       <c r="B1096" s="5" t="s">
         <v>7</v>
@@ -16211,7 +16238,7 @@
     </row>
     <row r="1097" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1097" s="3" t="s">
-        <v>2054</v>
+        <v>2053</v>
       </c>
       <c r="B1097" s="5" t="s">
         <v>7</v>
@@ -16219,7 +16246,7 @@
     </row>
     <row r="1098" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1098" s="3" t="s">
-        <v>2056</v>
+        <v>2055</v>
       </c>
       <c r="B1098" s="5" t="s">
         <v>7</v>
@@ -16227,7 +16254,7 @@
     </row>
     <row r="1099" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1099" s="3" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="B1099" s="5" t="s">
         <v>7</v>
@@ -16235,7 +16262,7 @@
     </row>
     <row r="1100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1100" s="3" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="B1100" s="5" t="s">
         <v>7</v>
@@ -16243,7 +16270,7 @@
     </row>
     <row r="1101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1101" s="3" t="s">
-        <v>2063</v>
+        <v>2062</v>
       </c>
       <c r="B1101" s="5" t="s">
         <v>7</v>
@@ -16251,7 +16278,7 @@
     </row>
     <row r="1102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1102" s="3" t="s">
-        <v>2066</v>
+        <v>2065</v>
       </c>
       <c r="B1102" s="5" t="s">
         <v>20</v>
@@ -16259,7 +16286,7 @@
     </row>
     <row r="1103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1103" s="3" t="s">
-        <v>2074</v>
+        <v>2073</v>
       </c>
       <c r="B1103" s="5" t="s">
         <v>20</v>
@@ -16267,7 +16294,7 @@
     </row>
     <row r="1104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1104" s="3" t="s">
-        <v>2071</v>
+        <v>2070</v>
       </c>
       <c r="B1104" s="5" t="s">
         <v>20</v>
@@ -16275,7 +16302,7 @@
     </row>
     <row r="1105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1105" s="3" t="s">
-        <v>2075</v>
+        <v>2074</v>
       </c>
       <c r="B1105" s="5" t="s">
         <v>7</v>
@@ -16283,7 +16310,7 @@
     </row>
     <row r="1106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1106" s="3" t="s">
-        <v>2080</v>
+        <v>2079</v>
       </c>
       <c r="B1106" s="5" t="s">
         <v>7</v>
@@ -16291,7 +16318,7 @@
     </row>
     <row r="1107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1107" s="3" t="s">
-        <v>2081</v>
+        <v>2080</v>
       </c>
       <c r="B1107" s="5" t="s">
         <v>7</v>
@@ -16299,7 +16326,7 @@
     </row>
     <row r="1108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1108" s="3" t="s">
-        <v>2086</v>
+        <v>2085</v>
       </c>
       <c r="B1108" s="5" t="s">
         <v>7</v>
@@ -16307,7 +16334,7 @@
     </row>
     <row r="1109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1109" s="3" t="s">
-        <v>2087</v>
+        <v>2086</v>
       </c>
       <c r="B1109" s="5" t="s">
         <v>7</v>
@@ -16315,7 +16342,7 @@
     </row>
     <row r="1110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1110" s="3" t="s">
-        <v>2090</v>
+        <v>2089</v>
       </c>
       <c r="B1110" s="5" t="s">
         <v>7</v>
@@ -16323,7 +16350,7 @@
     </row>
     <row r="1111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1111" s="3" t="s">
-        <v>2094</v>
+        <v>2093</v>
       </c>
       <c r="B1111" s="5" t="s">
         <v>7</v>
@@ -16331,7 +16358,7 @@
     </row>
     <row r="1112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1112" s="3" t="s">
-        <v>2095</v>
+        <v>2094</v>
       </c>
       <c r="B1112" s="5" t="s">
         <v>7</v>
@@ -16339,7 +16366,7 @@
     </row>
     <row r="1113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1113" s="3" t="s">
-        <v>2097</v>
+        <v>2096</v>
       </c>
       <c r="B1113" s="5" t="s">
         <v>20</v>
@@ -16347,7 +16374,7 @@
     </row>
     <row r="1114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1114" s="3" t="s">
-        <v>2098</v>
+        <v>2097</v>
       </c>
       <c r="B1114" s="5" t="s">
         <v>20</v>
@@ -16355,7 +16382,7 @@
     </row>
     <row r="1115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1115" s="3" t="s">
-        <v>2099</v>
+        <v>2098</v>
       </c>
       <c r="B1115" s="5" t="s">
         <v>7</v>
@@ -16363,7 +16390,7 @@
     </row>
     <row r="1116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1116" s="3" t="s">
-        <v>2100</v>
+        <v>2099</v>
       </c>
       <c r="B1116" s="5" t="s">
         <v>7</v>
@@ -16371,7 +16398,7 @@
     </row>
     <row r="1117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1117" s="3" t="s">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="B1117" s="5" t="s">
         <v>7</v>
@@ -16379,7 +16406,7 @@
     </row>
     <row r="1118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1118" s="3" t="s">
-        <v>2103</v>
+        <v>2102</v>
       </c>
       <c r="B1118" s="5" t="s">
         <v>7</v>
@@ -16387,7 +16414,7 @@
     </row>
     <row r="1119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1119" s="3" t="s">
-        <v>2104</v>
+        <v>2103</v>
       </c>
       <c r="B1119" s="5" t="s">
         <v>7</v>
@@ -16395,7 +16422,7 @@
     </row>
     <row r="1120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1120" s="3" t="s">
-        <v>2107</v>
+        <v>2106</v>
       </c>
       <c r="B1120" s="5" t="s">
         <v>20</v>
@@ -16403,23 +16430,23 @@
     </row>
     <row r="1121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1121" s="3" t="s">
-        <v>2109</v>
+        <v>2108</v>
       </c>
       <c r="B1121" s="6" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1122" s="3" t="s">
+        <v>2109</v>
+      </c>
+      <c r="B1122" s="6" t="s">
         <v>2110</v>
-      </c>
-      <c r="B1122" s="6" t="s">
-        <v>2111</v>
       </c>
     </row>
     <row r="1123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1123" s="3" t="s">
-        <v>2114</v>
+        <v>2113</v>
       </c>
       <c r="B1123" s="5" t="s">
         <v>7</v>
@@ -16427,7 +16454,7 @@
     </row>
     <row r="1124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1124" s="3" t="s">
-        <v>2115</v>
+        <v>2114</v>
       </c>
       <c r="B1124" s="5" t="s">
         <v>7</v>
@@ -16435,7 +16462,7 @@
     </row>
     <row r="1125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1125" s="3" t="s">
-        <v>2117</v>
+        <v>2116</v>
       </c>
       <c r="B1125" s="5" t="s">
         <v>20</v>
@@ -16443,7 +16470,7 @@
     </row>
     <row r="1126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1126" s="3" t="s">
-        <v>2120</v>
+        <v>2119</v>
       </c>
       <c r="B1126" s="5" t="s">
         <v>20</v>
@@ -16451,7 +16478,7 @@
     </row>
     <row r="1127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1127" s="3" t="s">
-        <v>2123</v>
+        <v>2122</v>
       </c>
       <c r="B1127" s="5" t="s">
         <v>7</v>
@@ -16459,7 +16486,7 @@
     </row>
     <row r="1128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1128" s="3" t="s">
-        <v>2126</v>
+        <v>2125</v>
       </c>
       <c r="B1128" s="5" t="s">
         <v>7</v>
@@ -16467,7 +16494,7 @@
     </row>
     <row r="1129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1129" s="3" t="s">
-        <v>2131</v>
+        <v>2130</v>
       </c>
       <c r="B1129" s="5" t="s">
         <v>7</v>
@@ -16475,7 +16502,7 @@
     </row>
     <row r="1130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1130" s="3" t="s">
-        <v>2116</v>
+        <v>2115</v>
       </c>
       <c r="B1130" s="5" t="s">
         <v>20</v>
@@ -16483,7 +16510,7 @@
     </row>
     <row r="1131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1131" s="3" t="s">
-        <v>2132</v>
+        <v>2131</v>
       </c>
       <c r="B1131" s="5" t="s">
         <v>20</v>
@@ -16491,7 +16518,7 @@
     </row>
     <row r="1132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1132" s="3" t="s">
-        <v>2133</v>
+        <v>2132</v>
       </c>
       <c r="B1132" s="5" t="s">
         <v>20</v>
@@ -16499,7 +16526,7 @@
     </row>
     <row r="1133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1133" s="3" t="s">
-        <v>2134</v>
+        <v>2133</v>
       </c>
       <c r="B1133" s="5" t="s">
         <v>20</v>
@@ -16507,7 +16534,7 @@
     </row>
     <row r="1134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1134" s="3" t="s">
-        <v>2135</v>
+        <v>2134</v>
       </c>
       <c r="B1134" s="5" t="s">
         <v>20</v>
@@ -16515,7 +16542,7 @@
     </row>
     <row r="1135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1135" s="3" t="s">
-        <v>2136</v>
+        <v>2135</v>
       </c>
       <c r="B1135" s="5" t="s">
         <v>20</v>
@@ -16523,7 +16550,7 @@
     </row>
     <row r="1136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1136" s="3" t="s">
-        <v>2137</v>
+        <v>2136</v>
       </c>
       <c r="B1136" s="5" t="s">
         <v>20</v>
@@ -16531,7 +16558,7 @@
     </row>
     <row r="1137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1137" s="3" t="s">
-        <v>2138</v>
+        <v>2137</v>
       </c>
       <c r="B1137" s="5" t="s">
         <v>20</v>
@@ -16539,7 +16566,7 @@
     </row>
     <row r="1138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1138" s="3" t="s">
-        <v>2139</v>
+        <v>2138</v>
       </c>
       <c r="B1138" s="5" t="s">
         <v>20</v>
@@ -16547,7 +16574,7 @@
     </row>
     <row r="1139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1139" s="3" t="s">
-        <v>2140</v>
+        <v>2139</v>
       </c>
       <c r="B1139" s="5" t="s">
         <v>7</v>
@@ -16555,7 +16582,7 @@
     </row>
     <row r="1140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1140" s="3" t="s">
-        <v>2143</v>
+        <v>2142</v>
       </c>
       <c r="B1140" s="5" t="s">
         <v>7</v>
@@ -16563,7 +16590,7 @@
     </row>
     <row r="1141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1141" s="3" t="s">
-        <v>2146</v>
+        <v>2145</v>
       </c>
       <c r="B1141" s="5" t="s">
         <v>7</v>
@@ -16571,7 +16598,7 @@
     </row>
     <row r="1142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1142" s="3" t="s">
-        <v>2148</v>
+        <v>2147</v>
       </c>
       <c r="B1142" s="5" t="s">
         <v>7</v>
@@ -16579,7 +16606,7 @@
     </row>
     <row r="1143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1143" s="3" t="s">
-        <v>2150</v>
+        <v>2149</v>
       </c>
       <c r="B1143" s="5" t="s">
         <v>7</v>
@@ -16587,7 +16614,7 @@
     </row>
     <row r="1144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1144" s="3" t="s">
-        <v>2152</v>
+        <v>2151</v>
       </c>
       <c r="B1144" s="5" t="s">
         <v>7</v>
@@ -16595,7 +16622,7 @@
     </row>
     <row r="1145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1145" s="3" t="s">
-        <v>2154</v>
+        <v>2153</v>
       </c>
       <c r="B1145" s="5" t="s">
         <v>7</v>
@@ -16603,7 +16630,7 @@
     </row>
     <row r="1146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1146" s="3" t="s">
-        <v>2155</v>
+        <v>2154</v>
       </c>
       <c r="B1146" s="5" t="s">
         <v>7</v>
@@ -16611,7 +16638,7 @@
     </row>
     <row r="1147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1147" s="3" t="s">
-        <v>2157</v>
+        <v>2156</v>
       </c>
       <c r="B1147" s="5" t="s">
         <v>7</v>
@@ -16619,7 +16646,7 @@
     </row>
     <row r="1148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1148" s="3" t="s">
-        <v>2159</v>
+        <v>2158</v>
       </c>
       <c r="B1148" s="5" t="s">
         <v>7</v>
@@ -16627,7 +16654,7 @@
     </row>
     <row r="1149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1149" s="3" t="s">
-        <v>2160</v>
+        <v>2159</v>
       </c>
       <c r="B1149" s="5" t="s">
         <v>7</v>
@@ -16635,7 +16662,7 @@
     </row>
     <row r="1150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1150" s="3" t="s">
-        <v>2161</v>
+        <v>2160</v>
       </c>
       <c r="B1150" s="5" t="s">
         <v>7</v>
@@ -16643,7 +16670,7 @@
     </row>
     <row r="1151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1151" s="3" t="s">
-        <v>2162</v>
+        <v>2161</v>
       </c>
       <c r="B1151" s="5" t="s">
         <v>7</v>
@@ -16651,7 +16678,7 @@
     </row>
     <row r="1152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1152" s="3" t="s">
-        <v>2165</v>
+        <v>2164</v>
       </c>
       <c r="B1152" s="5" t="s">
         <v>20</v>
@@ -16659,7 +16686,7 @@
     </row>
     <row r="1153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1153" s="3" t="s">
-        <v>2171</v>
+        <v>2170</v>
       </c>
       <c r="B1153" s="5" t="s">
         <v>20</v>
@@ -16667,7 +16694,7 @@
     </row>
     <row r="1154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1154" s="3" t="s">
-        <v>2172</v>
+        <v>2171</v>
       </c>
       <c r="B1154" s="5" t="s">
         <v>20</v>
@@ -16675,7 +16702,7 @@
     </row>
     <row r="1155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1155" s="3" t="s">
-        <v>2173</v>
+        <v>2172</v>
       </c>
       <c r="B1155" s="5" t="s">
         <v>20</v>
@@ -16683,7 +16710,7 @@
     </row>
     <row r="1156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1156" s="3" t="s">
-        <v>2174</v>
+        <v>2173</v>
       </c>
       <c r="B1156" s="5" t="s">
         <v>20</v>
@@ -16691,7 +16718,7 @@
     </row>
     <row r="1157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1157" s="3" t="s">
-        <v>2175</v>
+        <v>2174</v>
       </c>
       <c r="B1157" s="5" t="s">
         <v>20</v>
@@ -16699,7 +16726,7 @@
     </row>
     <row r="1158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1158" t="s">
-        <v>2176</v>
+        <v>2175</v>
       </c>
       <c r="B1158" s="5" t="s">
         <v>7</v>
@@ -16707,7 +16734,7 @@
     </row>
     <row r="1159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1159" s="3" t="s">
-        <v>2178</v>
+        <v>2177</v>
       </c>
       <c r="B1159" s="5" t="s">
         <v>7</v>
@@ -16715,7 +16742,7 @@
     </row>
     <row r="1160" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1160" s="3" t="s">
-        <v>2181</v>
+        <v>2180</v>
       </c>
       <c r="B1160" s="5" t="s">
         <v>7</v>
@@ -16723,7 +16750,7 @@
     </row>
     <row r="1161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1161" s="3" t="s">
-        <v>2184</v>
+        <v>2183</v>
       </c>
       <c r="B1161" s="5" t="s">
         <v>7</v>
@@ -16731,7 +16758,7 @@
     </row>
     <row r="1162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1162" s="3" t="s">
-        <v>2186</v>
+        <v>2185</v>
       </c>
       <c r="B1162" s="5" t="s">
         <v>7</v>
@@ -16739,7 +16766,7 @@
     </row>
     <row r="1163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1163" s="3" t="s">
-        <v>2187</v>
+        <v>2186</v>
       </c>
       <c r="B1163" s="5" t="s">
         <v>7</v>
@@ -16747,7 +16774,7 @@
     </row>
     <row r="1164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1164" s="3" t="s">
-        <v>2188</v>
+        <v>2187</v>
       </c>
       <c r="B1164" s="5" t="s">
         <v>7</v>
@@ -16755,7 +16782,7 @@
     </row>
     <row r="1165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1165" s="3" t="s">
-        <v>2189</v>
+        <v>2188</v>
       </c>
       <c r="B1165" s="5" t="s">
         <v>7</v>
@@ -16763,7 +16790,7 @@
     </row>
     <row r="1166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1166" s="3" t="s">
-        <v>2190</v>
+        <v>2189</v>
       </c>
       <c r="B1166" s="5" t="s">
         <v>7</v>
@@ -16771,7 +16798,7 @@
     </row>
     <row r="1167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1167" s="3" t="s">
-        <v>2191</v>
+        <v>2190</v>
       </c>
       <c r="B1167" s="5" t="s">
         <v>7</v>
@@ -16779,7 +16806,7 @@
     </row>
     <row r="1168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1168" s="3" t="s">
-        <v>2194</v>
+        <v>2193</v>
       </c>
       <c r="B1168" s="5" t="s">
         <v>7</v>
@@ -16787,7 +16814,7 @@
     </row>
     <row r="1169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1169" s="3" t="s">
-        <v>2195</v>
+        <v>2194</v>
       </c>
       <c r="B1169" s="5" t="s">
         <v>7</v>
@@ -16795,7 +16822,7 @@
     </row>
     <row r="1170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1170" s="3" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="B1170" s="5" t="s">
         <v>7</v>
@@ -16803,7 +16830,7 @@
     </row>
     <row r="1171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1171" s="3" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="B1171" s="5" t="s">
         <v>20</v>
@@ -16811,7 +16838,7 @@
     </row>
     <row r="1172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1172" s="3" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="B1172" s="5" t="s">
         <v>20</v>
@@ -16819,7 +16846,7 @@
     </row>
     <row r="1173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1173" s="3" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="B1173" s="5" t="s">
         <v>20</v>
@@ -16827,7 +16854,7 @@
     </row>
     <row r="1174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1174" s="3" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="B1174" s="5" t="s">
         <v>20</v>
@@ -16835,7 +16862,7 @@
     </row>
     <row r="1175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1175" s="3" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="B1175" s="5" t="s">
         <v>20</v>
@@ -16843,7 +16870,7 @@
     </row>
     <row r="1176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1176" s="3" t="s">
-        <v>2202</v>
+        <v>2201</v>
       </c>
       <c r="B1176" s="5" t="s">
         <v>20</v>
@@ -16851,7 +16878,7 @@
     </row>
     <row r="1177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1177" s="3" t="s">
-        <v>2208</v>
+        <v>2207</v>
       </c>
       <c r="B1177" s="5" t="s">
         <v>20</v>
@@ -16859,7 +16886,7 @@
     </row>
     <row r="1178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1178" s="3" t="s">
-        <v>2207</v>
+        <v>2206</v>
       </c>
       <c r="B1178" s="5" t="s">
         <v>20</v>
@@ -16867,7 +16894,7 @@
     </row>
     <row r="1179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1179" s="3" t="s">
-        <v>2209</v>
+        <v>2208</v>
       </c>
       <c r="B1179" s="5" t="s">
         <v>20</v>
@@ -16875,7 +16902,7 @@
     </row>
     <row r="1180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1180" s="3" t="s">
-        <v>2216</v>
+        <v>2215</v>
       </c>
       <c r="B1180" s="5" t="s">
         <v>7</v>
@@ -16883,7 +16910,7 @@
     </row>
     <row r="1181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1181" s="3" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="B1181" s="5" t="s">
         <v>7</v>
@@ -16891,7 +16918,7 @@
     </row>
     <row r="1182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1182" s="3" t="s">
-        <v>2220</v>
+        <v>2219</v>
       </c>
       <c r="B1182" s="5" t="s">
         <v>20</v>
@@ -16899,7 +16926,7 @@
     </row>
     <row r="1183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1183" s="3" t="s">
-        <v>2221</v>
+        <v>2220</v>
       </c>
       <c r="B1183" s="5" t="s">
         <v>20</v>
@@ -16907,7 +16934,7 @@
     </row>
     <row r="1184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1184" s="3" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="B1184" s="5" t="s">
         <v>20</v>
@@ -16915,7 +16942,7 @@
     </row>
     <row r="1185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1185" s="3" t="s">
-        <v>2223</v>
+        <v>2222</v>
       </c>
       <c r="B1185" s="5" t="s">
         <v>20</v>
@@ -16923,7 +16950,7 @@
     </row>
     <row r="1186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1186" s="3" t="s">
-        <v>2224</v>
+        <v>2223</v>
       </c>
       <c r="B1186" s="5" t="s">
         <v>20</v>
@@ -16931,7 +16958,7 @@
     </row>
     <row r="1187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1187" s="3" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="B1187" s="5" t="s">
         <v>20</v>
@@ -16939,7 +16966,7 @@
     </row>
     <row r="1188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1188" s="3" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="B1188" s="5" t="s">
         <v>7</v>
@@ -16947,7 +16974,7 @@
     </row>
     <row r="1189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1189" s="3" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="B1189" s="5" t="s">
         <v>7</v>
@@ -16955,7 +16982,7 @@
     </row>
     <row r="1190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1190" s="3" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="B1190" s="5" t="s">
         <v>20</v>
@@ -16963,7 +16990,7 @@
     </row>
     <row r="1191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1191" s="3" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="B1191" s="5" t="s">
         <v>20</v>
@@ -16971,7 +16998,7 @@
     </row>
     <row r="1192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1192" s="3" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="B1192" s="5" t="s">
         <v>20</v>
@@ -16979,7 +17006,7 @@
     </row>
     <row r="1193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1193" s="3" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="B1193" s="5" t="s">
         <v>20</v>
@@ -16987,7 +17014,7 @@
     </row>
     <row r="1194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1194" s="3" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="B1194" s="5" t="s">
         <v>20</v>
@@ -16995,7 +17022,7 @@
     </row>
     <row r="1195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1195" s="3" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="B1195" s="5" t="s">
         <v>20</v>
@@ -17003,7 +17030,7 @@
     </row>
     <row r="1196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1196" s="3" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="B1196" s="5" t="s">
         <v>7</v>
@@ -17011,7 +17038,7 @@
     </row>
     <row r="1197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1197" s="3" t="s">
-        <v>2242</v>
+        <v>2241</v>
       </c>
       <c r="B1197" s="5" t="s">
         <v>7</v>
@@ -17019,7 +17046,7 @@
     </row>
     <row r="1198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1198" s="3" t="s">
-        <v>2243</v>
+        <v>2242</v>
       </c>
       <c r="B1198" s="5" t="s">
         <v>7</v>
@@ -17027,7 +17054,7 @@
     </row>
     <row r="1199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1199" s="3" t="s">
-        <v>2244</v>
+        <v>2243</v>
       </c>
       <c r="B1199" s="5" t="s">
         <v>7</v>
@@ -17035,7 +17062,7 @@
     </row>
     <row r="1200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1200" s="3" t="s">
-        <v>2245</v>
+        <v>2244</v>
       </c>
       <c r="B1200" s="5" t="s">
         <v>7</v>
@@ -17043,7 +17070,7 @@
     </row>
     <row r="1201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1201" s="3" t="s">
-        <v>2248</v>
+        <v>2247</v>
       </c>
       <c r="B1201" s="5" t="s">
         <v>7</v>
@@ -17051,7 +17078,7 @@
     </row>
     <row r="1202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1202" s="3" t="s">
-        <v>2253</v>
+        <v>2252</v>
       </c>
       <c r="B1202" s="5" t="s">
         <v>7</v>
@@ -17059,7 +17086,7 @@
     </row>
     <row r="1203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1203" s="3" t="s">
-        <v>2254</v>
+        <v>2253</v>
       </c>
       <c r="B1203" s="5" t="s">
         <v>20</v>
@@ -17067,7 +17094,7 @@
     </row>
     <row r="1204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1204" s="3" t="s">
-        <v>2256</v>
+        <v>2255</v>
       </c>
       <c r="B1204" s="5" t="s">
         <v>7</v>
@@ -17075,7 +17102,7 @@
     </row>
     <row r="1205" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1205" s="3" t="s">
-        <v>2257</v>
+        <v>2256</v>
       </c>
       <c r="B1205" s="5" t="s">
         <v>7</v>
@@ -17083,7 +17110,7 @@
     </row>
     <row r="1206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1206" s="3" t="s">
-        <v>2258</v>
+        <v>2257</v>
       </c>
       <c r="B1206" s="5" t="s">
         <v>7</v>
@@ -17091,7 +17118,7 @@
     </row>
     <row r="1207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1207" s="3" t="s">
-        <v>2260</v>
+        <v>2259</v>
       </c>
       <c r="B1207" s="5" t="s">
         <v>7</v>
@@ -17099,7 +17126,7 @@
     </row>
     <row r="1208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1208" s="3" t="s">
-        <v>2263</v>
+        <v>2262</v>
       </c>
       <c r="B1208" s="5" t="s">
         <v>7</v>
@@ -17107,7 +17134,7 @@
     </row>
     <row r="1209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1209" s="3" t="s">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B1209" s="5" t="s">
         <v>7</v>
@@ -17115,7 +17142,7 @@
     </row>
     <row r="1210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1210" s="3" t="s">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B1210" s="5" t="s">
         <v>7</v>
@@ -17123,7 +17150,7 @@
     </row>
     <row r="1211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1211" s="3" t="s">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="B1211" s="5" t="s">
         <v>7</v>
@@ -17131,7 +17158,7 @@
     </row>
     <row r="1212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1212" s="3" t="s">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="B1212" s="5" t="s">
         <v>7</v>
@@ -17139,7 +17166,7 @@
     </row>
     <row r="1213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1213" s="3" t="s">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="B1213" s="5" t="s">
         <v>7</v>
@@ -17147,7 +17174,7 @@
     </row>
     <row r="1214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1214" s="3" t="s">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="B1214" s="5" t="s">
         <v>7</v>
@@ -17155,7 +17182,7 @@
     </row>
     <row r="1215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1215" s="3" t="s">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="B1215" s="5" t="s">
         <v>7</v>
@@ -17163,7 +17190,7 @@
     </row>
     <row r="1216" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1216" s="3" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="B1216" s="5" t="s">
         <v>7</v>
@@ -17171,7 +17198,7 @@
     </row>
     <row r="1217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1217" s="3" t="s">
-        <v>2283</v>
+        <v>2282</v>
       </c>
       <c r="B1217" s="5" t="s">
         <v>20</v>
@@ -17179,7 +17206,7 @@
     </row>
     <row r="1218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1218" s="3" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="B1218" s="5" t="s">
         <v>7</v>
@@ -17187,7 +17214,7 @@
     </row>
     <row r="1219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1219" s="3" t="s">
-        <v>2287</v>
+        <v>2286</v>
       </c>
       <c r="B1219" s="5" t="s">
         <v>7</v>
@@ -17195,7 +17222,7 @@
     </row>
     <row r="1220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1220" s="3" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="B1220" s="5" t="s">
         <v>20</v>
@@ -17203,7 +17230,7 @@
     </row>
     <row r="1221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1221" s="3" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="B1221" s="5" t="s">
         <v>20</v>
@@ -17211,7 +17238,7 @@
     </row>
     <row r="1222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1222" s="3" t="s">
-        <v>2292</v>
+        <v>2291</v>
       </c>
       <c r="B1222" s="5" t="s">
         <v>20</v>
@@ -17219,7 +17246,7 @@
     </row>
     <row r="1223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1223" s="3" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="B1223" s="5" t="s">
         <v>20</v>
@@ -17227,7 +17254,7 @@
     </row>
     <row r="1224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1224" s="3" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="B1224" s="5" t="s">
         <v>20</v>
@@ -17235,7 +17262,7 @@
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1225" s="3" t="s">
-        <v>2297</v>
+        <v>2296</v>
       </c>
       <c r="B1225" s="5" t="s">
         <v>20</v>
@@ -17243,7 +17270,7 @@
     </row>
     <row r="1226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1226" s="3" t="s">
-        <v>2300</v>
+        <v>2299</v>
       </c>
       <c r="B1226" s="5" t="s">
         <v>7</v>
@@ -17251,7 +17278,7 @@
     </row>
     <row r="1227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1227" s="3" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B1227" s="5" t="s">
         <v>20</v>
@@ -17259,7 +17286,7 @@
     </row>
     <row r="1228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1228" s="3" t="s">
-        <v>2304</v>
+        <v>2303</v>
       </c>
       <c r="B1228" s="5" t="s">
         <v>20</v>
@@ -17267,7 +17294,7 @@
     </row>
     <row r="1229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1229" s="3" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="B1229" s="5" t="s">
         <v>20</v>
@@ -17275,7 +17302,7 @@
     </row>
     <row r="1230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1230" s="3" t="s">
-        <v>2308</v>
+        <v>2307</v>
       </c>
       <c r="B1230" s="5" t="s">
         <v>20</v>
@@ -17283,7 +17310,7 @@
     </row>
     <row r="1231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1231" s="3" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B1231" s="5" t="s">
         <v>20</v>
@@ -17291,7 +17318,7 @@
     </row>
     <row r="1232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1232" s="3" t="s">
-        <v>2312</v>
+        <v>2311</v>
       </c>
       <c r="B1232" s="5" t="s">
         <v>20</v>
@@ -17299,7 +17326,7 @@
     </row>
     <row r="1233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1233" s="3" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="B1233" s="5" t="s">
         <v>7</v>
@@ -17307,7 +17334,7 @@
     </row>
     <row r="1234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1234" s="3" t="s">
-        <v>2317</v>
+        <v>2316</v>
       </c>
       <c r="B1234" s="5" t="s">
         <v>7</v>
@@ -17315,7 +17342,7 @@
     </row>
     <row r="1235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1235" s="3" t="s">
-        <v>2320</v>
+        <v>2319</v>
       </c>
       <c r="B1235" s="5" t="s">
         <v>7</v>
@@ -17323,7 +17350,7 @@
     </row>
     <row r="1236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1236" s="3" t="s">
-        <v>2323</v>
+        <v>2322</v>
       </c>
       <c r="B1236" s="5" t="s">
         <v>7</v>
@@ -17331,7 +17358,7 @@
     </row>
     <row r="1237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1237" s="3" t="s">
-        <v>2326</v>
+        <v>2325</v>
       </c>
       <c r="B1237" s="5" t="s">
         <v>7</v>
@@ -17339,10 +17366,42 @@
     </row>
     <row r="1238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1238" s="3" t="s">
-        <v>2329</v>
+        <v>2328</v>
       </c>
       <c r="B1238" s="5" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1239" s="3" t="s">
+        <v>2333</v>
+      </c>
+      <c r="B1239" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1240" s="3" t="s">
+        <v>2334</v>
+      </c>
+      <c r="B1240" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1241" s="3" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B1241" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1242" s="3" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1242" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17352,7 +17411,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1238"/>
+  <dimension ref="A1:D1242"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -18867,7 +18926,7 @@
         <v>68</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>7</v>
@@ -31096,14 +31155,14 @@
       </c>
     </row>
     <row r="982" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A982" s="5">
-        <v>100914</v>
+      <c r="A982" s="5" t="s">
+        <v>2331</v>
       </c>
       <c r="B982" s="5" t="s">
-        <v>5</v>
+        <v>68</v>
       </c>
       <c r="C982" s="3" t="s">
-        <v>1862</v>
+        <v>2332</v>
       </c>
       <c r="D982" s="2" t="s">
         <v>7</v>
@@ -31111,13 +31170,13 @@
     </row>
     <row r="983" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A983" s="5" t="s">
+        <v>1863</v>
+      </c>
+      <c r="B983" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C983" s="3" t="s">
         <v>1864</v>
-      </c>
-      <c r="B983" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C983" s="3" t="s">
-        <v>1865</v>
       </c>
       <c r="D983" s="2" t="s">
         <v>7</v>
@@ -31125,13 +31184,13 @@
     </row>
     <row r="984" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A984" s="5" t="s">
+        <v>1865</v>
+      </c>
+      <c r="B984" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C984" s="3" t="s">
         <v>1866</v>
-      </c>
-      <c r="B984" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C984" s="3" t="s">
-        <v>1867</v>
       </c>
       <c r="D984" s="2" t="s">
         <v>7</v>
@@ -31139,13 +31198,13 @@
     </row>
     <row r="985" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A985" s="5" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B985" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C985" s="3" t="s">
         <v>1870</v>
-      </c>
-      <c r="B985" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C985" s="3" t="s">
-        <v>1871</v>
       </c>
       <c r="D985" s="2" t="s">
         <v>7</v>
@@ -31153,13 +31212,13 @@
     </row>
     <row r="986" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A986" s="5" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B986" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C986" s="3" t="s">
         <v>1878</v>
-      </c>
-      <c r="B986" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C986" s="3" t="s">
-        <v>1879</v>
       </c>
       <c r="D986" s="2" t="s">
         <v>7</v>
@@ -31167,13 +31226,13 @@
     </row>
     <row r="987" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A987" s="5" t="s">
+        <v>1879</v>
+      </c>
+      <c r="B987" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C987" s="3" t="s">
         <v>1880</v>
-      </c>
-      <c r="B987" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C987" s="3" t="s">
-        <v>1881</v>
       </c>
       <c r="D987" s="2" t="s">
         <v>7</v>
@@ -31181,13 +31240,13 @@
     </row>
     <row r="988" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A988" s="5" t="s">
+        <v>1881</v>
+      </c>
+      <c r="B988" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C988" s="3" t="s">
         <v>1882</v>
-      </c>
-      <c r="B988" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C988" s="3" t="s">
-        <v>1883</v>
       </c>
       <c r="D988" s="2" t="s">
         <v>7</v>
@@ -31195,13 +31254,13 @@
     </row>
     <row r="989" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A989" s="5" t="s">
+        <v>1883</v>
+      </c>
+      <c r="B989" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C989" s="3" t="s">
         <v>1884</v>
-      </c>
-      <c r="B989" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C989" s="3" t="s">
-        <v>1885</v>
       </c>
       <c r="D989" s="2" t="s">
         <v>7</v>
@@ -31209,13 +31268,13 @@
     </row>
     <row r="990" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A990" s="5" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B990" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C990" s="3" t="s">
         <v>1886</v>
-      </c>
-      <c r="B990" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C990" s="3" t="s">
-        <v>1887</v>
       </c>
       <c r="D990" s="2" t="s">
         <v>7</v>
@@ -31223,13 +31282,13 @@
     </row>
     <row r="991" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A991" s="5" t="s">
+        <v>1887</v>
+      </c>
+      <c r="B991" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C991" s="3" t="s">
         <v>1888</v>
-      </c>
-      <c r="B991" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C991" s="3" t="s">
-        <v>1889</v>
       </c>
       <c r="D991" s="2" t="s">
         <v>7</v>
@@ -31257,7 +31316,7 @@
         <v>5</v>
       </c>
       <c r="C993" s="3" t="s">
-        <v>1893</v>
+        <v>1892</v>
       </c>
       <c r="D993" s="2" t="s">
         <v>20</v>
@@ -31369,7 +31428,7 @@
         <v>5</v>
       </c>
       <c r="C1001" s="3" t="s">
-        <v>1901</v>
+        <v>1900</v>
       </c>
       <c r="D1001" s="2" t="s">
         <v>7</v>
@@ -31383,7 +31442,7 @@
         <v>5</v>
       </c>
       <c r="C1002" s="3" t="s">
-        <v>1904</v>
+        <v>1903</v>
       </c>
       <c r="D1002" s="2" t="s">
         <v>7</v>
@@ -31391,13 +31450,13 @@
     </row>
     <row r="1003" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1003" s="5" t="s">
+        <v>1905</v>
+      </c>
+      <c r="B1003" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1003" s="3" t="s">
         <v>1906</v>
-      </c>
-      <c r="B1003" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1003" s="3" t="s">
-        <v>1907</v>
       </c>
       <c r="D1003" s="2" t="s">
         <v>7</v>
@@ -31419,13 +31478,13 @@
     </row>
     <row r="1005" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1005" s="5" t="s">
+        <v>1908</v>
+      </c>
+      <c r="B1005" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1005" s="3" t="s">
         <v>1909</v>
-      </c>
-      <c r="B1005" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1005" s="3" t="s">
-        <v>1910</v>
       </c>
       <c r="D1005" s="2" t="s">
         <v>7</v>
@@ -31439,7 +31498,7 @@
         <v>5</v>
       </c>
       <c r="C1006" s="3" t="s">
-        <v>1912</v>
+        <v>1911</v>
       </c>
       <c r="D1006" s="2" t="s">
         <v>7</v>
@@ -31467,7 +31526,7 @@
         <v>5</v>
       </c>
       <c r="C1008" s="3" t="s">
-        <v>1916</v>
+        <v>1915</v>
       </c>
       <c r="D1008" s="2" t="s">
         <v>7</v>
@@ -31481,7 +31540,7 @@
         <v>5</v>
       </c>
       <c r="C1009" s="3" t="s">
-        <v>1919</v>
+        <v>1918</v>
       </c>
       <c r="D1009" s="2" t="s">
         <v>7</v>
@@ -31495,7 +31554,7 @@
         <v>5</v>
       </c>
       <c r="C1010" s="3" t="s">
-        <v>1920</v>
+        <v>1919</v>
       </c>
       <c r="D1010" s="2" t="s">
         <v>7</v>
@@ -31503,7 +31562,7 @@
     </row>
     <row r="1011" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1011" s="5" t="s">
-        <v>1922</v>
+        <v>1921</v>
       </c>
       <c r="B1011" s="5" t="s">
         <v>68</v>
@@ -31531,13 +31590,13 @@
     </row>
     <row r="1013" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1013" s="5" t="s">
+        <v>1923</v>
+      </c>
+      <c r="B1013" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1013" s="3" t="s">
         <v>1924</v>
-      </c>
-      <c r="B1013" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1013" s="3" t="s">
-        <v>1925</v>
       </c>
       <c r="D1013" s="2" t="s">
         <v>7</v>
@@ -31573,13 +31632,13 @@
     </row>
     <row r="1016" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1016" s="5" t="s">
+        <v>1928</v>
+      </c>
+      <c r="B1016" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1016" s="3" t="s">
         <v>1929</v>
-      </c>
-      <c r="B1016" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1016" s="3" t="s">
-        <v>1930</v>
       </c>
       <c r="D1016" s="2" t="s">
         <v>7</v>
@@ -31657,13 +31716,13 @@
     </row>
     <row r="1022" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1022" s="5" t="s">
+        <v>1937</v>
+      </c>
+      <c r="B1022" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1022" s="3" t="s">
         <v>1938</v>
-      </c>
-      <c r="B1022" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1022" s="3" t="s">
-        <v>1939</v>
       </c>
       <c r="D1022" s="2" t="s">
         <v>20</v>
@@ -31671,13 +31730,13 @@
     </row>
     <row r="1023" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1023" s="5" t="s">
+        <v>1940</v>
+      </c>
+      <c r="B1023" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1023" s="3" t="s">
         <v>1941</v>
-      </c>
-      <c r="B1023" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1023" s="3" t="s">
-        <v>1942</v>
       </c>
       <c r="D1023" s="2" t="s">
         <v>20</v>
@@ -31685,13 +31744,13 @@
     </row>
     <row r="1024" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1024" s="5" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1024" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1024" s="3" t="s">
         <v>1944</v>
-      </c>
-      <c r="B1024" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1024" s="3" t="s">
-        <v>1945</v>
       </c>
       <c r="D1024" s="2" t="s">
         <v>7</v>
@@ -31699,13 +31758,13 @@
     </row>
     <row r="1025" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1025" s="5" t="s">
+        <v>1946</v>
+      </c>
+      <c r="B1025" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1025" s="3" t="s">
         <v>1947</v>
-      </c>
-      <c r="B1025" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1025" s="3" t="s">
-        <v>1948</v>
       </c>
       <c r="D1025" s="2" t="s">
         <v>7</v>
@@ -31713,13 +31772,13 @@
     </row>
     <row r="1026" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1026" s="5" t="s">
+        <v>1952</v>
+      </c>
+      <c r="B1026" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1026" s="3" t="s">
         <v>1953</v>
-      </c>
-      <c r="B1026" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1026" s="3" t="s">
-        <v>1954</v>
       </c>
       <c r="D1026" s="2" t="s">
         <v>7</v>
@@ -31727,13 +31786,13 @@
     </row>
     <row r="1027" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1027" s="5" t="s">
+        <v>1950</v>
+      </c>
+      <c r="B1027" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1027" s="3" t="s">
         <v>1951</v>
-      </c>
-      <c r="B1027" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1027" s="3" t="s">
-        <v>1952</v>
       </c>
       <c r="D1027" s="2" t="s">
         <v>7</v>
@@ -32427,7 +32486,7 @@
     </row>
     <row r="1077" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1077" s="5" t="s">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="B1077" s="5" t="s">
         <v>68</v>
@@ -32441,7 +32500,7 @@
     </row>
     <row r="1078" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1078" s="5" t="s">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="B1078" s="5" t="s">
         <v>68</v>
@@ -32461,7 +32520,7 @@
         <v>5</v>
       </c>
       <c r="C1079" s="3" t="s">
-        <v>2009</v>
+        <v>2008</v>
       </c>
       <c r="D1079" s="2" t="s">
         <v>7</v>
@@ -32469,13 +32528,13 @@
     </row>
     <row r="1080" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1080" s="5" t="s">
+        <v>2010</v>
+      </c>
+      <c r="B1080" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1080" s="3" t="s">
         <v>2011</v>
-      </c>
-      <c r="B1080" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1080" s="3" t="s">
-        <v>2012</v>
       </c>
       <c r="D1080" s="2" t="s">
         <v>7</v>
@@ -32483,7 +32542,7 @@
     </row>
     <row r="1081" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1081" s="5" t="s">
-        <v>2014</v>
+        <v>2013</v>
       </c>
       <c r="B1081" s="5" t="s">
         <v>68</v>
@@ -32497,7 +32556,7 @@
     </row>
     <row r="1082" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1082" s="5" t="s">
-        <v>2016</v>
+        <v>2015</v>
       </c>
       <c r="B1082" s="5" t="s">
         <v>68</v>
@@ -32511,13 +32570,13 @@
     </row>
     <row r="1083" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1083" s="5" t="s">
+        <v>2017</v>
+      </c>
+      <c r="B1083" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1083" s="3" t="s">
         <v>2018</v>
-      </c>
-      <c r="B1083" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1083" s="3" t="s">
-        <v>2019</v>
       </c>
       <c r="D1083" s="2" t="s">
         <v>7</v>
@@ -32539,13 +32598,13 @@
     </row>
     <row r="1085" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1085" s="5" t="s">
+        <v>2021</v>
+      </c>
+      <c r="B1085" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1085" s="3" t="s">
         <v>2022</v>
-      </c>
-      <c r="B1085" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1085" s="3" t="s">
-        <v>2023</v>
       </c>
       <c r="D1085" s="2" t="s">
         <v>7</v>
@@ -32553,13 +32612,13 @@
     </row>
     <row r="1086" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1086" s="5" t="s">
+        <v>2024</v>
+      </c>
+      <c r="B1086" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1086" s="3" t="s">
         <v>2025</v>
-      </c>
-      <c r="B1086" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1086" s="3" t="s">
-        <v>2026</v>
       </c>
       <c r="D1086" s="2" t="s">
         <v>7</v>
@@ -32567,13 +32626,13 @@
     </row>
     <row r="1087" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1087" s="5" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B1087" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1087" s="3" t="s">
         <v>2028</v>
-      </c>
-      <c r="B1087" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1087" s="3" t="s">
-        <v>2029</v>
       </c>
       <c r="D1087" s="2" t="s">
         <v>7</v>
@@ -32581,13 +32640,13 @@
     </row>
     <row r="1088" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1088" s="5" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B1088" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1088" s="3" t="s">
         <v>2031</v>
-      </c>
-      <c r="B1088" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1088" s="3" t="s">
-        <v>2032</v>
       </c>
       <c r="D1088" s="2" t="s">
         <v>7</v>
@@ -32595,13 +32654,13 @@
     </row>
     <row r="1089" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1089" s="5" t="s">
+        <v>2032</v>
+      </c>
+      <c r="B1089" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1089" s="3" t="s">
         <v>2033</v>
-      </c>
-      <c r="B1089" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1089" s="3" t="s">
-        <v>2034</v>
       </c>
       <c r="D1089" s="2" t="s">
         <v>7</v>
@@ -32609,13 +32668,13 @@
     </row>
     <row r="1090" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1090" s="5" t="s">
+        <v>2036</v>
+      </c>
+      <c r="B1090" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1090" s="3" t="s">
         <v>2037</v>
-      </c>
-      <c r="B1090" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1090" s="3" t="s">
-        <v>2038</v>
       </c>
       <c r="D1090" s="2" t="s">
         <v>7</v>
@@ -32623,13 +32682,13 @@
     </row>
     <row r="1091" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1091" s="5" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B1091" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1091" s="3" t="s">
         <v>2039</v>
-      </c>
-      <c r="B1091" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1091" s="3" t="s">
-        <v>2040</v>
       </c>
       <c r="D1091" s="2" t="s">
         <v>7</v>
@@ -32637,13 +32696,13 @@
     </row>
     <row r="1092" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1092" s="5" t="s">
+        <v>2042</v>
+      </c>
+      <c r="B1092" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1092" s="3" t="s">
         <v>2043</v>
-      </c>
-      <c r="B1092" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1092" s="3" t="s">
-        <v>2044</v>
       </c>
       <c r="D1092" s="2" t="s">
         <v>7</v>
@@ -32651,13 +32710,13 @@
     </row>
     <row r="1093" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1093" s="5" t="s">
+        <v>2045</v>
+      </c>
+      <c r="B1093" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1093" s="3" t="s">
         <v>2046</v>
-      </c>
-      <c r="B1093" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1093" s="3" t="s">
-        <v>2047</v>
       </c>
       <c r="D1093" s="2" t="s">
         <v>7</v>
@@ -32665,13 +32724,13 @@
     </row>
     <row r="1094" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1094" s="5" t="s">
+        <v>2048</v>
+      </c>
+      <c r="B1094" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1094" s="3" t="s">
         <v>2049</v>
-      </c>
-      <c r="B1094" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1094" s="3" t="s">
-        <v>2050</v>
       </c>
       <c r="D1094" s="2" t="s">
         <v>7</v>
@@ -32707,13 +32766,13 @@
     </row>
     <row r="1097" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1097" s="5" t="s">
-        <v>2053</v>
+        <v>2052</v>
       </c>
       <c r="B1097" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C1097" s="3" t="s">
-        <v>2055</v>
+        <v>2054</v>
       </c>
       <c r="D1097" s="2" t="s">
         <v>7</v>
@@ -32721,13 +32780,13 @@
     </row>
     <row r="1098" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1098" s="5" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B1098" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1098" s="3" t="s">
         <v>2057</v>
-      </c>
-      <c r="B1098" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1098" s="3" t="s">
-        <v>2058</v>
       </c>
       <c r="D1098" s="2" t="s">
         <v>7</v>
@@ -32735,13 +32794,13 @@
     </row>
     <row r="1099" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1099" s="5" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1099" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1099" s="3" t="s">
         <v>2060</v>
-      </c>
-      <c r="B1099" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1099" s="3" t="s">
-        <v>2061</v>
       </c>
       <c r="D1099" s="2" t="s">
         <v>7</v>
@@ -32763,13 +32822,13 @@
     </row>
     <row r="1101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1101" s="5" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B1101" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1101" s="3" t="s">
         <v>2064</v>
-      </c>
-      <c r="B1101" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1101" s="3" t="s">
-        <v>2065</v>
       </c>
       <c r="D1101" s="2" t="s">
         <v>7</v>
@@ -32777,13 +32836,13 @@
     </row>
     <row r="1102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1102" s="5" t="s">
-        <v>2068</v>
+        <v>2067</v>
       </c>
       <c r="B1102" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C1102" s="3" t="s">
-        <v>2067</v>
+        <v>2066</v>
       </c>
       <c r="D1102" s="2" t="s">
         <v>20</v>
@@ -32791,13 +32850,13 @@
     </row>
     <row r="1103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1103" s="5" t="s">
+        <v>2068</v>
+      </c>
+      <c r="B1103" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1103" s="3" t="s">
         <v>2069</v>
-      </c>
-      <c r="B1103" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1103" s="3" t="s">
-        <v>2070</v>
       </c>
       <c r="D1103" s="2" t="s">
         <v>20</v>
@@ -32805,13 +32864,13 @@
     </row>
     <row r="1104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1104" s="5" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B1104" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1104" s="3" t="s">
         <v>2072</v>
-      </c>
-      <c r="B1104" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1104" s="3" t="s">
-        <v>2073</v>
       </c>
       <c r="D1104" s="2" t="s">
         <v>20</v>
@@ -32819,13 +32878,13 @@
     </row>
     <row r="1105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1105" s="5" t="s">
+        <v>2075</v>
+      </c>
+      <c r="B1105" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1105" s="3" t="s">
         <v>2076</v>
-      </c>
-      <c r="B1105" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1105" s="3" t="s">
-        <v>2077</v>
       </c>
       <c r="D1105" s="2" t="s">
         <v>7</v>
@@ -32833,13 +32892,13 @@
     </row>
     <row r="1106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1106" s="5" t="s">
+        <v>2077</v>
+      </c>
+      <c r="B1106" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1106" s="3" t="s">
         <v>2078</v>
-      </c>
-      <c r="B1106" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1106" s="3" t="s">
-        <v>2079</v>
       </c>
       <c r="D1106" s="2" t="s">
         <v>7</v>
@@ -32847,13 +32906,13 @@
     </row>
     <row r="1107" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1107" s="5" t="s">
+        <v>2081</v>
+      </c>
+      <c r="B1107" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1107" s="3" t="s">
         <v>2082</v>
-      </c>
-      <c r="B1107" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1107" s="3" t="s">
-        <v>2083</v>
       </c>
       <c r="D1107" s="2" t="s">
         <v>7</v>
@@ -32861,13 +32920,13 @@
     </row>
     <row r="1108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1108" s="5" t="s">
+        <v>2083</v>
+      </c>
+      <c r="B1108" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1108" s="3" t="s">
         <v>2084</v>
-      </c>
-      <c r="B1108" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1108" s="3" t="s">
-        <v>2085</v>
       </c>
       <c r="D1108" s="2" t="s">
         <v>7</v>
@@ -32875,13 +32934,13 @@
     </row>
     <row r="1109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1109" s="5" t="s">
+        <v>2087</v>
+      </c>
+      <c r="B1109" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1109" s="3" t="s">
         <v>2088</v>
-      </c>
-      <c r="B1109" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1109" s="3" t="s">
-        <v>2089</v>
       </c>
       <c r="D1109" s="2" t="s">
         <v>7</v>
@@ -32889,7 +32948,7 @@
     </row>
     <row r="1110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1110" s="5" t="s">
-        <v>2091</v>
+        <v>2090</v>
       </c>
       <c r="B1110" s="5" t="s">
         <v>68</v>
@@ -32903,13 +32962,13 @@
     </row>
     <row r="1111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1111" s="5" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1111" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1111" s="3" t="s">
         <v>2092</v>
-      </c>
-      <c r="B1111" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1111" s="3" t="s">
-        <v>2093</v>
       </c>
       <c r="D1111" s="2" t="s">
         <v>7</v>
@@ -32917,7 +32976,7 @@
     </row>
     <row r="1112" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1112" s="5" t="s">
-        <v>2096</v>
+        <v>2095</v>
       </c>
       <c r="B1112" s="5" t="s">
         <v>68</v>
@@ -32993,7 +33052,7 @@
         <v>5</v>
       </c>
       <c r="C1117" s="3" t="s">
-        <v>2102</v>
+        <v>2101</v>
       </c>
       <c r="D1117" s="2" t="s">
         <v>7</v>
@@ -33015,13 +33074,13 @@
     </row>
     <row r="1119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1119" s="5" t="s">
+        <v>2104</v>
+      </c>
+      <c r="B1119" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1119" s="3" t="s">
         <v>2105</v>
-      </c>
-      <c r="B1119" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1119" s="3" t="s">
-        <v>2106</v>
       </c>
       <c r="D1119" s="2" t="s">
         <v>7</v>
@@ -33035,7 +33094,7 @@
         <v>5</v>
       </c>
       <c r="C1120" s="3" t="s">
-        <v>2108</v>
+        <v>2107</v>
       </c>
       <c r="D1120" s="2" t="s">
         <v>20</v>
@@ -33049,10 +33108,10 @@
         <v>5</v>
       </c>
       <c r="C1121" s="3" t="s">
-        <v>2112</v>
+        <v>2111</v>
       </c>
       <c r="D1121" s="6" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1122" spans="1:4" x14ac:dyDescent="0.3">
@@ -33063,10 +33122,10 @@
         <v>5</v>
       </c>
       <c r="C1122" s="3" t="s">
-        <v>2113</v>
+        <v>2112</v>
       </c>
       <c r="D1122" s="6" t="s">
-        <v>2111</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="1123" spans="1:4" x14ac:dyDescent="0.3">
@@ -33085,13 +33144,13 @@
     </row>
     <row r="1124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1124" s="5" t="s">
+        <v>1943</v>
+      </c>
+      <c r="B1124" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1124" s="3" t="s">
         <v>1944</v>
-      </c>
-      <c r="B1124" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1124" s="3" t="s">
-        <v>1945</v>
       </c>
       <c r="D1124" s="2" t="s">
         <v>7</v>
@@ -33099,13 +33158,13 @@
     </row>
     <row r="1125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1125" s="5" t="s">
-        <v>2119</v>
+        <v>2118</v>
       </c>
       <c r="B1125" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C1125" s="3" t="s">
-        <v>2118</v>
+        <v>2117</v>
       </c>
       <c r="D1125" s="2" t="s">
         <v>20</v>
@@ -33113,13 +33172,13 @@
     </row>
     <row r="1126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1126" s="5" t="s">
+        <v>2120</v>
+      </c>
+      <c r="B1126" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1126" s="3" t="s">
         <v>2121</v>
-      </c>
-      <c r="B1126" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1126" s="3" t="s">
-        <v>2122</v>
       </c>
       <c r="D1126" s="2" t="s">
         <v>20</v>
@@ -33127,13 +33186,13 @@
     </row>
     <row r="1127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1127" s="5" t="s">
+        <v>2123</v>
+      </c>
+      <c r="B1127" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1127" s="3" t="s">
         <v>2124</v>
-      </c>
-      <c r="B1127" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1127" s="3" t="s">
-        <v>2125</v>
       </c>
       <c r="D1127" s="2" t="s">
         <v>7</v>
@@ -33141,13 +33200,13 @@
     </row>
     <row r="1128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1128" s="5" t="s">
+        <v>2126</v>
+      </c>
+      <c r="B1128" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1128" s="3" t="s">
         <v>2127</v>
-      </c>
-      <c r="B1128" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1128" s="3" t="s">
-        <v>2128</v>
       </c>
       <c r="D1128" s="2" t="s">
         <v>7</v>
@@ -33155,13 +33214,13 @@
     </row>
     <row r="1129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1129" s="5" t="s">
+        <v>2128</v>
+      </c>
+      <c r="B1129" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1129" s="3" t="s">
         <v>2129</v>
-      </c>
-      <c r="B1129" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1129" s="3" t="s">
-        <v>2130</v>
       </c>
       <c r="D1129" s="2" t="s">
         <v>7</v>
@@ -33295,13 +33354,13 @@
     </row>
     <row r="1139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1139" s="5" t="s">
+        <v>2140</v>
+      </c>
+      <c r="B1139" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1139" s="3" t="s">
         <v>2141</v>
-      </c>
-      <c r="B1139" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1139" s="3" t="s">
-        <v>2142</v>
       </c>
       <c r="D1139" s="2" t="s">
         <v>7</v>
@@ -33309,13 +33368,13 @@
     </row>
     <row r="1140" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1140" s="5" t="s">
+        <v>2143</v>
+      </c>
+      <c r="B1140" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1140" s="3" t="s">
         <v>2144</v>
-      </c>
-      <c r="B1140" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1140" s="3" t="s">
-        <v>2145</v>
       </c>
       <c r="D1140" s="2" t="s">
         <v>7</v>
@@ -33329,7 +33388,7 @@
         <v>5</v>
       </c>
       <c r="C1141" s="3" t="s">
-        <v>2147</v>
+        <v>2146</v>
       </c>
       <c r="D1141" s="2" t="s">
         <v>7</v>
@@ -33337,7 +33396,7 @@
     </row>
     <row r="1142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1142" s="5" t="s">
-        <v>2149</v>
+        <v>2148</v>
       </c>
       <c r="B1142" s="5" t="s">
         <v>68</v>
@@ -33351,7 +33410,7 @@
     </row>
     <row r="1143" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1143" s="5" t="s">
-        <v>2151</v>
+        <v>2150</v>
       </c>
       <c r="B1143" s="5" t="s">
         <v>68</v>
@@ -33365,7 +33424,7 @@
     </row>
     <row r="1144" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1144" s="5" t="s">
-        <v>2153</v>
+        <v>2152</v>
       </c>
       <c r="B1144" s="5" t="s">
         <v>68</v>
@@ -33393,7 +33452,7 @@
     </row>
     <row r="1146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1146" s="5" t="s">
-        <v>2156</v>
+        <v>2155</v>
       </c>
       <c r="B1146" s="5" t="s">
         <v>68</v>
@@ -33407,7 +33466,7 @@
     </row>
     <row r="1147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1147" s="5" t="s">
-        <v>2158</v>
+        <v>2157</v>
       </c>
       <c r="B1147" s="5" t="s">
         <v>68</v>
@@ -33435,13 +33494,13 @@
     </row>
     <row r="1149" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1149" s="5" t="s">
+        <v>2166</v>
+      </c>
+      <c r="B1149" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1149" s="3" t="s">
         <v>2167</v>
-      </c>
-      <c r="B1149" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1149" s="3" t="s">
-        <v>2168</v>
       </c>
       <c r="D1149" s="2" t="s">
         <v>7</v>
@@ -33449,13 +33508,13 @@
     </row>
     <row r="1150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1150" s="5" t="s">
+        <v>2168</v>
+      </c>
+      <c r="B1150" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1150" s="3" t="s">
         <v>2169</v>
-      </c>
-      <c r="B1150" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1150" s="3" t="s">
-        <v>2170</v>
       </c>
       <c r="D1150" s="2" t="s">
         <v>7</v>
@@ -33463,13 +33522,13 @@
     </row>
     <row r="1151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1151" s="5" t="s">
+        <v>2162</v>
+      </c>
+      <c r="B1151" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1151" s="3" t="s">
         <v>2163</v>
-      </c>
-      <c r="B1151" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1151" s="3" t="s">
-        <v>2164</v>
       </c>
       <c r="D1151" s="2" t="s">
         <v>7</v>
@@ -33477,7 +33536,7 @@
     </row>
     <row r="1152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1152" s="5" t="s">
-        <v>2166</v>
+        <v>2165</v>
       </c>
       <c r="B1152" s="5" t="s">
         <v>68</v>
@@ -33567,7 +33626,7 @@
         <v>5</v>
       </c>
       <c r="C1158" s="3" t="s">
-        <v>2177</v>
+        <v>2176</v>
       </c>
       <c r="D1158" s="2" t="s">
         <v>7</v>
@@ -33575,13 +33634,13 @@
     </row>
     <row r="1159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1159" s="5" t="s">
+        <v>2178</v>
+      </c>
+      <c r="B1159" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1159" s="3" t="s">
         <v>2179</v>
-      </c>
-      <c r="B1159" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1159" s="3" t="s">
-        <v>2180</v>
       </c>
       <c r="D1159" s="2" t="s">
         <v>7</v>
@@ -33589,13 +33648,13 @@
     </row>
     <row r="1160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1160" s="5" t="s">
-        <v>2183</v>
+        <v>2182</v>
       </c>
       <c r="B1160" s="5" t="s">
         <v>68</v>
       </c>
       <c r="C1160" s="3" t="s">
-        <v>2182</v>
+        <v>2181</v>
       </c>
       <c r="D1160" s="2" t="s">
         <v>7</v>
@@ -33603,7 +33662,7 @@
     </row>
     <row r="1161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1161" s="5" t="s">
-        <v>2185</v>
+        <v>2184</v>
       </c>
       <c r="B1161" s="5" t="s">
         <v>68</v>
@@ -33687,13 +33746,13 @@
     </row>
     <row r="1167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1167" s="5" t="s">
+        <v>2191</v>
+      </c>
+      <c r="B1167" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1167" s="3" t="s">
         <v>2192</v>
-      </c>
-      <c r="B1167" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1167" s="3" t="s">
-        <v>2193</v>
       </c>
       <c r="D1167" s="2" t="s">
         <v>7</v>
@@ -33813,13 +33872,13 @@
     </row>
     <row r="1176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1176" s="5" t="s">
+        <v>2202</v>
+      </c>
+      <c r="B1176" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1176" s="3" t="s">
         <v>2203</v>
-      </c>
-      <c r="B1176" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1176" s="3" t="s">
-        <v>2204</v>
       </c>
       <c r="D1176" s="2" t="s">
         <v>20</v>
@@ -33827,13 +33886,13 @@
     </row>
     <row r="1177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1177" s="5" t="s">
+        <v>2204</v>
+      </c>
+      <c r="B1177" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1177" s="3" t="s">
         <v>2205</v>
-      </c>
-      <c r="B1177" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1177" s="3" t="s">
-        <v>2206</v>
       </c>
       <c r="D1177" s="2" t="s">
         <v>20</v>
@@ -33841,13 +33900,13 @@
     </row>
     <row r="1178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1178" s="5" t="s">
+        <v>2209</v>
+      </c>
+      <c r="B1178" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1178" s="3" t="s">
         <v>2210</v>
-      </c>
-      <c r="B1178" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1178" s="3" t="s">
-        <v>2211</v>
       </c>
       <c r="D1178" s="2" t="s">
         <v>20</v>
@@ -33855,13 +33914,13 @@
     </row>
     <row r="1179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1179" s="5" t="s">
+        <v>2211</v>
+      </c>
+      <c r="B1179" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1179" s="3" t="s">
         <v>2212</v>
-      </c>
-      <c r="B1179" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1179" s="3" t="s">
-        <v>2213</v>
       </c>
       <c r="D1179" s="2" t="s">
         <v>20</v>
@@ -33869,13 +33928,13 @@
     </row>
     <row r="1180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1180" s="5" t="s">
+        <v>2213</v>
+      </c>
+      <c r="B1180" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1180" s="3" t="s">
         <v>2214</v>
-      </c>
-      <c r="B1180" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1180" s="3" t="s">
-        <v>2215</v>
       </c>
       <c r="D1180" s="2" t="s">
         <v>7</v>
@@ -33883,13 +33942,13 @@
     </row>
     <row r="1181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1181" s="5" t="s">
+        <v>2217</v>
+      </c>
+      <c r="B1181" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1181" s="3" t="s">
         <v>2218</v>
-      </c>
-      <c r="B1181" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1181" s="3" t="s">
-        <v>2219</v>
       </c>
       <c r="D1181" s="2" t="s">
         <v>7</v>
@@ -33981,13 +34040,13 @@
     </row>
     <row r="1188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1188" s="5" t="s">
+        <v>2226</v>
+      </c>
+      <c r="B1188" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1188" s="3" t="s">
         <v>2227</v>
-      </c>
-      <c r="B1188" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1188" s="3" t="s">
-        <v>2228</v>
       </c>
       <c r="D1188" s="2" t="s">
         <v>7</v>
@@ -33995,13 +34054,13 @@
     </row>
     <row r="1189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1189" s="5" t="s">
+        <v>2229</v>
+      </c>
+      <c r="B1189" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1189" s="3" t="s">
         <v>2230</v>
-      </c>
-      <c r="B1189" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1189" s="3" t="s">
-        <v>2231</v>
       </c>
       <c r="D1189" s="2" t="s">
         <v>7</v>
@@ -34015,7 +34074,7 @@
         <v>5</v>
       </c>
       <c r="C1190" s="3" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="D1190" s="2" t="s">
         <v>20</v>
@@ -34029,7 +34088,7 @@
         <v>5</v>
       </c>
       <c r="C1191" s="3" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="D1191" s="2" t="s">
         <v>20</v>
@@ -34043,7 +34102,7 @@
         <v>5</v>
       </c>
       <c r="C1192" s="3" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="D1192" s="2" t="s">
         <v>20</v>
@@ -34057,7 +34116,7 @@
         <v>5</v>
       </c>
       <c r="C1193" s="3" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="D1193" s="2" t="s">
         <v>20</v>
@@ -34093,13 +34152,13 @@
     </row>
     <row r="1196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1196" s="5" t="s">
+        <v>2239</v>
+      </c>
+      <c r="B1196" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1196" s="3" t="s">
         <v>2240</v>
-      </c>
-      <c r="B1196" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1196" s="3" t="s">
-        <v>2241</v>
       </c>
       <c r="D1196" s="2" t="s">
         <v>7</v>
@@ -34121,13 +34180,13 @@
     </row>
     <row r="1198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1198" s="5" t="s">
+        <v>2245</v>
+      </c>
+      <c r="B1198" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1198" s="3" t="s">
         <v>2246</v>
-      </c>
-      <c r="B1198" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1198" s="3" t="s">
-        <v>2247</v>
       </c>
       <c r="D1198" s="2" t="s">
         <v>7</v>
@@ -34163,13 +34222,13 @@
     </row>
     <row r="1201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1201" s="5" t="s">
+        <v>2248</v>
+      </c>
+      <c r="B1201" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1201" s="3" t="s">
         <v>2249</v>
-      </c>
-      <c r="B1201" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1201" s="3" t="s">
-        <v>2250</v>
       </c>
       <c r="D1201" s="2" t="s">
         <v>7</v>
@@ -34177,13 +34236,13 @@
     </row>
     <row r="1202" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1202" s="5" t="s">
+        <v>2250</v>
+      </c>
+      <c r="B1202" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1202" s="3" t="s">
         <v>2251</v>
-      </c>
-      <c r="B1202" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1202" s="3" t="s">
-        <v>2252</v>
       </c>
       <c r="D1202" s="2" t="s">
         <v>7</v>
@@ -34191,7 +34250,7 @@
     </row>
     <row r="1203" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1203" s="5" t="s">
-        <v>2255</v>
+        <v>2254</v>
       </c>
       <c r="B1203" s="5" t="s">
         <v>68</v>
@@ -34219,13 +34278,13 @@
     </row>
     <row r="1205" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1205" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B1205" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1205" s="3" t="s">
         <v>2270</v>
-      </c>
-      <c r="B1205" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1205" s="3" t="s">
-        <v>2271</v>
       </c>
       <c r="D1205" s="2" t="s">
         <v>7</v>
@@ -34233,7 +34292,7 @@
     </row>
     <row r="1206" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1206" s="5" t="s">
-        <v>2259</v>
+        <v>2258</v>
       </c>
       <c r="B1206" s="5" t="s">
         <v>68</v>
@@ -34247,13 +34306,13 @@
     </row>
     <row r="1207" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1207" s="5" t="s">
+        <v>2260</v>
+      </c>
+      <c r="B1207" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1207" s="3" t="s">
         <v>2261</v>
-      </c>
-      <c r="B1207" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1207" s="3" t="s">
-        <v>2262</v>
       </c>
       <c r="D1207" s="2" t="s">
         <v>7</v>
@@ -34261,13 +34320,13 @@
     </row>
     <row r="1208" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1208" s="5" t="s">
+        <v>2263</v>
+      </c>
+      <c r="B1208" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1208" s="3" t="s">
         <v>2264</v>
-      </c>
-      <c r="B1208" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1208" s="3" t="s">
-        <v>2265</v>
       </c>
       <c r="D1208" s="2" t="s">
         <v>7</v>
@@ -34275,7 +34334,7 @@
     </row>
     <row r="1209" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1209" s="1" t="s">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="B1209" s="1" t="s">
         <v>68</v>
@@ -34303,13 +34362,13 @@
     </row>
     <row r="1211" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1211" s="5" t="s">
+        <v>2269</v>
+      </c>
+      <c r="B1211" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1211" s="3" t="s">
         <v>2270</v>
-      </c>
-      <c r="B1211" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1211" s="3" t="s">
-        <v>2271</v>
       </c>
       <c r="D1211" s="2" t="s">
         <v>7</v>
@@ -34331,13 +34390,13 @@
     </row>
     <row r="1213" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1213" s="5" t="s">
+        <v>2273</v>
+      </c>
+      <c r="B1213" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1213" s="3" t="s">
         <v>2274</v>
-      </c>
-      <c r="B1213" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1213" s="3" t="s">
-        <v>2275</v>
       </c>
       <c r="D1213" s="2" t="s">
         <v>7</v>
@@ -34345,13 +34404,13 @@
     </row>
     <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1214" s="5" t="s">
+        <v>2276</v>
+      </c>
+      <c r="B1214" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1214" s="3" t="s">
         <v>2277</v>
-      </c>
-      <c r="B1214" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1214" s="3" t="s">
-        <v>2278</v>
       </c>
       <c r="D1214" s="2" t="s">
         <v>7</v>
@@ -34359,13 +34418,13 @@
     </row>
     <row r="1215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1215" s="5" t="s">
+        <v>2279</v>
+      </c>
+      <c r="B1215" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1215" s="3" t="s">
         <v>2280</v>
-      </c>
-      <c r="B1215" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1215" s="3" t="s">
-        <v>2281</v>
       </c>
       <c r="D1215" s="2" t="s">
         <v>7</v>
@@ -34401,13 +34460,13 @@
     </row>
     <row r="1218" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1218" s="5" t="s">
+        <v>2283</v>
+      </c>
+      <c r="B1218" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1218" s="3" t="s">
         <v>2284</v>
-      </c>
-      <c r="B1218" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1218" s="3" t="s">
-        <v>2285</v>
       </c>
       <c r="D1218" s="2" t="s">
         <v>7</v>
@@ -34415,13 +34474,13 @@
     </row>
     <row r="1219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1219" s="5" t="s">
+        <v>2287</v>
+      </c>
+      <c r="B1219" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1219" s="3" t="s">
         <v>2288</v>
-      </c>
-      <c r="B1219" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1219" s="3" t="s">
-        <v>2289</v>
       </c>
       <c r="D1219" s="2" t="s">
         <v>7</v>
@@ -34429,13 +34488,13 @@
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1220" s="5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1220" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1220" s="3" t="s">
         <v>2293</v>
-      </c>
-      <c r="B1220" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1220" s="3" t="s">
-        <v>2294</v>
       </c>
       <c r="D1220" s="2" t="s">
         <v>20</v>
@@ -34443,13 +34502,13 @@
     </row>
     <row r="1221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1221" s="5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1221" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1221" s="3" t="s">
         <v>2293</v>
-      </c>
-      <c r="B1221" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1221" s="3" t="s">
-        <v>2294</v>
       </c>
       <c r="D1221" s="2" t="s">
         <v>20</v>
@@ -34457,13 +34516,13 @@
     </row>
     <row r="1222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1222" s="5" t="s">
+        <v>2292</v>
+      </c>
+      <c r="B1222" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1222" s="3" t="s">
         <v>2293</v>
-      </c>
-      <c r="B1222" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1222" s="3" t="s">
-        <v>2294</v>
       </c>
       <c r="D1222" s="2" t="s">
         <v>20</v>
@@ -34471,13 +34530,13 @@
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1223" s="5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B1223" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1223" s="3" t="s">
         <v>2298</v>
-      </c>
-      <c r="B1223" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1223" s="3" t="s">
-        <v>2299</v>
       </c>
       <c r="D1223" s="2" t="s">
         <v>20</v>
@@ -34485,13 +34544,13 @@
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1224" s="5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B1224" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1224" s="3" t="s">
         <v>2298</v>
-      </c>
-      <c r="B1224" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1224" s="3" t="s">
-        <v>2299</v>
       </c>
       <c r="D1224" s="2" t="s">
         <v>20</v>
@@ -34499,13 +34558,13 @@
     </row>
     <row r="1225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1225" s="5" t="s">
+        <v>2297</v>
+      </c>
+      <c r="B1225" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1225" s="3" t="s">
         <v>2298</v>
-      </c>
-      <c r="B1225" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1225" s="3" t="s">
-        <v>2299</v>
       </c>
       <c r="D1225" s="2" t="s">
         <v>20</v>
@@ -34513,13 +34572,13 @@
     </row>
     <row r="1226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1226" s="5" t="s">
+        <v>2300</v>
+      </c>
+      <c r="B1226" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1226" s="3" t="s">
         <v>2301</v>
-      </c>
-      <c r="B1226" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1226" s="3" t="s">
-        <v>2302</v>
       </c>
       <c r="D1226" s="2" t="s">
         <v>7</v>
@@ -34541,13 +34600,13 @@
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1228" s="5" t="s">
+        <v>2304</v>
+      </c>
+      <c r="B1228" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1228" s="3" t="s">
         <v>2305</v>
-      </c>
-      <c r="B1228" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1228" s="3" t="s">
-        <v>2306</v>
       </c>
       <c r="D1228" s="2" t="s">
         <v>20</v>
@@ -34555,13 +34614,13 @@
     </row>
     <row r="1229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1229" s="5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B1229" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1229" s="3" t="s">
         <v>2309</v>
-      </c>
-      <c r="B1229" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1229" s="3" t="s">
-        <v>2310</v>
       </c>
       <c r="D1229" s="2" t="s">
         <v>20</v>
@@ -34569,13 +34628,13 @@
     </row>
     <row r="1230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1230" s="5" t="s">
+        <v>2308</v>
+      </c>
+      <c r="B1230" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1230" s="3" t="s">
         <v>2309</v>
-      </c>
-      <c r="B1230" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1230" s="3" t="s">
-        <v>2310</v>
       </c>
       <c r="D1230" s="2" t="s">
         <v>20</v>
@@ -34597,13 +34656,13 @@
     </row>
     <row r="1232" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1232" s="5" t="s">
+        <v>2312</v>
+      </c>
+      <c r="B1232" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1232" s="3" t="s">
         <v>2313</v>
-      </c>
-      <c r="B1232" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1232" s="3" t="s">
-        <v>2314</v>
       </c>
       <c r="D1232" s="2" t="s">
         <v>20</v>
@@ -34611,7 +34670,7 @@
     </row>
     <row r="1233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1233" s="5" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B1233" s="5" t="s">
         <v>68</v>
@@ -34625,13 +34684,13 @@
     </row>
     <row r="1234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1234" s="5" t="s">
+        <v>2317</v>
+      </c>
+      <c r="B1234" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1234" s="3" t="s">
         <v>2318</v>
-      </c>
-      <c r="B1234" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1234" s="3" t="s">
-        <v>2319</v>
       </c>
       <c r="D1234" s="2" t="s">
         <v>7</v>
@@ -34639,13 +34698,13 @@
     </row>
     <row r="1235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1235" s="5" t="s">
+        <v>2320</v>
+      </c>
+      <c r="B1235" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1235" s="3" t="s">
         <v>2321</v>
-      </c>
-      <c r="B1235" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1235" s="3" t="s">
-        <v>2322</v>
       </c>
       <c r="D1235" s="2" t="s">
         <v>7</v>
@@ -34653,13 +34712,13 @@
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1236" s="5" t="s">
+        <v>2323</v>
+      </c>
+      <c r="B1236" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1236" s="3" t="s">
         <v>2324</v>
-      </c>
-      <c r="B1236" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1236" s="3" t="s">
-        <v>2325</v>
       </c>
       <c r="D1236" s="2" t="s">
         <v>7</v>
@@ -34667,13 +34726,13 @@
     </row>
     <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1237" s="5" t="s">
+        <v>2326</v>
+      </c>
+      <c r="B1237" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1237" s="3" t="s">
         <v>2327</v>
-      </c>
-      <c r="B1237" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1237" s="3" t="s">
-        <v>2328</v>
       </c>
       <c r="D1237" s="2" t="s">
         <v>7</v>
@@ -34681,16 +34740,72 @@
     </row>
     <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1238" s="5" t="s">
+        <v>2329</v>
+      </c>
+      <c r="B1238" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1238" s="3" t="s">
         <v>2330</v>
       </c>
-      <c r="B1238" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1238" s="3" t="s">
-        <v>2331</v>
-      </c>
       <c r="D1238" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1239" s="1" t="s">
+        <v>2059</v>
+      </c>
+      <c r="B1239" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>2060</v>
+      </c>
+      <c r="D1239" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1240" s="5" t="s">
+        <v>2091</v>
+      </c>
+      <c r="B1240" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1240" s="3" t="s">
+        <v>2092</v>
+      </c>
+      <c r="D1240" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1241" s="5" t="s">
+        <v>2336</v>
+      </c>
+      <c r="B1241" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1241" s="3" t="s">
+        <v>2337</v>
+      </c>
+      <c r="D1241" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1242" s="5" t="s">
+        <v>2339</v>
+      </c>
+      <c r="B1242" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1242" s="3" t="s">
+        <v>2340</v>
+      </c>
+      <c r="D1242" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0627E266-F969-4325-BBC9-1148F1DBAFFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095409D5-3DE5-4CE6-A217-72243D41D7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
@@ -6873,9 +6873,6 @@
     <t>COMP 1962</t>
   </si>
   <si>
-    <t>DISJUNTOR DE CAIXA ABERTA TRIPOLAR  2000A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 03/2024)</t>
-  </si>
-  <si>
     <t>Quadro distrib. chapa pintada - sobrepor - Barr. trif., disj. geral, compacto - DIN - Cap. 18 disj. unip. - In barr. 100 A</t>
   </si>
   <si>
@@ -7063,6 +7060,9 @@
   </si>
   <si>
     <t>MICROFONE DE PISO (REFERÊNCIA: SBC 068282 01/2025)</t>
+  </si>
+  <si>
+    <t>DISJUNTOR CAIXA ABERTA TRIPOLAR  2000A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 03/2024)</t>
   </si>
 </sst>
 </file>
@@ -17182,7 +17182,7 @@
     </row>
     <row r="1215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1215" s="3" t="s">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="B1215" s="5" t="s">
         <v>7</v>
@@ -17190,7 +17190,7 @@
     </row>
     <row r="1216" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1216" s="3" t="s">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="B1216" s="5" t="s">
         <v>7</v>
@@ -17198,7 +17198,7 @@
     </row>
     <row r="1217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1217" s="3" t="s">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="B1217" s="5" t="s">
         <v>20</v>
@@ -17206,7 +17206,7 @@
     </row>
     <row r="1218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1218" s="3" t="s">
-        <v>2285</v>
+        <v>2284</v>
       </c>
       <c r="B1218" s="5" t="s">
         <v>7</v>
@@ -17214,7 +17214,7 @@
     </row>
     <row r="1219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1219" s="3" t="s">
-        <v>2286</v>
+        <v>2285</v>
       </c>
       <c r="B1219" s="5" t="s">
         <v>7</v>
@@ -17222,7 +17222,7 @@
     </row>
     <row r="1220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1220" s="3" t="s">
-        <v>2289</v>
+        <v>2288</v>
       </c>
       <c r="B1220" s="5" t="s">
         <v>20</v>
@@ -17230,7 +17230,7 @@
     </row>
     <row r="1221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1221" s="3" t="s">
-        <v>2290</v>
+        <v>2289</v>
       </c>
       <c r="B1221" s="5" t="s">
         <v>20</v>
@@ -17238,7 +17238,7 @@
     </row>
     <row r="1222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1222" s="3" t="s">
-        <v>2291</v>
+        <v>2290</v>
       </c>
       <c r="B1222" s="5" t="s">
         <v>20</v>
@@ -17246,7 +17246,7 @@
     </row>
     <row r="1223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1223" s="3" t="s">
-        <v>2294</v>
+        <v>2293</v>
       </c>
       <c r="B1223" s="5" t="s">
         <v>20</v>
@@ -17254,7 +17254,7 @@
     </row>
     <row r="1224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1224" s="3" t="s">
-        <v>2295</v>
+        <v>2294</v>
       </c>
       <c r="B1224" s="5" t="s">
         <v>20</v>
@@ -17262,7 +17262,7 @@
     </row>
     <row r="1225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1225" s="3" t="s">
-        <v>2296</v>
+        <v>2295</v>
       </c>
       <c r="B1225" s="5" t="s">
         <v>20</v>
@@ -17270,7 +17270,7 @@
     </row>
     <row r="1226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1226" s="3" t="s">
-        <v>2299</v>
+        <v>2298</v>
       </c>
       <c r="B1226" s="5" t="s">
         <v>7</v>
@@ -17278,7 +17278,7 @@
     </row>
     <row r="1227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1227" s="3" t="s">
-        <v>2302</v>
+        <v>2301</v>
       </c>
       <c r="B1227" s="5" t="s">
         <v>20</v>
@@ -17286,7 +17286,7 @@
     </row>
     <row r="1228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1228" s="3" t="s">
-        <v>2303</v>
+        <v>2302</v>
       </c>
       <c r="B1228" s="5" t="s">
         <v>20</v>
@@ -17294,7 +17294,7 @@
     </row>
     <row r="1229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1229" s="3" t="s">
-        <v>2306</v>
+        <v>2305</v>
       </c>
       <c r="B1229" s="5" t="s">
         <v>20</v>
@@ -17302,7 +17302,7 @@
     </row>
     <row r="1230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1230" s="3" t="s">
-        <v>2307</v>
+        <v>2306</v>
       </c>
       <c r="B1230" s="5" t="s">
         <v>20</v>
@@ -17310,7 +17310,7 @@
     </row>
     <row r="1231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1231" s="3" t="s">
-        <v>2310</v>
+        <v>2309</v>
       </c>
       <c r="B1231" s="5" t="s">
         <v>20</v>
@@ -17318,7 +17318,7 @@
     </row>
     <row r="1232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1232" s="3" t="s">
-        <v>2311</v>
+        <v>2310</v>
       </c>
       <c r="B1232" s="5" t="s">
         <v>20</v>
@@ -17326,7 +17326,7 @@
     </row>
     <row r="1233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1233" s="3" t="s">
-        <v>2314</v>
+        <v>2313</v>
       </c>
       <c r="B1233" s="5" t="s">
         <v>7</v>
@@ -17334,7 +17334,7 @@
     </row>
     <row r="1234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1234" s="3" t="s">
-        <v>2316</v>
+        <v>2315</v>
       </c>
       <c r="B1234" s="5" t="s">
         <v>7</v>
@@ -17342,7 +17342,7 @@
     </row>
     <row r="1235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1235" s="3" t="s">
-        <v>2319</v>
+        <v>2318</v>
       </c>
       <c r="B1235" s="5" t="s">
         <v>7</v>
@@ -17350,7 +17350,7 @@
     </row>
     <row r="1236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1236" s="3" t="s">
-        <v>2322</v>
+        <v>2321</v>
       </c>
       <c r="B1236" s="5" t="s">
         <v>7</v>
@@ -17358,7 +17358,7 @@
     </row>
     <row r="1237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1237" s="3" t="s">
-        <v>2325</v>
+        <v>2324</v>
       </c>
       <c r="B1237" s="5" t="s">
         <v>7</v>
@@ -17366,7 +17366,7 @@
     </row>
     <row r="1238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1238" s="3" t="s">
-        <v>2328</v>
+        <v>2327</v>
       </c>
       <c r="B1238" s="5" t="s">
         <v>20</v>
@@ -17374,7 +17374,7 @@
     </row>
     <row r="1239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1239" s="3" t="s">
-        <v>2333</v>
+        <v>2332</v>
       </c>
       <c r="B1239" s="5" t="s">
         <v>7</v>
@@ -17382,7 +17382,7 @@
     </row>
     <row r="1240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1240" s="3" t="s">
-        <v>2334</v>
+        <v>2333</v>
       </c>
       <c r="B1240" s="5" t="s">
         <v>7</v>
@@ -17390,7 +17390,7 @@
     </row>
     <row r="1241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1241" s="3" t="s">
-        <v>2335</v>
+        <v>2334</v>
       </c>
       <c r="B1241" s="5" t="s">
         <v>7</v>
@@ -17398,7 +17398,7 @@
     </row>
     <row r="1242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1242" s="3" t="s">
-        <v>2338</v>
+        <v>2337</v>
       </c>
       <c r="B1242" s="5" t="s">
         <v>7</v>
@@ -31156,13 +31156,13 @@
     </row>
     <row r="982" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A982" s="5" t="s">
+        <v>2330</v>
+      </c>
+      <c r="B982" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C982" s="3" t="s">
         <v>2331</v>
-      </c>
-      <c r="B982" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C982" s="3" t="s">
-        <v>2332</v>
       </c>
       <c r="D982" s="2" t="s">
         <v>7</v>
@@ -34403,14 +34403,14 @@
       </c>
     </row>
     <row r="1214" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1214" s="5" t="s">
+      <c r="A1214" s="1" t="s">
         <v>2276</v>
       </c>
-      <c r="B1214" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1214" s="3" t="s">
-        <v>2277</v>
+      <c r="B1214" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>2340</v>
       </c>
       <c r="D1214" s="2" t="s">
         <v>7</v>
@@ -34418,13 +34418,13 @@
     </row>
     <row r="1215" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1215" s="5" t="s">
+        <v>2278</v>
+      </c>
+      <c r="B1215" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1215" s="3" t="s">
         <v>2279</v>
-      </c>
-      <c r="B1215" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1215" s="3" t="s">
-        <v>2280</v>
       </c>
       <c r="D1215" s="2" t="s">
         <v>7</v>
@@ -34460,13 +34460,13 @@
     </row>
     <row r="1218" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1218" s="5" t="s">
+        <v>2282</v>
+      </c>
+      <c r="B1218" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1218" s="3" t="s">
         <v>2283</v>
-      </c>
-      <c r="B1218" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1218" s="3" t="s">
-        <v>2284</v>
       </c>
       <c r="D1218" s="2" t="s">
         <v>7</v>
@@ -34474,13 +34474,13 @@
     </row>
     <row r="1219" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1219" s="5" t="s">
+        <v>2286</v>
+      </c>
+      <c r="B1219" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1219" s="3" t="s">
         <v>2287</v>
-      </c>
-      <c r="B1219" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1219" s="3" t="s">
-        <v>2288</v>
       </c>
       <c r="D1219" s="2" t="s">
         <v>7</v>
@@ -34488,13 +34488,13 @@
     </row>
     <row r="1220" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1220" s="5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1220" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1220" s="3" t="s">
         <v>2292</v>
-      </c>
-      <c r="B1220" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1220" s="3" t="s">
-        <v>2293</v>
       </c>
       <c r="D1220" s="2" t="s">
         <v>20</v>
@@ -34502,13 +34502,13 @@
     </row>
     <row r="1221" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1221" s="5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1221" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1221" s="3" t="s">
         <v>2292</v>
-      </c>
-      <c r="B1221" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1221" s="3" t="s">
-        <v>2293</v>
       </c>
       <c r="D1221" s="2" t="s">
         <v>20</v>
@@ -34516,13 +34516,13 @@
     </row>
     <row r="1222" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1222" s="5" t="s">
+        <v>2291</v>
+      </c>
+      <c r="B1222" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1222" s="3" t="s">
         <v>2292</v>
-      </c>
-      <c r="B1222" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1222" s="3" t="s">
-        <v>2293</v>
       </c>
       <c r="D1222" s="2" t="s">
         <v>20</v>
@@ -34530,13 +34530,13 @@
     </row>
     <row r="1223" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1223" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1223" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1223" s="3" t="s">
         <v>2297</v>
-      </c>
-      <c r="B1223" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1223" s="3" t="s">
-        <v>2298</v>
       </c>
       <c r="D1223" s="2" t="s">
         <v>20</v>
@@ -34544,13 +34544,13 @@
     </row>
     <row r="1224" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1224" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1224" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1224" s="3" t="s">
         <v>2297</v>
-      </c>
-      <c r="B1224" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1224" s="3" t="s">
-        <v>2298</v>
       </c>
       <c r="D1224" s="2" t="s">
         <v>20</v>
@@ -34558,13 +34558,13 @@
     </row>
     <row r="1225" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1225" s="5" t="s">
+        <v>2296</v>
+      </c>
+      <c r="B1225" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1225" s="3" t="s">
         <v>2297</v>
-      </c>
-      <c r="B1225" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1225" s="3" t="s">
-        <v>2298</v>
       </c>
       <c r="D1225" s="2" t="s">
         <v>20</v>
@@ -34572,13 +34572,13 @@
     </row>
     <row r="1226" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1226" s="5" t="s">
+        <v>2299</v>
+      </c>
+      <c r="B1226" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1226" s="3" t="s">
         <v>2300</v>
-      </c>
-      <c r="B1226" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1226" s="3" t="s">
-        <v>2301</v>
       </c>
       <c r="D1226" s="2" t="s">
         <v>7</v>
@@ -34600,13 +34600,13 @@
     </row>
     <row r="1228" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1228" s="5" t="s">
+        <v>2303</v>
+      </c>
+      <c r="B1228" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1228" s="3" t="s">
         <v>2304</v>
-      </c>
-      <c r="B1228" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1228" s="3" t="s">
-        <v>2305</v>
       </c>
       <c r="D1228" s="2" t="s">
         <v>20</v>
@@ -34614,13 +34614,13 @@
     </row>
     <row r="1229" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1229" s="5" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1229" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1229" s="3" t="s">
         <v>2308</v>
-      </c>
-      <c r="B1229" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1229" s="3" t="s">
-        <v>2309</v>
       </c>
       <c r="D1229" s="2" t="s">
         <v>20</v>
@@ -34628,13 +34628,13 @@
     </row>
     <row r="1230" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1230" s="5" t="s">
+        <v>2307</v>
+      </c>
+      <c r="B1230" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1230" s="3" t="s">
         <v>2308</v>
-      </c>
-      <c r="B1230" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1230" s="3" t="s">
-        <v>2309</v>
       </c>
       <c r="D1230" s="2" t="s">
         <v>20</v>
@@ -34656,13 +34656,13 @@
     </row>
     <row r="1232" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A1232" s="5" t="s">
+        <v>2311</v>
+      </c>
+      <c r="B1232" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1232" s="3" t="s">
         <v>2312</v>
-      </c>
-      <c r="B1232" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1232" s="3" t="s">
-        <v>2313</v>
       </c>
       <c r="D1232" s="2" t="s">
         <v>20</v>
@@ -34670,7 +34670,7 @@
     </row>
     <row r="1233" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1233" s="5" t="s">
-        <v>2315</v>
+        <v>2314</v>
       </c>
       <c r="B1233" s="5" t="s">
         <v>68</v>
@@ -34684,13 +34684,13 @@
     </row>
     <row r="1234" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1234" s="5" t="s">
+        <v>2316</v>
+      </c>
+      <c r="B1234" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1234" s="3" t="s">
         <v>2317</v>
-      </c>
-      <c r="B1234" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1234" s="3" t="s">
-        <v>2318</v>
       </c>
       <c r="D1234" s="2" t="s">
         <v>7</v>
@@ -34698,13 +34698,13 @@
     </row>
     <row r="1235" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1235" s="5" t="s">
+        <v>2319</v>
+      </c>
+      <c r="B1235" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1235" s="3" t="s">
         <v>2320</v>
-      </c>
-      <c r="B1235" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1235" s="3" t="s">
-        <v>2321</v>
       </c>
       <c r="D1235" s="2" t="s">
         <v>7</v>
@@ -34712,13 +34712,13 @@
     </row>
     <row r="1236" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1236" s="5" t="s">
+        <v>2322</v>
+      </c>
+      <c r="B1236" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1236" s="3" t="s">
         <v>2323</v>
-      </c>
-      <c r="B1236" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1236" s="3" t="s">
-        <v>2324</v>
       </c>
       <c r="D1236" s="2" t="s">
         <v>7</v>
@@ -34726,13 +34726,13 @@
     </row>
     <row r="1237" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1237" s="5" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B1237" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1237" s="3" t="s">
         <v>2326</v>
-      </c>
-      <c r="B1237" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1237" s="3" t="s">
-        <v>2327</v>
       </c>
       <c r="D1237" s="2" t="s">
         <v>7</v>
@@ -34740,13 +34740,13 @@
     </row>
     <row r="1238" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1238" s="5" t="s">
+        <v>2328</v>
+      </c>
+      <c r="B1238" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1238" s="3" t="s">
         <v>2329</v>
-      </c>
-      <c r="B1238" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1238" s="3" t="s">
-        <v>2330</v>
       </c>
       <c r="D1238" s="2" t="s">
         <v>20</v>
@@ -34756,7 +34756,7 @@
       <c r="A1239" s="1" t="s">
         <v>2059</v>
       </c>
-      <c r="B1239" t="s">
+      <c r="B1239" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C1239" t="s">
@@ -34770,7 +34770,7 @@
       <c r="A1240" s="5" t="s">
         <v>2091</v>
       </c>
-      <c r="B1240" t="s">
+      <c r="B1240" s="1" t="s">
         <v>68</v>
       </c>
       <c r="C1240" s="3" t="s">
@@ -34782,13 +34782,13 @@
     </row>
     <row r="1241" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1241" s="5" t="s">
+        <v>2335</v>
+      </c>
+      <c r="B1241" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1241" s="3" t="s">
         <v>2336</v>
-      </c>
-      <c r="B1241" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1241" s="3" t="s">
-        <v>2337</v>
       </c>
       <c r="D1241" s="2" t="s">
         <v>7</v>
@@ -34796,13 +34796,13 @@
     </row>
     <row r="1242" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1242" s="5" t="s">
+        <v>2338</v>
+      </c>
+      <c r="B1242" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1242" s="3" t="s">
         <v>2339</v>
-      </c>
-      <c r="B1242" t="s">
-        <v>68</v>
-      </c>
-      <c r="C1242" s="3" t="s">
-        <v>2340</v>
       </c>
       <c r="D1242" s="2" t="s">
         <v>7</v>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{095409D5-3DE5-4CE6-A217-72243D41D7E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1443F1-3A68-4086-A5FD-A85E2D1E529C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6714" uniqueCount="2341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6720" uniqueCount="2344">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -7063,6 +7063,15 @@
   </si>
   <si>
     <t>DISJUNTOR CAIXA ABERTA TRIPOLAR  2000A - FORNECIMENTO E INSTALAÇÃO. (COMPOSIÇÃO DE REFERÊNCIA: SINAPI 101900 03/2024)</t>
+  </si>
+  <si>
+    <t>COMP 1976</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 450A , 30X5 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>Cobre - Barra - m - 30x5mm</t>
   </si>
 </sst>
 </file>
@@ -7461,7 +7470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1242"/>
+  <dimension ref="A1:B1243"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -17404,6 +17413,14 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1243" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1243" s="3" t="s">
+        <v>2343</v>
+      </c>
+      <c r="B1243" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17411,7 +17428,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1242"/>
+  <dimension ref="A1:D1243"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -34808,6 +34825,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1243" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1243" s="5" t="s">
+        <v>2341</v>
+      </c>
+      <c r="B1243" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1243" s="3" t="s">
+        <v>2342</v>
+      </c>
+      <c r="D1243" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C1443F1-3A68-4086-A5FD-A85E2D1E529C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37DF0E1-8E50-4418-B24A-0BBAD34DBFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6720" uniqueCount="2344">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6726" uniqueCount="2347">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -7072,6 +7072,15 @@
   </si>
   <si>
     <t>Cobre - Barra - m - 30x5mm</t>
+  </si>
+  <si>
+    <t>Cobre - Barra - m - 40x5mm</t>
+  </si>
+  <si>
+    <t>COMP 1977</t>
+  </si>
+  <si>
+    <t>BARRAMENTO DE COBRE PARA 510A , 40X5 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
   </si>
 </sst>
 </file>
@@ -7470,7 +7479,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1243"/>
+  <dimension ref="A1:B1244"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -17421,6 +17430,14 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1244" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1244" s="3" t="s">
+        <v>2344</v>
+      </c>
+      <c r="B1244" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17428,7 +17445,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1243"/>
+  <dimension ref="A1:D1244"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -34839,6 +34856,20 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1244" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1244" s="5" t="s">
+        <v>2345</v>
+      </c>
+      <c r="B1244" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1244" s="3" t="s">
+        <v>2346</v>
+      </c>
+      <c r="D1244" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:D226" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}"/>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/3D/base_de_dados.xlsx
+++ b/3D/base_de_dados.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PC- lixos\Downloads-24-11-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D37DF0E1-8E50-4418-B24A-0BBAD34DBFF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E24B10-0C4B-4CCD-9F35-4561E172E30C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{F08DF800-D7FB-4182-BEE8-B029C50FA673}"/>
   </bookViews>
   <sheets>
     <sheet name="Associa" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6726" uniqueCount="2347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6804" uniqueCount="2376">
   <si>
     <t>CÓDIGO</t>
   </si>
@@ -7081,6 +7081,93 @@
   </si>
   <si>
     <t>BARRAMENTO DE COBRE PARA 510A , 40X5 MM - (COMPOSIÇÃO DE REFERÊNCIA: 9006083 SIURB 07/2024)</t>
+  </si>
+  <si>
+    <t>- COMPOSIÇÃO PRÓPRIA - UNIDADES - PAINEL MODULAR -1200x600x400mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23</t>
+  </si>
+  <si>
+    <t>COMP 135</t>
+  </si>
+  <si>
+    <t>PAINEL MODULAR -1200x600x400mm- FORNECIMENTO E INSTALAÇÃO. AF_10/2020 - (COMPOSIÇÃO REFERENCIA CODIGO 101882 SINAPI 09/23)</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 16 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 25 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 25 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 35 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 35 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 4 mm² - Preto</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 4 mm² - Verde-amarelo</t>
+  </si>
+  <si>
+    <t>Cabo unipolar - Solar - Cobre - Isol. XLPE - 1,8KV - 4 mm² - Vermelho</t>
+  </si>
+  <si>
+    <t>COMP 1998</t>
+  </si>
+  <si>
+    <t>CABO FOTOVOLTAICO 16 MM² INSTALADO EM ELETRODUTO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (REFERÊNCIA: SINAPI 103503 08/2025)</t>
+  </si>
+  <si>
+    <t>COMP 1999</t>
+  </si>
+  <si>
+    <t>CABO FOTOVOLTAICO 25 MM² INSTALADO EM ELETRODUTO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (REFERÊNCIA: SINAPI 103503 08/2025)</t>
+  </si>
+  <si>
+    <t>COMP 2000</t>
+  </si>
+  <si>
+    <t>CABO FOTOVOLTAICO 35 MM² INSTALADO EM ELETRODUTO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (REFERÊNCIA: SINAPI 103503 08/2025)</t>
+  </si>
+  <si>
+    <t>COMP 2004</t>
+  </si>
+  <si>
+    <t>CABO FOTOVOLTAICO 4 MM² INSTALADO EM ELETRODUTO - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (REFERÊNCIA: SINAPI 103503 08/2025)</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Disjuntor corrente contínua - 2 polos - 800 Vcc - DIN - 20 A - 10 kA</t>
+  </si>
+  <si>
+    <t>COMP 1621</t>
+  </si>
+  <si>
+    <t>DISJUNTOR BIPOLAR TIPO DIN DE CORRENTE CONTÍNUA, CORRENTE NOMINAL DE 20A E 800VCC - FORNECIMENTO E INSTALAÇÃO. (REFERÊNCIA SINAPI 93662 12/2024)</t>
+  </si>
+  <si>
+    <t>COMP 1646</t>
+  </si>
+  <si>
+    <t>STRING BOX PARA SISTEMA FOTOVOLTAICO, 36 SLOT'S TIPO DIN - FORNECIMENTO E INSTALAÇÃO. AF_12/2021 (COMPOSIÇÃO REFERÊNCIA: SINAPI 103508 - 08/2025)</t>
+  </si>
+  <si>
+    <t>Elementos fotovoltaicos - Caixa de junção - Cap. 36 slot's DIN - IP65</t>
+  </si>
+  <si>
+    <t>Dispositivo de Proteção - Dispositivo de proteção contra surto - 275 V - 40 KA</t>
+  </si>
+  <si>
+    <t>COMP 140</t>
+  </si>
+  <si>
+    <t>DISPOSITIVO DE PROTEÇÃO CONTRA SURTO DPS 45KA - 275V (COMPOSIÇÃO DE REFERÊNCIA: ORSE 9041 - 05/2023)</t>
+  </si>
+  <si>
+    <t>Caixa de passagem - sobrepor - Aço pintada - ref Lukbox - 300x300x120 mm</t>
   </si>
 </sst>
 </file>
@@ -7479,7 +7566,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A62C0A3C-3A73-4C24-9726-9CC231B21D7A}">
-  <dimension ref="A1:B1244"/>
+  <dimension ref="A1:B1257"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="96.77734375" style="3" bestFit="1" customWidth="1"/>
@@ -17438,6 +17525,110 @@
         <v>20</v>
       </c>
     </row>
+    <row r="1245" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1245" s="3" t="s">
+        <v>2347</v>
+      </c>
+      <c r="B1245" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1246" s="3" t="s">
+        <v>2350</v>
+      </c>
+      <c r="B1246" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1247" s="3" t="s">
+        <v>2351</v>
+      </c>
+      <c r="B1247" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1248" s="3" t="s">
+        <v>2352</v>
+      </c>
+      <c r="B1248" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1249" s="3" t="s">
+        <v>2353</v>
+      </c>
+      <c r="B1249" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1250" s="3" t="s">
+        <v>2354</v>
+      </c>
+      <c r="B1250" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1251" s="3" t="s">
+        <v>2355</v>
+      </c>
+      <c r="B1251" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1252" s="3" t="s">
+        <v>2356</v>
+      </c>
+      <c r="B1252" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1253" s="3" t="s">
+        <v>2357</v>
+      </c>
+      <c r="B1253" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1254" s="3" t="s">
+        <v>2366</v>
+      </c>
+      <c r="B1254" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1255" s="3" t="s">
+        <v>2371</v>
+      </c>
+      <c r="B1255" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1256" s="3" t="s">
+        <v>2372</v>
+      </c>
+      <c r="B1256" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1257" s="3" t="s">
+        <v>2375</v>
+      </c>
+      <c r="B1257" s="5" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -17445,7 +17636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DACEE6F-7DD5-4F5D-8CC1-2F57EE446892}">
-  <dimension ref="A1:D1244"/>
+  <dimension ref="A1:D1257"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.33203125" style="5" bestFit="1" customWidth="1"/>
@@ -33166,7 +33357,7 @@
       <c r="A1123" s="1">
         <v>97887</v>
       </c>
-      <c r="B1123" s="1" t="s">
+      <c r="B1123" s="6" t="s">
         <v>5</v>
       </c>
       <c r="C1123" s="1" t="s">
@@ -34370,7 +34561,7 @@
       <c r="A1209" s="1" t="s">
         <v>2266</v>
       </c>
-      <c r="B1209" s="1" t="s">
+      <c r="B1209" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1209" t="s">
@@ -34440,7 +34631,7 @@
       <c r="A1214" s="1" t="s">
         <v>2276</v>
       </c>
-      <c r="B1214" s="1" t="s">
+      <c r="B1214" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1214" t="s">
@@ -34790,7 +34981,7 @@
       <c r="A1239" s="1" t="s">
         <v>2059</v>
       </c>
-      <c r="B1239" s="1" t="s">
+      <c r="B1239" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1239" t="s">
@@ -34804,7 +34995,7 @@
       <c r="A1240" s="5" t="s">
         <v>2091</v>
       </c>
-      <c r="B1240" s="1" t="s">
+      <c r="B1240" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1240" s="3" t="s">
@@ -34818,7 +35009,7 @@
       <c r="A1241" s="5" t="s">
         <v>2335</v>
       </c>
-      <c r="B1241" s="1" t="s">
+      <c r="B1241" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1241" s="3" t="s">
@@ -34832,7 +35023,7 @@
       <c r="A1242" s="5" t="s">
         <v>2338</v>
       </c>
-      <c r="B1242" s="1" t="s">
+      <c r="B1242" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1242" s="3" t="s">
@@ -34846,7 +35037,7 @@
       <c r="A1243" s="5" t="s">
         <v>2341</v>
       </c>
-      <c r="B1243" s="1" t="s">
+      <c r="B1243" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1243" s="3" t="s">
@@ -34860,7 +35051,7 @@
       <c r="A1244" s="5" t="s">
         <v>2345</v>
       </c>
-      <c r="B1244" s="1" t="s">
+      <c r="B1244" s="6" t="s">
         <v>68</v>
       </c>
       <c r="C1244" s="3" t="s">
@@ -34868,6 +35059,188 @@
       </c>
       <c r="D1244" s="2" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1245" s="5" t="s">
+        <v>2348</v>
+      </c>
+      <c r="B1245" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1245" s="3" t="s">
+        <v>2349</v>
+      </c>
+      <c r="D1245" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1246" s="5" t="s">
+        <v>2358</v>
+      </c>
+      <c r="B1246" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1246" s="3" t="s">
+        <v>2359</v>
+      </c>
+      <c r="D1246" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1247" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B1247" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1247" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D1247" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1248" s="5" t="s">
+        <v>2360</v>
+      </c>
+      <c r="B1248" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1248" s="3" t="s">
+        <v>2361</v>
+      </c>
+      <c r="D1248" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1249" s="5" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B1249" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1249" s="3" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D1249" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1250" s="5" t="s">
+        <v>2362</v>
+      </c>
+      <c r="B1250" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1250" s="3" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D1250" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1251" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B1251" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1251" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D1251" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1252" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B1252" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1252" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D1252" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1253" s="5" t="s">
+        <v>2364</v>
+      </c>
+      <c r="B1253" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1253" s="3" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D1253" s="2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1254" s="5" t="s">
+        <v>2367</v>
+      </c>
+      <c r="B1254" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1254" s="3" t="s">
+        <v>2368</v>
+      </c>
+      <c r="D1254" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1255" s="5" t="s">
+        <v>2369</v>
+      </c>
+      <c r="B1255" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1255" s="3" t="s">
+        <v>2370</v>
+      </c>
+      <c r="D1255" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1256" s="5" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B1256" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1256" s="3" t="s">
+        <v>2374</v>
+      </c>
+      <c r="D1256" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1257" s="5" t="s">
+        <v>1769</v>
+      </c>
+      <c r="B1257" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1257" s="3" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D1257" s="2" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
